--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32666-2025</t>
+          <t>A 17932-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1035,14 +1035,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45838</v>
+        <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1088,258 +1088,258 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17932-2023 artfynd.xlsx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17932-2023 karta.png", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17932-2023 georefererad karta.tif", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17932-2023 FSC-klagomål.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17932-2023 FSC-klagomål mail.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17932-2023 tillsynsbegäran.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17932-2023 tillsynsbegäran mail.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14752-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45742</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 14752-2025 artfynd.xlsx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 14752-2025 karta.png", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 14752-2025 georefererad karta.tif", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14752-2025 FSC-klagomål.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14752-2025 FSC-klagomål mail.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14752-2025 tillsynsbegäran.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14752-2025 tillsynsbegäran mail.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32666-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Guldlockmossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 32666-2025 artfynd.xlsx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 32666-2025 karta.png", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 32666-2025 georefererad karta.tif", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 32666-2025 FSC-klagomål.docx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 32666-2025 FSC-klagomål mail.docx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 32666-2025 tillsynsbegäran.docx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 32666-2025 tillsynsbegäran mail.docx", "A 32666-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17932-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17932-2023 artfynd.xlsx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17932-2023 karta.png", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17932-2023 georefererad karta.tif", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17932-2023 FSC-klagomål.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17932-2023 FSC-klagomål mail.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17932-2023 tillsynsbegäran.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17932-2023 tillsynsbegäran mail.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 14752-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45742</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 14752-2025 artfynd.xlsx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 14752-2025 karta.png", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 14752-2025 georefererad karta.tif", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14752-2025 FSC-klagomål.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14752-2025 FSC-klagomål mail.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14752-2025 tillsynsbegäran.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14752-2025 tillsynsbegäran mail.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45238</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25575-2025</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1678,14 +1678,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45040</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1697,19 +1697,14 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1736,49 +1731,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10515-2025</t>
+          <t>A 47783-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45721</v>
+        <v>45931</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,13 +1803,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1844,46 +1839,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 47783-2025</t>
+          <t>A 18733-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1892,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45931</v>
+        <v>46128</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,17 +1908,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1937,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1953,42 +1948,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55331-2025</t>
+          <t>A 48163-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +1997,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45971</v>
+        <v>45589</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,13 +2013,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2058,147 +2053,151 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 55331-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Mandelriska</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 18733-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11709-2024</t>
+          <t>A 39899-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2212,10 +2211,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45166</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2228,16 +2227,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>15.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2252,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2268,35 +2267,39 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
         <v/>
       </c>
     </row>
@@ -2320,7 +2323,7 @@
         <v>46191</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2411,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5009-2025</t>
+          <t>A 11709-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2422,10 +2425,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45691</v>
+        <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2438,17 +2441,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2462,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2478,260 +2481,256 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 56739-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 5009-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>Ljungpipare</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 17920-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 39899-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45166</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48163-2024</t>
+          <t>A 25575-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2741,14 +2740,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45589</v>
+        <v>45803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,14 +2759,19 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>14.4</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2794,53 +2798,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56739-2023</t>
+          <t>A 10515-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,14 +2850,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45244</v>
+        <v>45721</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2910,35 +2910,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19561-2022</t>
+          <t>A 12828-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44693</v>
+        <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12828-2022</t>
+          <t>A 12836-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12836-2022</t>
+          <t>A 19561-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44642</v>
+        <v>44693</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60987-2021</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44497</v>
+        <v>44788</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 60987-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4574,7 +4574,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10977-2022</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44628</v>
+        <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19559-2022</t>
+          <t>A 10977-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44693</v>
+        <v>44628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18157-2022</t>
+          <t>A 11979-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44684</v>
+        <v>44635</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2377-2022</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44579</v>
+        <v>45244</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13923-2022</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44650</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4951,13 +4951,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5000,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29373-2022</t>
+          <t>A 18157-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5014,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44753</v>
+        <v>44684</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5029,13 +5024,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>12.5</v>
+        <v>6.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5078,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11979-2022</t>
+          <t>A 19559-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5092,10 +5082,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44635</v>
+        <v>44693</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5108,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5151,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29345-2022</t>
+          <t>A 2377-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5165,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44753</v>
+        <v>44579</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5181,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5224,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5238,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45592</v>
+        <v>45390</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 13923-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5307,14 +5297,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45517</v>
+        <v>44650</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5326,8 +5316,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5365,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5384,10 +5379,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45057</v>
+        <v>45419</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5395,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5443,7 +5438,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5457,10 +5452,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45545</v>
+        <v>44722</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5468,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5516,7 +5511,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 29373-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5525,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44683</v>
+        <v>44753</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5545,8 +5540,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45751</v>
+        <v>44824</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 29345-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44929</v>
+        <v>44753</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45345</v>
+        <v>45804</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5818,14 +5818,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45187</v>
+        <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5891,14 +5891,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45399</v>
+        <v>45397</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5910,8 +5910,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5950,11 +5955,31 @@
         <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr"/>
+      <c r="Z63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD63">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5964,14 +5989,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45399</v>
+        <v>45382</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +6009,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6027,7 +6052,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6041,10 +6066,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45238</v>
+        <v>45884</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6110,14 +6135,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45736</v>
+        <v>45250</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6173,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6187,10 +6212,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45736</v>
+        <v>45256</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6228,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6271,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6256,14 +6281,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45099</v>
+        <v>44973</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6301,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6344,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6333,10 +6358,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44852</v>
+        <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6349,7 +6374,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6392,7 +6417,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6406,10 +6431,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45728</v>
+        <v>45408</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6447,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6490,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6479,10 +6504,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45798</v>
+        <v>44852</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6495,7 +6520,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6563,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6552,10 +6577,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45313</v>
+        <v>45446</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6593,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6636,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6650,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45798</v>
+        <v>44769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6666,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6709,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6723,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45798</v>
+        <v>45294</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,7 +6739,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6757,7 +6782,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6771,10 +6796,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45799</v>
+        <v>45345</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6812,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6855,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6869,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6860,7 +6885,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6903,7 +6928,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6942,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45589</v>
+        <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6958,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7001,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7015,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45582</v>
+        <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7031,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7074,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7088,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45582</v>
+        <v>45337</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7104,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7147,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7136,10 +7161,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45811</v>
+        <v>45896</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7177,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7220,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7205,14 +7230,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45328</v>
+        <v>45896</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7224,13 +7249,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7273,7 +7293,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7287,10 +7307,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45603</v>
+        <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7303,7 +7323,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7346,7 +7366,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7360,10 +7380,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46024</v>
+        <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7376,7 +7396,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7419,7 +7439,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7433,10 +7453,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44881</v>
+        <v>46094</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7449,7 +7469,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7492,7 +7512,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7506,10 +7526,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45728</v>
+        <v>45905</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7522,7 +7542,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7565,7 +7585,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7579,10 +7599,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45897</v>
+        <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7595,7 +7615,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7638,7 +7658,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7652,10 +7672,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45896</v>
+        <v>45646</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7668,7 +7688,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7711,7 +7731,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7725,10 +7745,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45896</v>
+        <v>44881</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7741,7 +7761,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7784,7 +7804,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7798,10 +7818,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45896</v>
+        <v>46104</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7814,7 +7834,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7857,7 +7877,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7867,14 +7887,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45566</v>
+        <v>46104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7887,7 +7907,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7930,7 +7950,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 14886-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7944,10 +7964,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45896</v>
+        <v>46104</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7960,7 +7980,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8003,7 +8023,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8017,10 +8037,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45896</v>
+        <v>46104</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8033,7 +8053,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8076,7 +8096,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8090,10 +8110,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44909</v>
+        <v>45917</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8106,7 +8126,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8149,7 +8169,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8163,10 +8183,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45902</v>
+        <v>45918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8179,7 +8199,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8222,7 +8242,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8236,10 +8256,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45446</v>
+        <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8252,7 +8272,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8295,7 +8315,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8309,10 +8329,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8325,7 +8345,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8368,7 +8388,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8382,10 +8402,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44784</v>
+        <v>45399</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8398,7 +8418,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8441,7 +8461,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8451,14 +8471,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45215</v>
+        <v>45399</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8471,7 +8491,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8514,7 +8534,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8528,10 +8548,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45826</v>
+        <v>46111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8543,8 +8563,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8587,7 +8612,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8601,10 +8626,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44824</v>
+        <v>45922</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8617,7 +8642,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8660,7 +8685,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8670,14 +8695,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46044</v>
+        <v>45014</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8690,7 +8715,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8733,7 +8758,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8747,10 +8772,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45917</v>
+        <v>46119</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8763,7 +8788,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8806,7 +8831,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8820,10 +8845,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45917</v>
+        <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8836,7 +8861,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8879,7 +8904,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8893,10 +8918,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45917</v>
+        <v>45571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8909,7 +8934,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8952,7 +8977,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8966,10 +8991,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46035</v>
+        <v>46119</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8982,7 +9007,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9025,7 +9050,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9039,10 +9064,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46035</v>
+        <v>45030</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9055,7 +9080,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9098,7 +9123,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9108,14 +9133,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46035</v>
+        <v>45566</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9128,7 +9153,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9171,7 +9196,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9185,10 +9210,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9201,7 +9226,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9244,7 +9269,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9258,10 +9283,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44714</v>
+        <v>44784</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9274,7 +9299,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.1</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9317,7 +9342,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9331,10 +9356,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45085</v>
+        <v>44930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9347,7 +9372,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9390,7 +9415,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9404,10 +9429,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45922</v>
+        <v>44587</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9420,7 +9445,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9463,7 +9488,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9473,14 +9498,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44606</v>
+        <v>45471</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9493,7 +9518,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9536,7 +9561,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9550,10 +9575,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44623</v>
+        <v>44587</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9566,7 +9591,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9609,7 +9634,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9623,10 +9648,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45930</v>
+        <v>45047</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9639,7 +9664,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9682,7 +9707,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9696,10 +9721,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45337</v>
+        <v>46128</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9712,7 +9737,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9755,7 +9780,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9769,10 +9794,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44587</v>
+        <v>44965</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9785,7 +9810,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9828,7 +9853,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9842,10 +9867,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45743</v>
+        <v>45938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9858,7 +9883,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9901,7 +9926,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9911,14 +9936,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45471</v>
+        <v>45274</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9931,7 +9956,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9974,7 +9999,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9988,10 +10013,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45747</v>
+        <v>45211</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10004,7 +10029,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10047,7 +10072,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10061,10 +10086,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44587</v>
+        <v>45917</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10077,7 +10102,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10120,7 +10145,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10130,14 +10155,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46070</v>
+        <v>45943</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10149,13 +10174,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>7.2</v>
+        <v>0.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10198,7 +10218,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10212,10 +10232,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44980</v>
+        <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10228,7 +10248,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10271,7 +10291,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10285,10 +10305,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45244</v>
+        <v>45057</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10301,7 +10321,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10344,7 +10364,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10358,10 +10378,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45804</v>
+        <v>45399</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10374,7 +10394,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10417,7 +10437,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10431,10 +10451,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45938</v>
+        <v>45238</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10447,7 +10467,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10490,7 +10510,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10504,10 +10524,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45943</v>
+        <v>45589</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10520,7 +10540,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>42</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10563,7 +10583,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10573,14 +10593,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45456</v>
+        <v>45558</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10593,7 +10613,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10636,7 +10656,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10650,10 +10670,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44769</v>
+        <v>45799</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10666,7 +10686,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10709,7 +10729,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10723,10 +10743,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45419</v>
+        <v>45958</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10739,7 +10759,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10782,7 +10802,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10792,14 +10812,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45062</v>
+        <v>45287</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10812,7 +10832,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.4</v>
+        <v>11.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10855,7 +10875,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10869,10 +10889,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46094</v>
+        <v>45964</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10885,7 +10905,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10928,7 +10948,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 14886-2026</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10942,10 +10962,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46104</v>
+        <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10958,7 +10978,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>13.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11001,7 +11021,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11015,10 +11035,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46104</v>
+        <v>45966</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11031,7 +11051,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11074,7 +11094,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 56261-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11084,14 +11104,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46104</v>
+        <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11104,7 +11124,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11147,7 +11167,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11161,10 +11181,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46104</v>
+        <v>45057</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11177,7 +11197,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11220,7 +11240,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11234,10 +11254,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45958</v>
+        <v>45978</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11250,7 +11270,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11293,7 +11313,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11307,10 +11327,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45058</v>
+        <v>45639</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11323,7 +11343,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11366,7 +11386,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11380,10 +11400,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45646</v>
+        <v>44645</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11396,7 +11416,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11439,7 +11459,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11453,10 +11473,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46111</v>
+        <v>45672</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11468,13 +11488,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11517,7 +11532,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11531,10 +11546,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45964</v>
+        <v>45056</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11547,7 +11562,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11590,7 +11605,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11604,10 +11619,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46119</v>
+        <v>45946</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11620,7 +11635,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11663,7 +11678,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11677,10 +11692,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45965</v>
+        <v>46141</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11693,7 +11708,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>13.4</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11736,7 +11751,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11750,10 +11765,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46119</v>
+        <v>45085</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11766,7 +11781,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11809,7 +11824,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11823,10 +11838,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45966</v>
+        <v>45134</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11839,7 +11854,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11882,7 +11897,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11896,10 +11911,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45274</v>
+        <v>46141</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11912,7 +11927,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11955,7 +11970,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11969,10 +11984,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44784</v>
+        <v>45582</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11985,7 +12000,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12028,7 +12043,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12042,10 +12057,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46128</v>
+        <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12058,7 +12073,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12101,7 +12116,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12115,10 +12130,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44838</v>
+        <v>46142</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12131,7 +12146,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12174,7 +12189,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56261-2025</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12184,14 +12199,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45974</v>
+        <v>45592</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12204,7 +12219,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12247,7 +12262,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12261,10 +12276,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12277,7 +12292,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.3</v>
+        <v>11.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12320,7 +12335,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12334,10 +12349,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45799</v>
+        <v>45993</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12393,7 +12408,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12407,10 +12422,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45946</v>
+        <v>45994</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12423,7 +12438,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.8</v>
+        <v>8.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12466,7 +12481,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12480,10 +12495,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45917</v>
+        <v>46000</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12496,7 +12511,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12539,7 +12554,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12553,10 +12568,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45993</v>
+        <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12569,7 +12584,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12612,7 +12627,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12626,10 +12641,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45994</v>
+        <v>45062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12642,7 +12657,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.9</v>
+        <v>0.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12685,7 +12700,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12699,10 +12714,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45994</v>
+        <v>44978</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12715,7 +12730,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>11.5</v>
+        <v>2.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12758,7 +12773,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12772,10 +12787,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45399</v>
+        <v>46154</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12788,7 +12803,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12831,7 +12846,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12845,10 +12860,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45390</v>
+        <v>46154</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12861,7 +12876,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12904,7 +12919,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12918,10 +12933,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46000</v>
+        <v>45817</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12934,7 +12949,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12977,7 +12992,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12987,14 +13002,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45134</v>
+        <v>46035</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13006,8 +13021,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13050,7 +13070,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13064,10 +13084,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45337</v>
+        <v>45427</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13080,7 +13100,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>12.8</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13123,7 +13143,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13137,10 +13157,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45602</v>
+        <v>45134</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13153,7 +13173,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13196,7 +13216,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13210,10 +13230,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45636</v>
+        <v>44966</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13226,7 +13246,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13269,7 +13289,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13283,10 +13303,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45096</v>
+        <v>46024</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13299,7 +13319,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13342,7 +13362,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13356,10 +13376,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46141</v>
+        <v>45043</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13372,7 +13392,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13415,7 +13435,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13429,10 +13449,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46141</v>
+        <v>45751</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13445,7 +13465,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13488,7 +13508,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13502,10 +13522,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45134</v>
+        <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13518,7 +13538,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13561,7 +13581,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13575,10 +13595,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45571</v>
+        <v>44642</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13591,7 +13611,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13634,7 +13654,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13648,10 +13668,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45589</v>
+        <v>45246</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13664,7 +13684,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13707,7 +13727,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13721,10 +13741,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45030</v>
+        <v>45475</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13737,7 +13757,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13780,7 +13800,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13794,10 +13814,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46142</v>
+        <v>44714</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13810,7 +13830,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13853,7 +13873,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13867,10 +13887,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45672</v>
+        <v>46007</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13883,7 +13903,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13926,7 +13946,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13940,10 +13960,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46154</v>
+        <v>45917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13956,7 +13976,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13999,7 +14019,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14013,10 +14033,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46154</v>
+        <v>46044</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14029,7 +14049,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14072,7 +14092,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14082,14 +14102,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44630</v>
+        <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14102,7 +14122,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14145,7 +14165,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14159,10 +14179,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44550</v>
+        <v>45215</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14175,7 +14195,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14218,7 +14238,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14228,14 +14248,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46035</v>
+        <v>45034</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14247,13 +14267,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14296,7 +14311,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14310,10 +14325,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45134</v>
+        <v>45058</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14326,7 +14341,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14369,7 +14384,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14383,10 +14398,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45427</v>
+        <v>44784</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14399,7 +14414,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14442,7 +14457,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14452,14 +14467,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45817</v>
+        <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14472,7 +14487,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14515,7 +14530,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14529,10 +14544,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46163</v>
+        <v>46035</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14545,7 +14560,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14588,7 +14603,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14602,10 +14617,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46007</v>
+        <v>44746</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14618,7 +14633,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14661,7 +14676,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14675,10 +14690,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45917</v>
+        <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14691,7 +14706,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14734,7 +14749,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14744,14 +14759,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46171</v>
+        <v>46035</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14764,7 +14779,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14807,7 +14822,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14817,14 +14832,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46239</v>
+        <v>46070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14836,8 +14851,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14880,7 +14900,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14894,10 +14914,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46239</v>
+        <v>45337</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14910,7 +14930,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14953,7 +14973,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14963,14 +14983,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45419</v>
+        <v>44501</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14983,7 +15003,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15026,7 +15046,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15040,10 +15060,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46197</v>
+        <v>44501</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15056,7 +15076,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15099,7 +15119,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15109,14 +15129,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44659</v>
+        <v>44550</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15129,7 +15149,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15172,7 +15192,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15186,10 +15206,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45582</v>
+        <v>45307</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15202,7 +15222,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15245,7 +15265,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15255,14 +15275,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45287</v>
+        <v>45001</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15275,7 +15295,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>11.4</v>
+        <v>6.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15318,7 +15338,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15332,10 +15352,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46203</v>
+        <v>45545</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15348,7 +15368,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15391,7 +15411,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15405,10 +15425,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46246</v>
+        <v>45096</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15421,7 +15441,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15464,7 +15484,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15478,10 +15498,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46239</v>
+        <v>45337</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15494,7 +15514,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15537,7 +15557,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15551,10 +15571,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46247</v>
+        <v>45581</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15567,7 +15587,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>11.1</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15610,7 +15630,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15624,10 +15644,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45001</v>
+        <v>44980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15640,7 +15660,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15683,7 +15703,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15697,10 +15717,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46209</v>
+        <v>45134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15713,7 +15733,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>8.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15756,7 +15776,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15770,10 +15790,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44722</v>
+        <v>45134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15786,7 +15806,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15829,7 +15849,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15843,10 +15863,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44973</v>
+        <v>45348</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15859,7 +15879,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15902,7 +15922,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15916,10 +15936,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45382</v>
+        <v>46239</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15932,7 +15952,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>11.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15975,7 +15995,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15989,10 +16009,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45337</v>
+        <v>46197</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16005,7 +16025,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16048,7 +16068,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16062,10 +16082,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46262</v>
+        <v>46239</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16078,7 +16098,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16121,7 +16141,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16131,14 +16151,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46220</v>
+        <v>44659</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16151,7 +16171,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16194,7 +16214,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16208,10 +16228,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45001</v>
+        <v>44630</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16224,7 +16244,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16267,7 +16287,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16281,10 +16301,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16297,7 +16317,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16340,7 +16360,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16354,10 +16374,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45639</v>
+        <v>45134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16370,7 +16390,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16413,7 +16433,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16427,10 +16447,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45250</v>
+        <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16443,7 +16463,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>19</v>
+        <v>3.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16486,7 +16506,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16500,10 +16520,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46224</v>
+        <v>46203</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16516,7 +16536,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16559,7 +16579,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16573,10 +16593,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46224</v>
+        <v>45517</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16589,7 +16609,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16632,7 +16652,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16646,10 +16666,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45281</v>
+        <v>46246</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16662,7 +16682,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16705,7 +16725,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16719,10 +16739,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44642</v>
+        <v>45594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16735,7 +16755,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16778,7 +16798,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16792,10 +16812,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46279</v>
+        <v>44909</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16808,7 +16828,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16851,7 +16871,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16861,14 +16881,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45408</v>
+        <v>46247</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16881,7 +16901,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>6.6</v>
+        <v>11.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16924,7 +16944,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16938,10 +16958,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45475</v>
+        <v>45337</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16954,7 +16974,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16997,7 +17017,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17011,10 +17031,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45034</v>
+        <v>46209</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17027,7 +17047,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17070,7 +17090,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17084,10 +17104,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44930</v>
+        <v>45281</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17100,7 +17120,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17143,7 +17163,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17157,10 +17177,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44746</v>
+        <v>45602</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17173,7 +17193,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17216,7 +17236,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17230,10 +17250,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45057</v>
+        <v>45592</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17246,7 +17266,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17289,7 +17309,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17303,10 +17323,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44747</v>
+        <v>45244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17319,7 +17339,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17362,7 +17382,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17376,10 +17396,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44978</v>
+        <v>46262</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17392,7 +17412,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17435,7 +17455,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17449,10 +17469,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45348</v>
+        <v>44838</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17465,7 +17485,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17508,7 +17528,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17518,14 +17538,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45034</v>
+        <v>45419</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17538,7 +17558,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17581,7 +17601,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17595,10 +17615,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45582</v>
+        <v>46220</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17611,7 +17631,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17654,7 +17674,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17668,10 +17688,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45043</v>
+        <v>44683</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17684,7 +17704,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17727,7 +17747,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17737,14 +17757,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45397</v>
+        <v>46220</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17756,13 +17776,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17801,31 +17816,11 @@
         <v>0</v>
       </c>
       <c r="V225" s="2" t="inlineStr"/>
-      <c r="Z225">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA225">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB225">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC225">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD225">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17839,10 +17834,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45047</v>
+        <v>46224</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17855,7 +17850,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17898,7 +17893,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17912,10 +17907,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45256</v>
+        <v>46224</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17928,7 +17923,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17971,7 +17966,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17985,10 +17980,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45594</v>
+        <v>44929</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18044,7 +18039,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18058,10 +18053,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45134</v>
+        <v>44930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18074,7 +18069,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18117,7 +18112,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18131,10 +18126,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45211</v>
+        <v>45571</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18147,7 +18142,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18190,7 +18185,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18204,10 +18199,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45246</v>
+        <v>45077</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18220,7 +18215,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18263,7 +18258,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18277,10 +18272,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44645</v>
+        <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18288,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18336,7 +18331,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18350,10 +18345,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45337</v>
+        <v>46279</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18366,7 +18361,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18409,7 +18404,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18423,10 +18418,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45244</v>
+        <v>45786</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18439,7 +18434,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18482,7 +18477,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18496,10 +18491,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45077</v>
+        <v>45721</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18512,7 +18507,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18555,7 +18550,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18569,10 +18564,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44965</v>
+        <v>45565</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18585,7 +18580,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18628,7 +18623,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18638,14 +18633,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45307</v>
+        <v>45736</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18658,7 +18653,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18701,7 +18696,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18715,10 +18710,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45056</v>
+        <v>45736</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18731,7 +18726,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18774,7 +18769,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18788,10 +18783,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45558</v>
+        <v>45735</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18804,7 +18799,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.2</v>
+        <v>5.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18847,7 +18842,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18857,14 +18852,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44930</v>
+        <v>45728</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18877,7 +18872,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18920,7 +18915,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18934,10 +18929,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44501</v>
+        <v>45798</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18950,7 +18945,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18993,7 +18988,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19007,10 +19002,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44501</v>
+        <v>45798</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19023,7 +19018,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19066,7 +19061,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19080,10 +19075,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45294</v>
+        <v>45798</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19096,7 +19091,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19139,7 +19134,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19149,14 +19144,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44788</v>
+        <v>45799</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19169,7 +19164,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19212,7 +19207,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19226,10 +19221,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19242,7 +19237,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19285,7 +19280,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19299,10 +19294,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44966</v>
+        <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19358,7 +19353,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19368,14 +19363,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45014</v>
+        <v>45589</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19388,7 +19383,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19431,7 +19426,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19445,10 +19440,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45244</v>
+        <v>45603</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19461,7 +19456,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19504,7 +19499,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19514,14 +19509,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45571</v>
+        <v>45328</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19533,8 +19528,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19591,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45134</v>
+        <v>45811</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45592</v>
+        <v>45728</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45786</v>
+        <v>45826</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19810,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45721</v>
+        <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45565</v>
+        <v>45743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45735</v>
+        <v>45747</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20032,7 +20032,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45040</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45742</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55617-2023</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45238</v>
+        <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1633,42 +1633,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25575-2025</t>
+          <t>A 48163-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1678,14 +1678,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45589</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1697,19 +1697,14 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1736,49 +1731,53 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10515-2025</t>
+          <t>A 18733-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1791,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45721</v>
+        <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,17 +1807,17 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1832,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1844,39 +1843,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
         <v/>
       </c>
     </row>
@@ -1900,7 +1899,7 @@
         <v>45931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1988,7 +1987,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55331-2025</t>
+          <t>A 27794-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45971</v>
+        <v>46191</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,20 +2017,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2042,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2058,35 +2057,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Åkerrättika</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
         <v/>
       </c>
     </row>
@@ -2110,7 +2109,7 @@
         <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2198,7 +2197,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18733-2026</t>
+          <t>A 55331-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2212,10 +2211,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46128</v>
+        <v>45971</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2228,16 +2227,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2252,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2268,42 +2267,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5009-2025</t>
+          <t>A 55617-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2317,10 +2316,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45691</v>
+        <v>45238</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2333,7 +2332,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2373,365 +2372,365 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 39899-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45166</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 56739-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 5009-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>Ljungpipare</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 17920-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 27794-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Åkerrättika</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 39899-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45166</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48163-2024</t>
+          <t>A 25575-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2741,14 +2740,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45589</v>
+        <v>45803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2760,14 +2759,19 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>14.4</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2794,53 +2798,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56739-2023</t>
+          <t>A 10515-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,14 +2850,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45244</v>
+        <v>45721</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2910,35 +2910,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34717-2022</t>
+          <t>A 54899-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44795</v>
+        <v>44886</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54899-2022</t>
+          <t>A 34717-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44886</v>
+        <v>44795</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60987-2021</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 10977-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44497</v>
+        <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10977-2022</t>
+          <t>A 60987-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44628</v>
+        <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45592</v>
+        <v>44788</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45517</v>
+        <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5380,14 +5380,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45057</v>
+        <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45545</v>
+        <v>45397</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5472,8 +5472,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5512,11 +5517,31 @@
         <v>0</v>
       </c>
       <c r="V57" s="2" t="inlineStr"/>
+      <c r="Z57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45751</v>
+        <v>45382</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5571,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44683</v>
+        <v>45250</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5644,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5687,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5701,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>45313</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5717,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5760,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5745,14 +5770,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44929</v>
+        <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5790,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5833,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5822,10 +5847,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45399</v>
+        <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5863,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5891,14 +5916,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45399</v>
+        <v>45294</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5936,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5954,7 +5979,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5968,10 +5993,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45345</v>
+        <v>45337</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +6009,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6027,7 +6052,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6041,10 +6066,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45238</v>
+        <v>45636</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6110,14 +6135,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45099</v>
+        <v>44881</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6173,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6187,10 +6212,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45313</v>
+        <v>45646</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6228,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6271,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6256,14 +6281,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44852</v>
+        <v>45014</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6301,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6344,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6333,10 +6358,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44881</v>
+        <v>44623</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6392,7 +6417,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6406,10 +6431,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45798</v>
+        <v>45571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6447,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6490,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6479,10 +6504,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45798</v>
+        <v>45030</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6495,7 +6520,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6563,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6552,10 +6577,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45798</v>
+        <v>44769</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6593,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6636,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6650,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45799</v>
+        <v>45826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6666,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6709,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6723,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45566</v>
+        <v>46070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6713,8 +6738,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6757,7 +6787,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6767,14 +6797,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46024</v>
+        <v>45566</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6817,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6860,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6874,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45884</v>
+        <v>45211</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6903,7 +6933,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6947,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44909</v>
+        <v>45582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6963,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7006,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7020,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45589</v>
+        <v>45057</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7036,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7079,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7093,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45582</v>
+        <v>45399</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7109,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7152,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7136,10 +7166,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45582</v>
+        <v>45238</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7182,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7225,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7209,10 +7239,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45446</v>
+        <v>45589</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7225,7 +7255,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.4</v>
+        <v>42</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7268,7 +7298,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7282,10 +7312,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44784</v>
+        <v>45558</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7298,7 +7328,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7341,7 +7371,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7355,10 +7385,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45811</v>
+        <v>44606</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7371,7 +7401,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7414,7 +7444,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7424,14 +7454,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45328</v>
+        <v>46094</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7443,13 +7473,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7492,7 +7517,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7502,14 +7527,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45603</v>
+        <v>45287</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7522,7 +7547,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>11.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7565,7 +7590,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7579,10 +7604,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44824</v>
+        <v>46104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7595,7 +7620,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7638,7 +7663,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7652,10 +7677,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45728</v>
+        <v>46104</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7668,7 +7693,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7711,7 +7736,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 14886-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7725,10 +7750,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45897</v>
+        <v>46104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7741,7 +7766,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7784,7 +7809,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7798,10 +7823,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45896</v>
+        <v>46104</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7814,7 +7839,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7857,7 +7882,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7871,10 +7896,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45896</v>
+        <v>45743</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7887,7 +7912,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7930,7 +7955,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7944,10 +7969,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45896</v>
+        <v>45747</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7960,7 +7985,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8003,7 +8028,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8017,10 +8042,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45896</v>
+        <v>46111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8032,8 +8057,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8076,7 +8106,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8090,10 +8120,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45896</v>
+        <v>45057</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8106,7 +8136,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8149,7 +8179,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8163,10 +8193,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44714</v>
+        <v>45639</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8179,7 +8209,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8222,7 +8252,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8236,10 +8266,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45085</v>
+        <v>46119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8252,7 +8282,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8295,7 +8325,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8309,10 +8339,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44623</v>
+        <v>45896</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8325,7 +8355,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8368,7 +8398,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8382,10 +8412,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45826</v>
+        <v>45804</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8398,7 +8428,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8441,7 +8471,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8455,10 +8485,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45902</v>
+        <v>45896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8471,7 +8501,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8514,7 +8544,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8528,10 +8558,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45905</v>
+        <v>45896</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8544,7 +8574,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8587,7 +8617,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8601,10 +8631,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45337</v>
+        <v>45672</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8617,7 +8647,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8660,7 +8690,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8674,10 +8704,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44980</v>
+        <v>46119</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8690,7 +8720,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8733,7 +8763,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8747,10 +8777,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45244</v>
+        <v>45896</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8763,7 +8793,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8806,7 +8836,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8820,10 +8850,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45917</v>
+        <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8836,7 +8866,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8879,7 +8909,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8893,10 +8923,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45917</v>
+        <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8909,7 +8939,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8952,7 +8982,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8966,10 +8996,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45917</v>
+        <v>45884</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8982,7 +9012,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9025,7 +9055,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9039,10 +9069,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45918</v>
+        <v>46128</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9055,7 +9085,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9098,7 +9128,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9112,10 +9142,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44606</v>
+        <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9128,7 +9158,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9171,7 +9201,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9185,10 +9215,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45922</v>
+        <v>45582</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9201,7 +9231,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9244,7 +9274,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9254,14 +9284,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45456</v>
+        <v>44747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9274,7 +9304,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9317,7 +9347,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9331,10 +9361,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45419</v>
+        <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9347,7 +9377,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9390,7 +9420,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9404,10 +9434,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45930</v>
+        <v>45905</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9420,7 +9450,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9463,7 +9493,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9477,10 +9507,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45743</v>
+        <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9493,7 +9523,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9536,7 +9566,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9550,10 +9580,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44587</v>
+        <v>45918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9566,7 +9596,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9609,7 +9639,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9619,14 +9649,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45471</v>
+        <v>44978</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9639,7 +9669,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9682,7 +9712,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9696,10 +9726,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45747</v>
+        <v>45917</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9712,7 +9742,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9755,7 +9785,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9769,10 +9799,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44587</v>
+        <v>45917</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9785,7 +9815,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9828,7 +9858,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9842,10 +9872,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45804</v>
+        <v>45922</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9858,7 +9888,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9901,7 +9931,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9915,10 +9945,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45215</v>
+        <v>45799</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9931,7 +9961,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9974,7 +10004,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9988,10 +10018,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45062</v>
+        <v>45043</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10004,7 +10034,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10047,7 +10077,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10061,10 +10091,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45938</v>
+        <v>45751</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10077,7 +10107,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10120,7 +10150,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10134,10 +10164,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45943</v>
+        <v>44642</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10150,7 +10180,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10193,7 +10223,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10207,10 +10237,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46044</v>
+        <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10223,7 +10253,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10266,7 +10296,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10280,10 +10310,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44769</v>
+        <v>45475</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10296,7 +10326,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10339,7 +10369,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10353,10 +10383,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46035</v>
+        <v>44714</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10369,7 +10399,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10412,7 +10442,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10426,10 +10456,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46035</v>
+        <v>45946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10442,7 +10472,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10485,7 +10515,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10499,10 +10529,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46035</v>
+        <v>46141</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10515,7 +10545,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10558,7 +10588,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10572,10 +10602,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45058</v>
+        <v>46141</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10588,7 +10618,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10631,7 +10661,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10645,10 +10675,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45646</v>
+        <v>45930</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10661,7 +10691,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10704,7 +10734,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10718,10 +10748,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45958</v>
+        <v>46142</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10734,7 +10764,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10777,7 +10807,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10791,10 +10821,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45964</v>
+        <v>45058</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10807,7 +10837,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10850,7 +10880,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10860,14 +10890,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45965</v>
+        <v>45099</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10880,7 +10910,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>13.4</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10923,7 +10953,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10937,10 +10967,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45274</v>
+        <v>44587</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10953,7 +10983,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10996,7 +11026,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11006,14 +11036,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44784</v>
+        <v>45471</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11026,7 +11056,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11069,7 +11099,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11083,10 +11113,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45966</v>
+        <v>44587</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11099,7 +11129,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11142,7 +11172,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11156,10 +11186,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44838</v>
+        <v>46154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11215,7 +11245,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11225,14 +11255,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46070</v>
+        <v>46154</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11244,13 +11274,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11293,7 +11318,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56261-2025</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11303,14 +11328,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45974</v>
+        <v>45938</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11323,7 +11348,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11366,7 +11391,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11380,10 +11405,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45978</v>
+        <v>45817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11396,7 +11421,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11439,7 +11464,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11449,14 +11474,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45399</v>
+        <v>46035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11468,8 +11493,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11512,7 +11542,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11526,10 +11556,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45390</v>
+        <v>45427</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11542,7 +11572,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11585,7 +11615,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11599,10 +11629,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45993</v>
+        <v>45134</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11615,7 +11645,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11658,7 +11688,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11672,10 +11702,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45994</v>
+        <v>45337</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11688,7 +11718,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11731,7 +11761,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11745,10 +11775,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45994</v>
+        <v>44501</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11761,7 +11791,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11804,7 +11834,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11818,10 +11848,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45134</v>
+        <v>44501</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11834,7 +11864,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11877,7 +11907,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11891,10 +11921,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46000</v>
+        <v>44550</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11907,7 +11937,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11950,7 +11980,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11964,10 +11994,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45337</v>
+        <v>45307</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11980,7 +12010,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>12.8</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12023,7 +12053,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12037,10 +12067,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45602</v>
+        <v>46163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12053,7 +12083,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12096,7 +12126,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12110,10 +12140,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45636</v>
+        <v>45545</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12126,7 +12156,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12186,7 +12216,7 @@
         <v>45096</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12242,7 +12272,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12256,10 +12286,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45134</v>
+        <v>45581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12272,7 +12302,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12315,7 +12345,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12329,10 +12359,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46094</v>
+        <v>46007</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12345,7 +12375,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12388,7 +12418,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12402,10 +12432,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45571</v>
+        <v>45943</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12418,7 +12448,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12461,7 +12491,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12475,10 +12505,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45589</v>
+        <v>44980</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12491,7 +12521,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>42</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12534,7 +12564,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12548,10 +12578,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45030</v>
+        <v>45917</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12564,7 +12594,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12607,7 +12637,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14886-2026</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12621,10 +12651,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46104</v>
+        <v>45134</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12637,7 +12667,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12680,7 +12710,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12694,10 +12724,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46104</v>
+        <v>45348</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12710,7 +12740,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12753,7 +12783,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12763,14 +12793,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46104</v>
+        <v>46171</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12783,7 +12813,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12826,7 +12856,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12840,10 +12870,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46104</v>
+        <v>45244</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12856,7 +12886,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12899,7 +12929,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12913,10 +12943,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45672</v>
+        <v>45134</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12929,7 +12959,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12972,7 +13002,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12986,10 +13016,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46111</v>
+        <v>45958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13001,13 +13031,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13050,7 +13075,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13064,10 +13089,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44630</v>
+        <v>45337</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13080,7 +13105,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>10.6</v>
+        <v>12.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13123,7 +13148,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13137,10 +13162,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44550</v>
+        <v>45964</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13153,7 +13178,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13196,7 +13221,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13210,10 +13235,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46119</v>
+        <v>45965</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13226,7 +13251,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>13.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13269,7 +13294,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13283,10 +13308,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46119</v>
+        <v>45281</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13299,7 +13324,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.3</v>
+        <v>7.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13342,7 +13367,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13356,10 +13381,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46128</v>
+        <v>46197</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13372,7 +13397,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13415,7 +13440,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13425,14 +13450,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45419</v>
+        <v>45966</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13445,7 +13470,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13488,7 +13513,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13498,14 +13523,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44659</v>
+        <v>45602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13518,7 +13543,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13561,7 +13586,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 56261-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13571,14 +13596,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45582</v>
+        <v>45974</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13591,7 +13616,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13634,7 +13659,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13644,14 +13669,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45287</v>
+        <v>45978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13664,7 +13689,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11.4</v>
+        <v>3.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13707,7 +13732,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13721,10 +13746,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45799</v>
+        <v>46203</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13737,7 +13762,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13780,7 +13805,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13794,10 +13819,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45001</v>
+        <v>46246</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13810,7 +13835,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13853,7 +13878,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13867,10 +13892,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44722</v>
+        <v>46247</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13883,7 +13908,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>11.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13926,7 +13951,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13940,10 +13965,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44973</v>
+        <v>44838</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13956,7 +13981,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13999,7 +14024,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14013,10 +14038,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45946</v>
+        <v>44683</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14029,7 +14054,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14072,7 +14097,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14086,10 +14111,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45382</v>
+        <v>45244</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14145,7 +14170,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14159,10 +14184,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45337</v>
+        <v>46209</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14175,7 +14200,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14218,7 +14243,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14232,10 +14257,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45917</v>
+        <v>45187</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14248,7 +14273,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14291,7 +14316,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14305,10 +14330,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45001</v>
+        <v>45390</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14321,7 +14346,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14364,7 +14389,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14378,10 +14403,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45639</v>
+        <v>44722</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14394,7 +14419,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14437,7 +14462,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14451,10 +14476,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45250</v>
+        <v>44824</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14467,7 +14492,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>19</v>
+        <v>1.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14510,7 +14535,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14524,10 +14549,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45281</v>
+        <v>45994</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14540,7 +14565,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14583,7 +14608,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14597,10 +14622,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46141</v>
+        <v>45993</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14613,7 +14638,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14656,7 +14681,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14670,10 +14695,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46141</v>
+        <v>45256</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14686,7 +14711,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14729,7 +14754,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14743,10 +14768,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44642</v>
+        <v>44973</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14759,7 +14784,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14802,7 +14827,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14816,10 +14841,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46142</v>
+        <v>45994</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14832,7 +14857,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.4</v>
+        <v>8.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14875,7 +14900,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14885,14 +14910,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45408</v>
+        <v>46000</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14905,7 +14930,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14948,7 +14973,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14962,10 +14987,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45475</v>
+        <v>46262</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14978,7 +15003,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15021,7 +15046,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15035,10 +15060,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45034</v>
+        <v>46220</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15051,7 +15076,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15094,7 +15119,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15108,10 +15133,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46154</v>
+        <v>44852</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15124,7 +15149,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15167,7 +15192,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15181,10 +15206,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44930</v>
+        <v>46220</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15197,7 +15222,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15240,7 +15265,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15254,10 +15279,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46154</v>
+        <v>46224</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15270,7 +15295,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15313,7 +15338,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15323,14 +15348,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46035</v>
+        <v>46224</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15342,13 +15367,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15391,7 +15411,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15405,10 +15425,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45134</v>
+        <v>45345</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15421,7 +15441,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15464,7 +15484,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15478,10 +15498,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45427</v>
+        <v>45399</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15494,7 +15514,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15537,7 +15557,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15547,14 +15567,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45817</v>
+        <v>45399</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15567,7 +15587,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15610,7 +15630,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15624,10 +15644,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44746</v>
+        <v>44784</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15640,7 +15660,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15683,7 +15703,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15697,10 +15717,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45057</v>
+        <v>44930</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15713,7 +15733,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15756,7 +15776,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15770,10 +15790,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44747</v>
+        <v>45047</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15786,7 +15806,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15829,7 +15849,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15843,10 +15863,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44978</v>
+        <v>44965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15859,7 +15879,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15902,7 +15922,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15916,10 +15936,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46163</v>
+        <v>45274</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15932,7 +15952,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15975,7 +15995,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15989,10 +16009,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45348</v>
+        <v>46024</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16005,7 +16025,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16048,7 +16068,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16062,10 +16082,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45034</v>
+        <v>44645</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16078,7 +16098,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16121,7 +16141,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16135,10 +16155,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45582</v>
+        <v>45056</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16151,7 +16171,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16194,7 +16214,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16208,10 +16228,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46007</v>
+        <v>46279</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16224,7 +16244,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16267,7 +16287,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16281,10 +16301,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45043</v>
+        <v>45085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16297,7 +16317,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16340,7 +16360,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16354,10 +16374,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45917</v>
+        <v>45134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16370,7 +16390,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16413,7 +16433,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16423,14 +16443,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45397</v>
+        <v>45592</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16442,13 +16462,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16487,31 +16502,11 @@
         <v>0</v>
       </c>
       <c r="V207" s="2" t="inlineStr"/>
-      <c r="Z207">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA207">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB207">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC207">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD207">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16521,14 +16516,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46171</v>
+        <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16541,7 +16536,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16584,7 +16579,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16598,10 +16593,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45047</v>
+        <v>46239</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16614,7 +16609,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16657,7 +16652,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16671,10 +16666,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45256</v>
+        <v>45001</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16687,7 +16682,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16730,7 +16725,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16744,10 +16739,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45594</v>
+        <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16760,7 +16755,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16803,7 +16798,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16817,10 +16812,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45134</v>
+        <v>46239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16833,7 +16828,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16876,7 +16871,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16890,10 +16885,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45211</v>
+        <v>44966</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16906,7 +16901,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16949,7 +16944,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16963,10 +16958,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45246</v>
+        <v>45034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16979,7 +16974,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17022,7 +17017,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17036,10 +17031,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44645</v>
+        <v>46044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17052,7 +17047,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17095,7 +17090,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17109,10 +17104,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46197</v>
+        <v>44784</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17125,7 +17120,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17168,7 +17163,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17182,10 +17177,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46203</v>
+        <v>45215</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17198,7 +17193,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17241,7 +17236,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17255,10 +17250,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46246</v>
+        <v>44746</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17271,7 +17266,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17314,7 +17309,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17328,10 +17323,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46247</v>
+        <v>45001</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17344,7 +17339,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>11.1</v>
+        <v>6.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17387,7 +17382,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17404,7 +17399,7 @@
         <v>45337</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17417,7 +17412,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17460,7 +17455,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17474,10 +17469,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45244</v>
+        <v>45134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17490,7 +17485,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17533,7 +17528,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17547,10 +17542,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46209</v>
+        <v>46035</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17563,7 +17558,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17606,7 +17601,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17620,10 +17615,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45077</v>
+        <v>46035</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17636,7 +17631,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17679,7 +17674,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17693,10 +17688,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44965</v>
+        <v>46035</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17709,7 +17704,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17752,7 +17747,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17762,14 +17757,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45307</v>
+        <v>44659</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17782,7 +17777,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17825,7 +17820,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17839,10 +17834,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45056</v>
+        <v>44630</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17855,7 +17850,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>10.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17898,7 +17893,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17912,10 +17907,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46262</v>
+        <v>45517</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17928,7 +17923,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17971,7 +17966,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17985,10 +17980,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46220</v>
+        <v>45594</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18001,7 +17996,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18044,7 +18039,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18058,10 +18053,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45558</v>
+        <v>44909</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18074,7 +18069,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.2</v>
+        <v>5.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18117,7 +18112,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18131,10 +18126,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46220</v>
+        <v>45592</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18147,7 +18142,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18190,7 +18185,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18204,10 +18199,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46224</v>
+        <v>45244</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18220,7 +18215,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18263,7 +18258,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18273,14 +18268,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44930</v>
+        <v>45419</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18288,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18336,7 +18331,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18350,10 +18345,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46224</v>
+        <v>44929</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18366,7 +18361,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18409,7 +18404,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18423,10 +18418,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44501</v>
+        <v>44930</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18439,7 +18434,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18482,7 +18477,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18496,10 +18491,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44501</v>
+        <v>45571</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18512,7 +18507,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18555,7 +18550,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18569,10 +18564,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45294</v>
+        <v>45077</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18585,7 +18580,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18628,7 +18623,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18638,14 +18633,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44788</v>
+        <v>45034</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18658,7 +18653,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18701,7 +18696,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18715,10 +18710,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45581</v>
+        <v>45786</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18731,7 +18726,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18774,7 +18769,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18788,10 +18783,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44966</v>
+        <v>45721</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18804,7 +18799,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18847,7 +18842,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18857,14 +18852,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45014</v>
+        <v>45565</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18877,7 +18872,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18920,7 +18915,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18930,14 +18925,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45244</v>
+        <v>45736</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18950,7 +18945,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18993,7 +18988,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19007,10 +19002,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45571</v>
+        <v>45736</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19023,7 +19018,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19066,7 +19061,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19080,10 +19075,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46279</v>
+        <v>45735</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19096,7 +19091,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19139,7 +19134,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19149,14 +19144,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45134</v>
+        <v>45728</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19169,7 +19164,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19212,7 +19207,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19226,10 +19221,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45592</v>
+        <v>45798</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19242,7 +19237,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19285,7 +19280,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19299,10 +19294,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46239</v>
+        <v>45798</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19315,7 +19310,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19358,7 +19353,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19372,10 +19367,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46239</v>
+        <v>45798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19388,7 +19383,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19431,7 +19426,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19445,10 +19440,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46239</v>
+        <v>45799</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19461,7 +19456,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19504,7 +19499,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19518,10 +19513,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45786</v>
+        <v>45582</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19534,7 +19529,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19572,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19586,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45721</v>
+        <v>45582</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19602,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19645,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19659,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45565</v>
+        <v>45589</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19675,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19718,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19732,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45735</v>
+        <v>45603</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19748,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19791,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19805,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45736</v>
+        <v>45328</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19825,8 +19820,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45736</v>
+        <v>45811</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19952,14 +19952,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
         <v>45728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20032,7 +20032,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45742</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45838</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45238</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45373</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45931</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45971</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45040</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>46191</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45166</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>46128</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45589</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>45244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45721</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45592</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45057</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45751</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44683</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45187</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45399</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45399</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45238</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45345</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45099</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44852</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44881</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44909</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45566</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44824</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45446</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44784</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44623</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45337</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45244</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45419</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45062</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45646</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>45058</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44784</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>45274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>45884</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45946</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45399</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45390</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45896</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45896</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>45896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45896</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45134</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45902</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45337</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>45636</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45096</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>46141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>46141</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>45134</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>45922</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45571</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45589</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45030</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>45930</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>46142</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44587</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45471</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44587</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45672</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>45938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44630</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44550</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45943</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>45419</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45582</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45287</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45964</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45001</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44722</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45966</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>46154</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44973</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>45382</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>45337</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>45001</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>45974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>46154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45978</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45639</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45250</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45281</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>46035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>45993</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>45134</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45427</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45817</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46163</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>45994</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44642</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>46000</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45408</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45475</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45034</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>46007</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44930</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46171</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>46024</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44746</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45057</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44978</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45348</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45034</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45215</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45582</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>46044</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>45043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45397</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>46035</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>46035</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>46035</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>46070</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45047</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45256</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45594</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45134</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45211</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>46094</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>46104</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>46104</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>46104</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>46104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45246</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44645</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>46197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>46111</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>46119</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>46119</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45337</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46128</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45244</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>46203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45077</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44965</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>46246</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45799</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45307</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>46247</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45056</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45558</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>46209</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>44930</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44501</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44501</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45294</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44788</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45581</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44966</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45014</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>46262</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46220</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45244</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>46220</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45571</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45134</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>46224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>46224</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45592</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>46279</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45786</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45721</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45565</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45735</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45736</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45736</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>46239</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>46239</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45728</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45798</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>46239</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45798</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45798</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45799</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45589</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45582</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45582</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45328</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45603</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45728</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45826</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44606</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45743</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45747</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45804</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>44769</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE258"/>
+  <dimension ref="A1:AE259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45742</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45838</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45238</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11709-2024</t>
+          <t>A 47783-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45373</v>
+        <v>45931</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1738,147 +1738,147 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 11709-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Gullklöver</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 47783-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5009-2025</t>
+          <t>A 55331-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45691</v>
+        <v>45971</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1948,151 +1948,151 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5009-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Ljungpipare</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 55331-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45971</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mandelriska</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17920-2023</t>
+          <t>A 27794-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45040</v>
+        <v>46191</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2122,20 +2122,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2162,147 +2162,147 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Åkerrättika</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 17920-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45040</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>Vanlig padda</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27794-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Åkerrättika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39899-2023</t>
+          <t>A 18733-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45166</v>
+        <v>46128</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2332,17 +2332,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.6</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2372,147 +2372,147 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 39899-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45166</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 18733-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>45589</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>45244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45721</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 60987-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60987-2021</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4647,7 +4647,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45592</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45057</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45751</v>
+        <v>44683</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44683</v>
+        <v>45751</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
         <v>44929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45187</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45399</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45399</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45238</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45345</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45099</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44852</v>
+        <v>45313</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6246,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45313</v>
+        <v>44852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6336,7 +6336,7 @@
         <v>44881</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6402,14 +6402,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44909</v>
+        <v>45566</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6475,14 +6475,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45566</v>
+        <v>45446</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6538,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6552,10 +6552,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44824</v>
+        <v>44784</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45446</v>
+        <v>44824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6684,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44784</v>
+        <v>44909</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6774,7 +6774,7 @@
         <v>44714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44623</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45337</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45244</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45419</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45062</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45646</v>
+        <v>45884</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
         <v>45058</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44784</v>
+        <v>45646</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45274</v>
+        <v>45799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44838</v>
+        <v>44769</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7779,7 +7779,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45884</v>
+        <v>45946</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7852,7 +7852,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45946</v>
+        <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7925,7 +7925,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45917</v>
+        <v>44784</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7998,7 +7998,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45399</v>
+        <v>44838</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45390</v>
+        <v>45897</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8144,7 +8144,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45897</v>
+        <v>45917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8234,7 +8234,7 @@
         <v>45896</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45896</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>45896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45896</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45134</v>
+        <v>45902</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8655,7 +8655,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45902</v>
+        <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8728,7 +8728,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8742,10 +8742,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8801,7 +8801,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45337</v>
+        <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>12.8</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45602</v>
+        <v>45917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8947,7 +8947,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45636</v>
+        <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9020,7 +9020,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45096</v>
+        <v>45922</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9093,7 +9093,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46141</v>
+        <v>45399</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9166,7 +9166,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46141</v>
+        <v>45390</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9239,7 +9239,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45134</v>
+        <v>45930</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45917</v>
+        <v>44587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9385,7 +9385,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9395,14 +9395,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45917</v>
+        <v>45471</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9458,7 +9458,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45917</v>
+        <v>44587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9531,7 +9531,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45918</v>
+        <v>46141</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45922</v>
+        <v>46141</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45571</v>
+        <v>45134</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9750,7 +9750,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45589</v>
+        <v>46142</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>42</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9837,10 +9837,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45030</v>
+        <v>45337</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.2</v>
+        <v>12.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9896,7 +9896,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45930</v>
+        <v>45602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9969,7 +9969,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9983,10 +9983,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46142</v>
+        <v>45636</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10042,7 +10042,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44587</v>
+        <v>45096</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10115,7 +10115,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10125,14 +10125,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45471</v>
+        <v>46154</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10188,7 +10188,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10202,10 +10202,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44587</v>
+        <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10261,7 +10261,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45672</v>
+        <v>45943</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45938</v>
+        <v>45134</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10421,10 +10421,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44630</v>
+        <v>46154</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10480,7 +10480,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44550</v>
+        <v>45571</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10553,7 +10553,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10563,14 +10563,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45943</v>
+        <v>46035</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10582,8 +10582,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10626,7 +10631,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10636,14 +10641,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45419</v>
+        <v>45589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10656,7 +10661,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>42</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10699,7 +10704,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10709,14 +10714,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44659</v>
+        <v>45030</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10772,7 +10777,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10786,10 +10791,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45582</v>
+        <v>45958</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10802,7 +10807,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10845,7 +10850,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10855,14 +10860,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45287</v>
+        <v>45134</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10875,7 +10880,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>11.4</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10918,7 +10923,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10932,10 +10937,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45958</v>
+        <v>45427</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10948,7 +10953,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10991,7 +10996,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11005,10 +11010,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45964</v>
+        <v>45817</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11021,7 +11026,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11064,7 +11069,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11078,10 +11083,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45001</v>
+        <v>45964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11094,7 +11099,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.9</v>
+        <v>5.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11154,7 +11159,7 @@
         <v>45965</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11210,7 +11215,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11224,10 +11229,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44722</v>
+        <v>45966</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11240,7 +11245,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11283,7 +11288,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11297,10 +11302,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45966</v>
+        <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11313,7 +11318,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11356,7 +11361,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11370,10 +11375,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46154</v>
+        <v>45672</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11386,7 +11391,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11429,7 +11434,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 56261-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11439,14 +11444,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44973</v>
+        <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11459,7 +11464,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11502,7 +11507,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11516,10 +11521,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45382</v>
+        <v>45978</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11532,7 +11537,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11575,7 +11580,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11589,10 +11594,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45337</v>
+        <v>44630</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11605,7 +11610,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11648,7 +11653,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11662,10 +11667,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45001</v>
+        <v>44550</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11678,7 +11683,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11721,7 +11726,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 56261-2025</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11731,14 +11736,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45974</v>
+        <v>46007</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11751,7 +11756,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11794,7 +11799,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11808,10 +11813,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46154</v>
+        <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11824,7 +11829,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11867,7 +11872,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11877,14 +11882,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45978</v>
+        <v>46171</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11897,7 +11902,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11940,7 +11945,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11950,14 +11955,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45639</v>
+        <v>45419</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11970,7 +11975,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12013,7 +12018,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12023,14 +12028,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45250</v>
+        <v>44659</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12043,7 +12048,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>19</v>
+        <v>0.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12086,7 +12091,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12100,10 +12105,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45281</v>
+        <v>45993</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12116,7 +12121,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12159,7 +12164,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12169,14 +12174,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46035</v>
+        <v>45994</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12188,13 +12193,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12237,7 +12237,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12251,10 +12251,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45993</v>
+        <v>45582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12310,7 +12310,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12320,14 +12320,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45134</v>
+        <v>45287</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>11.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12383,7 +12383,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12397,10 +12397,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45427</v>
+        <v>45994</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45817</v>
+        <v>46000</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12529,7 +12529,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12543,10 +12543,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46163</v>
+        <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12602,7 +12602,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12616,10 +12616,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45994</v>
+        <v>44722</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.9</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12675,7 +12675,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45994</v>
+        <v>44973</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12748,7 +12748,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44642</v>
+        <v>45382</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12821,7 +12821,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12835,10 +12835,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46000</v>
+        <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12894,7 +12894,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45408</v>
+        <v>45001</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12981,10 +12981,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45475</v>
+        <v>45639</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13040,7 +13040,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45034</v>
+        <v>46024</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13113,7 +13113,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46007</v>
+        <v>45250</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>19</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13186,7 +13186,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13200,10 +13200,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45917</v>
+        <v>45281</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13259,7 +13259,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13273,10 +13273,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44930</v>
+        <v>45215</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13342,14 +13342,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46171</v>
+        <v>46044</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13405,7 +13405,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46024</v>
+        <v>46035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13492,10 +13492,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44746</v>
+        <v>46035</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13551,7 +13551,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13565,10 +13565,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45057</v>
+        <v>46035</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13624,7 +13624,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13638,10 +13638,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44747</v>
+        <v>44642</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13697,7 +13697,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13707,14 +13707,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44978</v>
+        <v>45408</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13770,7 +13770,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13784,10 +13784,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45348</v>
+        <v>45475</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13843,7 +13843,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13853,14 +13853,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45034</v>
+        <v>46070</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13872,8 +13872,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13916,7 +13921,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13930,10 +13935,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45215</v>
+        <v>46197</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13946,7 +13951,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13989,7 +13994,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14003,10 +14008,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45582</v>
+        <v>45034</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14019,7 +14024,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14062,7 +14067,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14076,10 +14081,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46044</v>
+        <v>44930</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14092,7 +14097,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14135,7 +14140,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14149,10 +14154,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45043</v>
+        <v>46094</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14165,7 +14170,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14208,1278 +14213,1278 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
+          <t>A 28190-2022</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>44746</v>
+      </c>
+      <c r="E177" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178" ht="15" customHeight="1">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>A 20536-2023</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>45057</v>
+      </c>
+      <c r="E178" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179" ht="15" customHeight="1">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>A 29365-2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E179" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0</v>
+      </c>
+      <c r="V179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180" ht="15" customHeight="1">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>A 33412-2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E180" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>A 28385-2022</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>44747</v>
+      </c>
+      <c r="E181" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182" ht="15" customHeight="1">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>A 9732-2023</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>44978</v>
+      </c>
+      <c r="E182" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0</v>
+      </c>
+      <c r="V182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183" ht="15" customHeight="1">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>A 14886-2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E183" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>A 14853-2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E184" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>A 14873-2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E185" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186" ht="15" customHeight="1">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>A 14875-2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0</v>
+      </c>
+      <c r="V186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187" ht="15" customHeight="1">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>A 33354-2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0</v>
+      </c>
+      <c r="V187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188" ht="15" customHeight="1">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>A 7640-2024</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>5</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189" ht="15" customHeight="1">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>A 17077-2023</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>45034</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>A 46520-2024</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>45582</v>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>A 18715-2023</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0</v>
+      </c>
+      <c r="V191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192" ht="15" customHeight="1">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>A 16192-2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193" ht="15" customHeight="1">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>A 14798-2024</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D177" s="1" t="n">
+      <c r="D193" s="1" t="n">
         <v>45397</v>
       </c>
-      <c r="E177" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
+      <c r="E193" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I177" t="n">
+      <c r="I193" t="n">
         <v>2.8</v>
       </c>
-      <c r="J177" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" t="n">
-        <v>0</v>
-      </c>
-      <c r="L177" t="n">
-        <v>0</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0</v>
-      </c>
-      <c r="N177" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" t="n">
-        <v>0</v>
-      </c>
-      <c r="U177" t="n">
-        <v>0</v>
-      </c>
-      <c r="V177" s="2" t="inlineStr"/>
-      <c r="Z177">
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="Z193">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
         <v/>
       </c>
-      <c r="AA177">
+      <c r="AA193">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
         <v/>
       </c>
-      <c r="AB177">
+      <c r="AB193">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
         <v/>
       </c>
-      <c r="AC177">
+      <c r="AC193">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
         <v/>
       </c>
-      <c r="AD177">
+      <c r="AD193">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>A 1930-2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D178" s="1" t="n">
-        <v>46035</v>
-      </c>
-      <c r="E178" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J178" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" t="n">
-        <v>0</v>
-      </c>
-      <c r="N178" t="n">
-        <v>0</v>
-      </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="n">
-        <v>0</v>
-      </c>
-      <c r="T178" t="n">
-        <v>0</v>
-      </c>
-      <c r="U178" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>A 1925-2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D179" s="1" t="n">
-        <v>46035</v>
-      </c>
-      <c r="E179" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0</v>
-      </c>
-      <c r="N179" t="n">
-        <v>0</v>
-      </c>
-      <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0</v>
-      </c>
-      <c r="S179" t="n">
-        <v>0</v>
-      </c>
-      <c r="T179" t="n">
-        <v>0</v>
-      </c>
-      <c r="U179" t="n">
-        <v>0</v>
-      </c>
-      <c r="V179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>A 1933-2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D180" s="1" t="n">
-        <v>46035</v>
-      </c>
-      <c r="E180" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J180" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>A 9289-2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D181" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E181" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I181" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182" ht="15" customHeight="1">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>A 19051-2023</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D182" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="E182" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I182" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>A 59692-2023</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="n">
-        <v>45256</v>
-      </c>
-      <c r="E183" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J183" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="n">
-        <v>0</v>
-      </c>
-      <c r="T183" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" s="2" t="inlineStr"/>
-    </row>
-    <row r="184" ht="15" customHeight="1">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>A 49131-2024</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D184" s="1" t="n">
-        <v>45594</v>
-      </c>
-      <c r="E184" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I184" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J184" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" t="n">
-        <v>0</v>
-      </c>
-      <c r="M184" t="n">
-        <v>0</v>
-      </c>
-      <c r="N184" t="n">
-        <v>0</v>
-      </c>
-      <c r="O184" t="n">
-        <v>0</v>
-      </c>
-      <c r="P184" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="n">
-        <v>0</v>
-      </c>
-      <c r="T184" t="n">
-        <v>0</v>
-      </c>
-      <c r="U184" t="n">
-        <v>0</v>
-      </c>
-      <c r="V184" s="2" t="inlineStr"/>
-    </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>A 33942-2023</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D185" s="1" t="n">
-        <v>45134</v>
-      </c>
-      <c r="E185" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I185" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J185" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" t="n">
-        <v>0</v>
-      </c>
-      <c r="L185" t="n">
-        <v>0</v>
-      </c>
-      <c r="M185" t="n">
-        <v>0</v>
-      </c>
-      <c r="N185" t="n">
-        <v>0</v>
-      </c>
-      <c r="O185" t="n">
-        <v>0</v>
-      </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" t="n">
-        <v>0</v>
-      </c>
-      <c r="T185" t="n">
-        <v>0</v>
-      </c>
-      <c r="U185" t="n">
-        <v>0</v>
-      </c>
-      <c r="V185" s="2" t="inlineStr"/>
-    </row>
-    <row r="186" ht="15" customHeight="1">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>A 49481-2023</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D186" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E186" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I186" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J186" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0</v>
-      </c>
-      <c r="M186" t="n">
-        <v>0</v>
-      </c>
-      <c r="N186" t="n">
-        <v>0</v>
-      </c>
-      <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="n">
-        <v>0</v>
-      </c>
-      <c r="T186" t="n">
-        <v>0</v>
-      </c>
-      <c r="U186" t="n">
-        <v>0</v>
-      </c>
-      <c r="V186" s="2" t="inlineStr"/>
-    </row>
-    <row r="187" ht="15" customHeight="1">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>A 13491-2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D187" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E187" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I187" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J187" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" t="n">
-        <v>0</v>
-      </c>
-      <c r="L187" t="n">
-        <v>0</v>
-      </c>
-      <c r="M187" t="n">
-        <v>0</v>
-      </c>
-      <c r="N187" t="n">
-        <v>0</v>
-      </c>
-      <c r="O187" t="n">
-        <v>0</v>
-      </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0</v>
-      </c>
-      <c r="S187" t="n">
-        <v>0</v>
-      </c>
-      <c r="T187" t="n">
-        <v>0</v>
-      </c>
-      <c r="U187" t="n">
-        <v>0</v>
-      </c>
-      <c r="V187" s="2" t="inlineStr"/>
-    </row>
-    <row r="188" ht="15" customHeight="1">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>A 14886-2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D188" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E188" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I188" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J188" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" t="n">
-        <v>0</v>
-      </c>
-      <c r="M188" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" t="n">
-        <v>0</v>
-      </c>
-      <c r="U188" t="n">
-        <v>0</v>
-      </c>
-      <c r="V188" s="2" t="inlineStr"/>
-    </row>
-    <row r="189" ht="15" customHeight="1">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>A 14853-2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D189" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E189" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I189" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0</v>
-      </c>
-      <c r="M189" t="n">
-        <v>0</v>
-      </c>
-      <c r="N189" t="n">
-        <v>0</v>
-      </c>
-      <c r="O189" t="n">
-        <v>0</v>
-      </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="n">
-        <v>0</v>
-      </c>
-      <c r="T189" t="n">
-        <v>0</v>
-      </c>
-      <c r="U189" t="n">
-        <v>0</v>
-      </c>
-      <c r="V189" s="2" t="inlineStr"/>
-    </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>A 14873-2026</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D190" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E190" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I190" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J190" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" t="n">
-        <v>0</v>
-      </c>
-      <c r="N190" t="n">
-        <v>0</v>
-      </c>
-      <c r="O190" t="n">
-        <v>0</v>
-      </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="n">
-        <v>0</v>
-      </c>
-      <c r="T190" t="n">
-        <v>0</v>
-      </c>
-      <c r="U190" t="n">
-        <v>0</v>
-      </c>
-      <c r="V190" s="2" t="inlineStr"/>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>A 14875-2026</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D191" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E191" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I191" t="n">
-        <v>1</v>
-      </c>
-      <c r="J191" t="n">
-        <v>0</v>
-      </c>
-      <c r="K191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" t="n">
-        <v>0</v>
-      </c>
-      <c r="M191" t="n">
-        <v>0</v>
-      </c>
-      <c r="N191" t="n">
-        <v>0</v>
-      </c>
-      <c r="O191" t="n">
-        <v>0</v>
-      </c>
-      <c r="P191" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0</v>
-      </c>
-      <c r="S191" t="n">
-        <v>0</v>
-      </c>
-      <c r="T191" t="n">
-        <v>0</v>
-      </c>
-      <c r="U191" t="n">
-        <v>0</v>
-      </c>
-      <c r="V191" s="2" t="inlineStr"/>
-    </row>
-    <row r="192" ht="15" customHeight="1">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>A 57699-2023</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="n">
-        <v>45246</v>
-      </c>
-      <c r="E192" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I192" t="n">
-        <v>4</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>0</v>
-      </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="n">
-        <v>0</v>
-      </c>
-      <c r="T192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="n">
-        <v>0</v>
-      </c>
-      <c r="V192" s="2" t="inlineStr"/>
-    </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>A 13334-2022</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="n">
-        <v>44645</v>
-      </c>
-      <c r="E193" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J193" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="n">
-        <v>0</v>
-      </c>
-      <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" s="2" t="inlineStr"/>
-    </row>
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15493,10 +15498,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46197</v>
+        <v>46119</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15509,7 +15514,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15552,7 +15557,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15566,10 +15571,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15581,13 +15586,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15630,7 +15630,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46119</v>
+        <v>46128</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15703,7 +15703,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15717,10 +15717,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46119</v>
+        <v>45047</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15776,7 +15776,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15790,10 +15790,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45337</v>
+        <v>45256</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15849,7 +15849,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15863,10 +15863,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46128</v>
+        <v>45594</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15936,10 +15936,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45244</v>
+        <v>45134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15995,7 +15995,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16009,10 +16009,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16068,7 +16068,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16082,10 +16082,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45077</v>
+        <v>45211</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16141,7 +16141,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16155,10 +16155,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44965</v>
+        <v>45246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46246</v>
+        <v>44645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16287,7 +16287,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45799</v>
+        <v>46262</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16360,7 +16360,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16374,10 +16374,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45307</v>
+        <v>46220</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16433,7 +16433,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16447,10 +16447,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46247</v>
+        <v>46220</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>11.1</v>
+        <v>3.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16506,7 +16506,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16520,10 +16520,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45056</v>
+        <v>45337</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16579,7 +16579,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16593,10 +16593,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45558</v>
+        <v>46224</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16652,7 +16652,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16666,10 +16666,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46209</v>
+        <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16739,10 +16739,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44930</v>
+        <v>45244</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44501</v>
+        <v>45077</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44501</v>
+        <v>44965</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16944,7 +16944,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45294</v>
+        <v>45307</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17027,14 +17027,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44788</v>
+        <v>45056</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17104,10 +17104,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45581</v>
+        <v>46279</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17163,7 +17163,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17177,10 +17177,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44966</v>
+        <v>45558</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17236,7 +17236,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17246,14 +17246,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45014</v>
+        <v>44930</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17309,7 +17309,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17323,10 +17323,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46262</v>
+        <v>46239</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17382,7 +17382,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17396,10 +17396,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46220</v>
+        <v>46239</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17455,7 +17455,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17469,10 +17469,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45244</v>
+        <v>44501</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17528,7 +17528,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17542,10 +17542,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46220</v>
+        <v>44501</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17601,7 +17601,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45571</v>
+        <v>46239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45134</v>
+        <v>45294</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17747,7 +17747,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 38798-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17761,10 +17761,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46224</v>
+        <v>46286</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17820,7 +17820,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17830,14 +17830,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46224</v>
+        <v>44788</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17893,7 +17893,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45592</v>
+        <v>45581</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17966,7 +17966,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17980,10 +17980,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46279</v>
+        <v>44966</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18039,7 +18039,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18049,14 +18049,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45786</v>
+        <v>45014</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18112,7 +18112,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18126,10 +18126,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45721</v>
+        <v>45244</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18185,7 +18185,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18199,10 +18199,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45565</v>
+        <v>45571</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18258,7 +18258,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45735</v>
+        <v>45134</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18331,7 +18331,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18341,14 +18341,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45736</v>
+        <v>45592</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18404,7 +18404,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18418,10 +18418,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45736</v>
+        <v>45786</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18477,7 +18477,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18491,10 +18491,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46239</v>
+        <v>45721</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18550,7 +18550,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18564,10 +18564,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46239</v>
+        <v>45565</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>11.5</v>
+        <v>2.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18623,7 +18623,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18633,14 +18633,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45728</v>
+        <v>45735</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18696,7 +18696,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18706,14 +18706,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45798</v>
+        <v>45736</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18769,7 +18769,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18783,10 +18783,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46239</v>
+        <v>45736</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18852,14 +18852,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45798</v>
+        <v>45728</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18915,7 +18915,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18932,7 +18932,7 @@
         <v>45798</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18988,7 +18988,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19002,10 +19002,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45799</v>
+        <v>45798</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19061,7 +19061,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19075,10 +19075,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45589</v>
+        <v>45798</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19134,7 +19134,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19148,10 +19148,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45582</v>
+        <v>45799</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19207,7 +19207,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19221,10 +19221,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45582</v>
+        <v>45589</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19294,10 +19294,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45811</v>
+        <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19353,7 +19353,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19363,14 +19363,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45328</v>
+        <v>45582</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19382,13 +19382,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I247" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19431,7 +19426,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19445,10 +19440,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45603</v>
+        <v>45811</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19461,7 +19456,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19504,7 +19499,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19514,14 +19509,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45728</v>
+        <v>45328</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19533,8 +19528,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19591,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45826</v>
+        <v>45603</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44606</v>
+        <v>45728</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45743</v>
+        <v>45826</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19810,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45747</v>
+        <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45804</v>
+        <v>45743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44769</v>
+        <v>45747</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20015,24 +20015,24 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 130-2022</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44571</v>
+        <v>45804</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20088,148 +20088,221 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
+          <t>S 130-2022</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Åtgärd i nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E257" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>0</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="n">
+        <v>0</v>
+      </c>
+      <c r="V257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258" ht="15" customHeight="1">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>S 1659-2024</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D257" s="1" t="n">
+      <c r="D258" s="1" t="n">
         <v>45432</v>
       </c>
-      <c r="E257" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I257" t="n">
+      <c r="E258" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
         <v>2.5</v>
       </c>
-      <c r="J257" t="n">
-        <v>0</v>
-      </c>
-      <c r="K257" t="n">
-        <v>0</v>
-      </c>
-      <c r="L257" t="n">
-        <v>0</v>
-      </c>
-      <c r="M257" t="n">
-        <v>0</v>
-      </c>
-      <c r="N257" t="n">
-        <v>0</v>
-      </c>
-      <c r="O257" t="n">
-        <v>0</v>
-      </c>
-      <c r="P257" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="n">
-        <v>0</v>
-      </c>
-      <c r="T257" t="n">
-        <v>0</v>
-      </c>
-      <c r="U257" t="n">
-        <v>0</v>
-      </c>
-      <c r="V257" s="2" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="n">
+        <v>0</v>
+      </c>
+      <c r="V258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>S 2050-2025</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D258" s="1" t="n">
+      <c r="D259" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E258" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I258" t="n">
+      <c r="E259" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
         <v>2.2</v>
       </c>
-      <c r="J258" t="n">
-        <v>0</v>
-      </c>
-      <c r="K258" t="n">
-        <v>0</v>
-      </c>
-      <c r="L258" t="n">
-        <v>0</v>
-      </c>
-      <c r="M258" t="n">
-        <v>0</v>
-      </c>
-      <c r="N258" t="n">
-        <v>0</v>
-      </c>
-      <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0</v>
-      </c>
-      <c r="S258" t="n">
-        <v>0</v>
-      </c>
-      <c r="T258" t="n">
-        <v>0</v>
-      </c>
-      <c r="U258" t="n">
-        <v>0</v>
-      </c>
-      <c r="V258" s="2" t="inlineStr"/>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>0</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="n">
+        <v>0</v>
+      </c>
+      <c r="V259" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45742</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45838</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55617-2023</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45238</v>
+        <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1633,777 +1633,782 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 25575-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45803</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 47783-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 10515-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45721</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 11709-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 48163-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 55331-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 55617-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45238</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 47783-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 11709-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 55331-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Mandelriska</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 5009-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45691</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ljungpipare</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 27794-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Åkerrättika</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 17920-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18733-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
@@ -2424,7 +2429,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,7 +2521,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48163-2024</t>
+          <t>A 18733-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45589</v>
+        <v>46128</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2546,17 +2551,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14.4</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2570,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2586,39 +2591,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
         <v/>
       </c>
     </row>
@@ -2642,7 +2643,7 @@
         <v>45244</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2730,7 +2731,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25575-2025</t>
+          <t>A 5009-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2740,14 +2741,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45803</v>
+        <v>45691</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2759,19 +2760,14 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2798,49 +2794,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ljungpipare</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 10515-2025</t>
+          <t>A 27794-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45721</v>
+        <v>46191</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2870,20 +2870,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2894,10 +2894,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2906,39 +2906,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Åkerrättika</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60987-2021</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10977-2022</t>
+          <t>A 60987-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44628</v>
+        <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 10977-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44497</v>
+        <v>44628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13923-2022</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44650</v>
+        <v>45582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4951,13 +4951,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5000,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29373-2022</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5014,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44753</v>
+        <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5029,13 +5024,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>12.5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5078,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11979-2022</t>
+          <t>A 13923-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5088,14 +5078,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44635</v>
+        <v>44650</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5107,8 +5097,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5151,7 +5146,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29345-2022</t>
+          <t>A 29373-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5168,7 +5163,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5180,8 +5175,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 29345-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45592</v>
+        <v>44753</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 11979-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45517</v>
+        <v>44635</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45057</v>
+        <v>44978</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45545</v>
+        <v>45786</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44683</v>
+        <v>44788</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45751</v>
+        <v>45721</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44929</v>
+        <v>45565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5745,14 +5745,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45187</v>
+        <v>45736</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45399</v>
+        <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5891,14 +5891,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45399</v>
+        <v>45735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45238</v>
+        <v>45043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45345</v>
+        <v>45751</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6110,14 +6110,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45099</v>
+        <v>44642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6173,7 +6173,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45313</v>
+        <v>45246</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6246,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44852</v>
+        <v>45475</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6319,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44881</v>
+        <v>45419</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6392,7 +6392,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6402,14 +6402,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45566</v>
+        <v>44714</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6475,14 +6475,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45446</v>
+        <v>45456</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6538,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6548,14 +6548,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44784</v>
+        <v>45728</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44824</v>
+        <v>44769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6684,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6694,14 +6694,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44909</v>
+        <v>45397</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6713,8 +6713,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6753,11 +6758,31 @@
         <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr"/>
+      <c r="Z74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6771,10 +6796,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44714</v>
+        <v>45382</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6812,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6855,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6869,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45085</v>
+        <v>45250</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6860,7 +6885,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6903,7 +6928,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6942,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44623</v>
+        <v>45058</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6958,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7001,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7015,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44980</v>
+        <v>45798</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7031,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7074,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7088,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45337</v>
+        <v>45798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7104,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7147,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7132,14 +7157,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45244</v>
+        <v>45099</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7177,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7220,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7205,14 +7230,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45456</v>
+        <v>45798</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7225,7 +7250,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7268,7 +7293,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7282,10 +7307,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45419</v>
+        <v>45313</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7298,7 +7323,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7341,7 +7366,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7351,14 +7376,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45062</v>
+        <v>45408</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7371,7 +7396,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7414,7 +7439,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7428,10 +7453,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45884</v>
+        <v>45799</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7444,7 +7469,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7487,7 +7512,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7501,10 +7526,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45058</v>
+        <v>45896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7517,7 +7542,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7560,7 +7585,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7574,10 +7599,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45646</v>
+        <v>45896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7590,7 +7615,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7633,7 +7658,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7647,10 +7672,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45799</v>
+        <v>45896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7663,7 +7688,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7706,7 +7731,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7720,10 +7745,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44769</v>
+        <v>45896</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7736,7 +7761,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7779,7 +7804,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7793,10 +7818,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45946</v>
+        <v>45896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7809,7 +7834,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7852,7 +7877,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7866,10 +7891,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45274</v>
+        <v>45446</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7882,7 +7907,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7925,7 +7950,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7939,10 +7964,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44784</v>
+        <v>45897</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7955,7 +7980,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7998,7 +8023,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8012,10 +8037,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44838</v>
+        <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8028,7 +8053,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8071,7 +8096,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8085,10 +8110,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45897</v>
+        <v>45337</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8101,7 +8126,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8144,7 +8169,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8158,10 +8183,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45917</v>
+        <v>45294</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8174,7 +8199,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8217,7 +8242,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8231,10 +8256,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45896</v>
+        <v>44501</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8247,7 +8272,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8290,7 +8315,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8304,10 +8329,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45896</v>
+        <v>44501</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8320,7 +8345,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8363,7 +8388,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8377,10 +8402,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45896</v>
+        <v>44550</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8393,7 +8418,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8436,7 +8461,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8450,10 +8475,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45896</v>
+        <v>45307</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8466,7 +8491,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8509,7 +8534,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8523,10 +8548,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8539,7 +8564,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8582,7 +8607,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8596,10 +8621,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45902</v>
+        <v>45545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8612,7 +8637,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8655,7 +8680,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8669,10 +8694,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45905</v>
+        <v>45096</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8685,7 +8710,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8728,7 +8753,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8742,10 +8767,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45917</v>
+        <v>45581</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8758,7 +8783,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8801,7 +8826,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8815,10 +8840,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45917</v>
+        <v>45337</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8831,7 +8856,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8874,7 +8899,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8888,10 +8913,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45917</v>
+        <v>44980</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8904,7 +8929,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8947,7 +8972,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8961,10 +8986,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8977,7 +9002,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9020,7 +9045,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9034,10 +9059,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45922</v>
+        <v>45134</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9050,7 +9075,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9093,7 +9118,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9107,10 +9132,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45399</v>
+        <v>45918</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9166,7 +9191,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9180,10 +9205,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45390</v>
+        <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9239,7 +9264,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9253,10 +9278,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45930</v>
+        <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9312,7 +9337,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9326,10 +9351,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44587</v>
+        <v>45348</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9342,7 +9367,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9385,7 +9410,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9395,14 +9420,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45471</v>
+        <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9415,7 +9440,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9458,7 +9483,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9472,10 +9497,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44587</v>
+        <v>45636</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9488,7 +9513,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9531,7 +9556,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9545,10 +9570,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46141</v>
+        <v>45244</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9561,7 +9586,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9604,7 +9629,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9618,10 +9643,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46141</v>
+        <v>45134</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9634,7 +9659,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9677,7 +9702,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9691,10 +9716,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45134</v>
+        <v>45646</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9707,7 +9732,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9750,7 +9775,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9764,10 +9789,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46142</v>
+        <v>44881</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9780,7 +9805,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9823,7 +9848,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9837,10 +9862,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45337</v>
+        <v>45582</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9853,7 +9878,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>12.8</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9896,7 +9921,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9910,10 +9935,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45602</v>
+        <v>45582</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9926,7 +9951,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9969,7 +9994,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9983,10 +10008,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45636</v>
+        <v>45589</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9999,7 +10024,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10042,7 +10067,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10056,10 +10081,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45096</v>
+        <v>45930</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10072,7 +10097,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10115,7 +10140,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10129,10 +10154,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46154</v>
+        <v>45603</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10145,7 +10170,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10188,7 +10213,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10198,14 +10223,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45938</v>
+        <v>45328</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10217,8 +10242,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10261,7 +10291,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10275,10 +10305,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45943</v>
+        <v>45811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10291,7 +10321,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10334,7 +10364,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10348,10 +10378,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45134</v>
+        <v>44587</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10364,7 +10394,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10407,7 +10437,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10417,14 +10447,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46154</v>
+        <v>45471</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10437,7 +10467,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10480,7 +10510,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10494,10 +10524,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45571</v>
+        <v>44587</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10510,7 +10540,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10553,7 +10583,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10563,14 +10593,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46035</v>
+        <v>45728</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10582,13 +10612,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10631,7 +10656,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10645,10 +10670,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45589</v>
+        <v>45938</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10661,7 +10686,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>42</v>
+        <v>5.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10704,7 +10729,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10714,14 +10739,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45030</v>
+        <v>45014</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10734,7 +10759,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10777,7 +10802,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10791,10 +10816,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45958</v>
+        <v>44623</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10807,7 +10832,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10850,7 +10875,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10864,10 +10889,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45134</v>
+        <v>45571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10880,7 +10905,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10923,7 +10948,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10937,10 +10962,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45427</v>
+        <v>45030</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10953,7 +10978,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10996,7 +11021,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11010,10 +11035,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45817</v>
+        <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11026,7 +11051,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11069,7 +11094,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11083,10 +11108,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45964</v>
+        <v>45337</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11099,7 +11124,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.1</v>
+        <v>12.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11142,7 +11167,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11152,14 +11177,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45965</v>
+        <v>45566</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11172,7 +11197,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>13.4</v>
+        <v>5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11215,7 +11240,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11229,10 +11254,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45966</v>
+        <v>45211</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11245,7 +11270,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11288,7 +11313,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11302,10 +11327,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46163</v>
+        <v>45281</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11318,7 +11343,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11361,7 +11386,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11375,10 +11400,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45672</v>
+        <v>45582</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11391,7 +11416,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11434,7 +11459,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56261-2025</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11444,14 +11469,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45974</v>
+        <v>45602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11464,7 +11489,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11507,7 +11532,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11521,10 +11546,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45978</v>
+        <v>45057</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11537,7 +11562,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11580,7 +11605,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11594,10 +11619,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44630</v>
+        <v>45399</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11610,7 +11635,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11653,7 +11678,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11667,10 +11692,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44550</v>
+        <v>45238</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11683,7 +11708,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11726,7 +11751,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11740,10 +11765,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46007</v>
+        <v>45589</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11756,7 +11781,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>42</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11799,7 +11824,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11813,10 +11838,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45917</v>
+        <v>45958</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11829,7 +11854,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11872,7 +11897,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11882,14 +11907,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46171</v>
+        <v>45558</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11902,7 +11927,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.5</v>
+        <v>0.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11945,7 +11970,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11955,14 +11980,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45419</v>
+        <v>45964</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11975,7 +12000,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12018,7 +12043,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12028,14 +12053,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44659</v>
+        <v>45965</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12048,7 +12073,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.2</v>
+        <v>13.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12091,7 +12116,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12105,10 +12130,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45993</v>
+        <v>45966</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12121,7 +12146,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12164,7 +12189,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12174,14 +12199,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45994</v>
+        <v>45287</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12194,7 +12219,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12237,7 +12262,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 56261-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12247,14 +12272,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45582</v>
+        <v>45974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12267,7 +12292,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12310,7 +12335,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12320,14 +12345,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45287</v>
+        <v>45978</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12340,7 +12365,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>11.4</v>
+        <v>3.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12383,7 +12408,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12397,10 +12422,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45994</v>
+        <v>44838</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12413,7 +12438,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12456,7 +12481,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12470,10 +12495,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46000</v>
+        <v>45826</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12486,7 +12511,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12529,7 +12554,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12543,10 +12568,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45001</v>
+        <v>45057</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12559,7 +12584,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12602,7 +12627,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12616,10 +12641,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44722</v>
+        <v>44683</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12632,7 +12657,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12675,7 +12700,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12689,10 +12714,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44973</v>
+        <v>45639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12705,7 +12730,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12748,7 +12773,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12762,10 +12787,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45382</v>
+        <v>45244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12821,7 +12846,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12835,10 +12860,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45337</v>
+        <v>45187</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12851,7 +12876,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12894,7 +12919,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12908,10 +12933,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45001</v>
+        <v>45390</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12924,7 +12949,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12967,7 +12992,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12981,10 +13006,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45639</v>
+        <v>45672</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12997,7 +13022,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13040,7 +13065,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13054,10 +13079,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46024</v>
+        <v>44722</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13070,7 +13095,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13113,7 +13138,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13127,10 +13152,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45250</v>
+        <v>44824</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13143,7 +13168,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>19</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13186,7 +13211,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13200,10 +13225,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45281</v>
+        <v>45994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13216,7 +13241,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13259,7 +13284,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13273,10 +13298,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45215</v>
+        <v>45993</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13289,7 +13314,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13332,7 +13357,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13346,10 +13371,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46044</v>
+        <v>45994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13362,7 +13387,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>8.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13405,7 +13430,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13419,10 +13444,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46035</v>
+        <v>46024</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13435,7 +13460,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13478,7 +13503,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13492,10 +13517,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46035</v>
+        <v>46000</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13508,7 +13533,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13551,7 +13576,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13565,10 +13590,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46035</v>
+        <v>45256</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13581,7 +13606,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13624,7 +13649,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13638,10 +13663,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44642</v>
+        <v>44973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13654,7 +13679,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13697,7 +13722,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13707,14 +13732,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45408</v>
+        <v>46044</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13727,7 +13752,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13770,7 +13795,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13784,10 +13809,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45475</v>
+        <v>45215</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13800,7 +13825,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13843,7 +13868,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13853,14 +13878,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46070</v>
+        <v>44852</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13872,13 +13897,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13921,7 +13941,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13935,10 +13955,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46197</v>
+        <v>45345</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13951,7 +13971,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13994,7 +14014,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14008,10 +14028,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45034</v>
+        <v>46035</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14024,7 +14044,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14067,7 +14087,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14081,10 +14101,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44930</v>
+        <v>46035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14097,7 +14117,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14140,7 +14160,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14154,10 +14174,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46094</v>
+        <v>46035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14170,7 +14190,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14213,7 +14233,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14227,10 +14247,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44746</v>
+        <v>45399</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14243,7 +14263,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14286,7 +14306,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14296,14 +14316,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45057</v>
+        <v>45399</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14316,7 +14336,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14359,7 +14379,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 38798-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14373,10 +14393,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46203</v>
+        <v>46286</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14389,7 +14409,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14432,7 +14452,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14446,10 +14466,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46246</v>
+        <v>44784</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14462,7 +14482,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14505,7 +14525,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14519,10 +14539,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44747</v>
+        <v>44930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14578,7 +14598,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14592,10 +14612,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44978</v>
+        <v>45047</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14608,7 +14628,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14651,7 +14671,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14886-2026</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14665,10 +14685,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46104</v>
+        <v>44965</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14681,7 +14701,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14724,7 +14744,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14734,14 +14754,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46104</v>
+        <v>46070</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14753,8 +14773,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14797,7 +14822,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14811,10 +14836,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46104</v>
+        <v>45274</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14827,7 +14852,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14870,7 +14895,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14884,10 +14909,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46104</v>
+        <v>46246</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14900,7 +14925,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14943,7 +14968,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14957,10 +14982,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46247</v>
+        <v>44645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14973,7 +14998,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15016,7 +15041,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15030,10 +15055,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45348</v>
+        <v>45056</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15046,7 +15071,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15089,7 +15114,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15103,10 +15128,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45034</v>
+        <v>45085</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15119,7 +15144,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15162,7 +15187,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15176,10 +15201,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45582</v>
+        <v>45134</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15192,7 +15217,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15235,7 +15260,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15249,10 +15274,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45043</v>
+        <v>44606</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15265,7 +15290,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15308,7 +15333,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15322,10 +15347,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46111</v>
+        <v>45592</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15337,13 +15362,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>6.8</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15386,7 +15406,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15396,14 +15416,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45397</v>
+        <v>45001</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15415,13 +15435,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15460,31 +15475,11 @@
         <v>0</v>
       </c>
       <c r="V193" s="2" t="inlineStr"/>
-      <c r="Z193">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA193">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB193">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC193">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD193">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15498,10 +15493,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46119</v>
+        <v>46094</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15514,7 +15509,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15557,7 +15552,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15571,10 +15566,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46119</v>
+        <v>45062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15587,7 +15582,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15630,7 +15625,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15644,10 +15639,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46128</v>
+        <v>44966</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15660,7 +15655,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15703,7 +15698,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15717,10 +15712,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45047</v>
+        <v>46104</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15733,7 +15728,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15776,7 +15771,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15790,10 +15785,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45256</v>
+        <v>46104</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15806,7 +15801,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15849,7 +15844,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 14886-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15863,10 +15858,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45594</v>
+        <v>46104</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15879,7 +15874,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15922,7 +15917,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15936,10 +15931,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45134</v>
+        <v>46104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15952,7 +15947,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15995,7 +15990,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16009,10 +16004,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46209</v>
+        <v>45743</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16025,7 +16020,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16068,7 +16063,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16082,10 +16077,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45211</v>
+        <v>45034</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16098,7 +16093,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16141,7 +16136,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16155,10 +16150,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45246</v>
+        <v>44784</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16171,7 +16166,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16214,7 +16209,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16228,10 +16223,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44645</v>
+        <v>46111</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16243,8 +16238,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16287,7 +16287,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46262</v>
+        <v>44746</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16360,7 +16360,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16374,10 +16374,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46220</v>
+        <v>45747</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16433,7 +16433,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16447,10 +16447,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46220</v>
+        <v>45001</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16506,7 +16506,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16520,10 +16520,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45337</v>
+        <v>46119</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16579,7 +16579,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16593,10 +16593,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46224</v>
+        <v>45337</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16652,7 +16652,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16666,10 +16666,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46224</v>
+        <v>46119</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16739,10 +16739,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45244</v>
+        <v>45134</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45077</v>
+        <v>46128</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16881,14 +16881,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44965</v>
+        <v>44659</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16944,7 +16944,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45307</v>
+        <v>44630</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>10.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45056</v>
+        <v>45804</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17104,10 +17104,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46279</v>
+        <v>45917</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17163,7 +17163,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17177,10 +17177,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45558</v>
+        <v>45517</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17236,7 +17236,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17250,10 +17250,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44930</v>
+        <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17309,7 +17309,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17323,10 +17323,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46239</v>
+        <v>44909</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17382,7 +17382,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17396,10 +17396,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46239</v>
+        <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>11.5</v>
+        <v>1.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17455,7 +17455,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17469,10 +17469,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44501</v>
+        <v>45592</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17528,7 +17528,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17542,10 +17542,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44501</v>
+        <v>45799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17601,7 +17601,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46239</v>
+        <v>45244</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17684,14 +17684,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45294</v>
+        <v>45419</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17747,7 +17747,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 38798-2026</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17761,10 +17761,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46286</v>
+        <v>44929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17820,7 +17820,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17830,14 +17830,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44788</v>
+        <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17893,7 +17893,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17907,10 +17907,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45581</v>
+        <v>44930</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17966,7 +17966,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17980,10 +17980,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44966</v>
+        <v>46141</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18039,7 +18039,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18049,14 +18049,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45014</v>
+        <v>45571</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18126,10 +18126,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45244</v>
+        <v>45077</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18185,7 +18185,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18199,10 +18199,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45571</v>
+        <v>46141</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18258,7 +18258,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45134</v>
+        <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18331,7 +18331,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18345,10 +18345,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45592</v>
+        <v>46142</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18404,7 +18404,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18418,10 +18418,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45786</v>
+        <v>46154</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18477,7 +18477,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18491,10 +18491,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45721</v>
+        <v>46154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18550,7 +18550,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18564,10 +18564,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45565</v>
+        <v>45817</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18623,7 +18623,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18633,14 +18633,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45735</v>
+        <v>46035</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18652,8 +18652,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18696,7 +18701,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18706,14 +18711,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45736</v>
+        <v>45427</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18726,7 +18731,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18769,7 +18774,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18783,10 +18788,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45736</v>
+        <v>45134</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18799,7 +18804,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18842,7 +18847,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18852,14 +18857,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45728</v>
+        <v>46163</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18872,7 +18877,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18915,7 +18920,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18929,10 +18934,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45798</v>
+        <v>46007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18945,7 +18950,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18988,7 +18993,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19002,10 +19007,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45798</v>
+        <v>45917</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19018,7 +19023,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19061,7 +19066,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19071,14 +19076,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45798</v>
+        <v>46171</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19091,7 +19096,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19134,7 +19139,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19148,10 +19153,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45799</v>
+        <v>46197</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19164,7 +19169,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19207,7 +19212,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19221,10 +19226,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45589</v>
+        <v>46203</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19237,7 +19242,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19280,7 +19285,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19294,10 +19299,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45582</v>
+        <v>46247</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19310,7 +19315,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.1</v>
+        <v>11.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19353,7 +19358,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19367,10 +19372,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45582</v>
+        <v>46209</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19383,7 +19388,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19426,7 +19431,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19440,10 +19445,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45811</v>
+        <v>46262</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19456,7 +19461,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19499,7 +19504,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19509,14 +19514,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45328</v>
+        <v>46220</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19528,13 +19533,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19591,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45603</v>
+        <v>46220</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45728</v>
+        <v>46224</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45826</v>
+        <v>46224</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19810,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44606</v>
+        <v>46279</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45743</v>
+        <v>46239</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45747</v>
+        <v>46239</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20015,7 +20015,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20029,10 +20029,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45804</v>
+        <v>46239</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20105,7 +20105,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45432</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14752-2025</t>
+          <t>A 32666-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45742</v>
+        <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1197,149 +1197,149 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 32666-2025 artfynd.xlsx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 32666-2025 karta.png", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 32666-2025 georefererad karta.tif", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 32666-2025 FSC-klagomål.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 32666-2025 FSC-klagomål mail.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 32666-2025 tillsynsbegäran.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 32666-2025 tillsynsbegäran mail.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 14752-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45742</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 14752-2025 artfynd.xlsx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 14752-2025 karta.png", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 14752-2025 georefererad karta.tif", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14752-2025 FSC-klagomål.docx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14752-2025 FSC-klagomål mail.docx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14752-2025 tillsynsbegäran.docx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14752-2025 tillsynsbegäran mail.docx", "A 14752-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32666-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Guldlockmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 32666-2025 artfynd.xlsx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 32666-2025 karta.png", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 32666-2025 georefererad karta.tif", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 32666-2025 FSC-klagomål.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 32666-2025 FSC-klagomål mail.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 32666-2025 tillsynsbegäran.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 32666-2025 tillsynsbegäran mail.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55617-2023</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45238</v>
+        <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1633,1315 +1633,1315 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 25575-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45803</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 47783-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 48163-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 55331-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 10515-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45721</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 18733-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 27794-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Åkerrättika</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 11709-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 55617-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45238</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 47783-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J12" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 39899-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45166</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 11709-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 56739-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
         <v/>
       </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 55331-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45971</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 5009-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Mandelriska</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 5009-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45691</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Ljungpipare</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 17920-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 27794-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Åkerrättika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18733-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 39899-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45166</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 48163-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45589</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 56739-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 25575-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45803</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 10515-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45721</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5234,14 +5234,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45592</v>
+        <v>44788</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45517</v>
+        <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5380,14 +5380,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45057</v>
+        <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5453,14 +5453,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45545</v>
+        <v>45397</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5472,8 +5472,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5512,11 +5517,31 @@
         <v>0</v>
       </c>
       <c r="V57" s="2" t="inlineStr"/>
+      <c r="Z57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45751</v>
+        <v>45382</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5571,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44683</v>
+        <v>45250</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5644,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5687,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5701,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44929</v>
+        <v>45313</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5717,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5760,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5745,14 +5770,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45187</v>
+        <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5790,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5833,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5822,10 +5847,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45399</v>
+        <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5863,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5891,14 +5916,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45399</v>
+        <v>46024</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5936,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5954,7 +5979,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5968,10 +5993,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45238</v>
+        <v>45294</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +6009,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6027,7 +6052,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6041,10 +6066,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45099</v>
+        <v>45728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6114,10 +6139,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45313</v>
+        <v>45798</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6173,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6187,10 +6212,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44852</v>
+        <v>45798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6228,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6271,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6260,10 +6285,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44881</v>
+        <v>45798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6301,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6344,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6329,14 +6354,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45566</v>
+        <v>44769</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6349,7 +6374,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6392,7 +6417,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6406,10 +6431,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44909</v>
+        <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6447,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6490,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6479,10 +6504,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45446</v>
+        <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6495,7 +6520,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6563,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6552,10 +6577,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45345</v>
+        <v>45896</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6593,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6636,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6650,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44824</v>
+        <v>45896</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6666,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6709,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6723,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44784</v>
+        <v>45896</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,7 +6739,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6757,7 +6782,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6771,10 +6796,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44714</v>
+        <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6812,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6855,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6869,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45085</v>
+        <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6860,7 +6885,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6903,7 +6928,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6942,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44623</v>
+        <v>46044</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6958,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7001,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7015,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45337</v>
+        <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7031,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7074,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7088,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44980</v>
+        <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7104,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7147,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7136,10 +7161,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45244</v>
+        <v>45636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7177,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7220,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7209,10 +7234,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45419</v>
+        <v>45646</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7225,7 +7250,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7268,7 +7293,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7282,10 +7307,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45062</v>
+        <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7298,7 +7323,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7341,7 +7366,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7351,14 +7376,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45456</v>
+        <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7371,7 +7396,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7414,7 +7439,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7428,10 +7453,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45804</v>
+        <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7444,7 +7469,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7487,7 +7512,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7501,10 +7526,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45884</v>
+        <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7517,7 +7542,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7560,7 +7585,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7574,10 +7599,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45058</v>
+        <v>46035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7590,7 +7615,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7633,7 +7658,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7647,10 +7672,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45799</v>
+        <v>46035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7663,7 +7688,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7706,7 +7731,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7720,10 +7745,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45646</v>
+        <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7736,7 +7761,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7779,7 +7804,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7793,10 +7818,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44769</v>
+        <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7809,7 +7834,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7852,7 +7877,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7866,10 +7891,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45274</v>
+        <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7882,7 +7907,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7925,7 +7950,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7939,10 +7964,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44784</v>
+        <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7955,7 +7980,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7998,7 +8023,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8012,10 +8037,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45897</v>
+        <v>45922</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8028,7 +8053,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8071,7 +8096,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8081,14 +8106,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45896</v>
+        <v>46070</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8100,8 +8125,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8144,7 +8174,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8154,14 +8184,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45896</v>
+        <v>45014</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8174,7 +8204,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8217,7 +8247,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8231,10 +8261,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45896</v>
+        <v>44623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8247,7 +8277,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8290,7 +8320,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8304,10 +8334,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45896</v>
+        <v>45571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8320,7 +8350,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8363,7 +8393,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8377,10 +8407,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45896</v>
+        <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8393,7 +8423,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8436,7 +8466,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8450,10 +8480,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44838</v>
+        <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8466,7 +8496,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8509,7 +8539,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8519,14 +8549,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45946</v>
+        <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8539,7 +8569,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8582,7 +8612,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8596,10 +8626,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45902</v>
+        <v>45582</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8612,7 +8642,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8655,7 +8685,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8669,10 +8699,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45905</v>
+        <v>45582</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8685,7 +8715,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8728,7 +8758,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8742,10 +8772,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45917</v>
+        <v>45589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8758,7 +8788,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8801,7 +8831,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8815,10 +8845,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45917</v>
+        <v>44587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8831,7 +8861,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8874,7 +8904,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8884,14 +8914,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45917</v>
+        <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8904,7 +8934,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8947,7 +8977,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8961,10 +8991,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45917</v>
+        <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8977,7 +9007,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9020,7 +9050,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9034,10 +9064,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45918</v>
+        <v>45603</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9050,7 +9080,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9093,7 +9123,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9103,14 +9133,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45922</v>
+        <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9122,8 +9152,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9166,7 +9201,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9180,10 +9215,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45399</v>
+        <v>45211</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9196,7 +9231,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9239,7 +9274,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9253,10 +9288,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45390</v>
+        <v>45938</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9269,7 +9304,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9312,7 +9347,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9326,10 +9361,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45930</v>
+        <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9342,7 +9377,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9385,7 +9420,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9399,10 +9434,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44587</v>
+        <v>45057</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9415,7 +9450,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9458,7 +9493,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9472,10 +9507,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45134</v>
+        <v>45399</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9488,7 +9523,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9531,7 +9566,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9541,14 +9576,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45471</v>
+        <v>46094</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9561,7 +9596,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9604,7 +9639,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9618,10 +9653,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44587</v>
+        <v>45238</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9634,7 +9669,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9677,7 +9712,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9691,10 +9726,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45337</v>
+        <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9707,7 +9742,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>12.8</v>
+        <v>0.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9750,7 +9785,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9764,10 +9799,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45602</v>
+        <v>45589</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9780,7 +9815,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>42</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9823,7 +9858,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9837,10 +9872,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45636</v>
+        <v>45811</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9853,7 +9888,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9896,7 +9931,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9910,10 +9945,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45096</v>
+        <v>45558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9926,7 +9961,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9969,7 +10004,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9983,10 +10018,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45938</v>
+        <v>46104</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9999,7 +10034,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10042,7 +10077,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10056,10 +10091,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45134</v>
+        <v>46104</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10072,7 +10107,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10115,7 +10150,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 14886-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10129,10 +10164,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45943</v>
+        <v>46104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10145,7 +10180,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10188,7 +10223,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10202,10 +10237,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45571</v>
+        <v>46104</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10218,7 +10253,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10261,7 +10296,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10275,10 +10310,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45589</v>
+        <v>46111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10290,8 +10325,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10334,7 +10374,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10344,14 +10384,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45030</v>
+        <v>45287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10364,7 +10404,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.2</v>
+        <v>11.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10424,7 +10464,7 @@
         <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10480,7 +10520,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10494,10 +10534,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45964</v>
+        <v>46119</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10510,7 +10550,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10553,7 +10593,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10567,10 +10607,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45965</v>
+        <v>46119</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10583,7 +10623,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>13.4</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10626,7 +10666,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10640,10 +10680,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45672</v>
+        <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10656,7 +10696,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10699,7 +10739,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10713,10 +10753,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45966</v>
+        <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10729,7 +10769,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.4</v>
+        <v>13.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10772,7 +10812,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10786,10 +10826,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46141</v>
+        <v>45728</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10802,7 +10842,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10845,7 +10885,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10859,10 +10899,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46141</v>
+        <v>45966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10875,7 +10915,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10918,7 +10958,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10932,10 +10972,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44630</v>
+        <v>45057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10948,7 +10988,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10991,7 +11031,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11005,10 +11045,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44550</v>
+        <v>45639</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11021,7 +11061,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11081,7 +11121,7 @@
         <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11154,7 +11194,7 @@
         <v>45978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11210,7 +11250,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11220,14 +11260,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45419</v>
+        <v>46128</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11240,7 +11280,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11283,7 +11323,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11293,14 +11333,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44659</v>
+        <v>45672</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11313,7 +11353,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11356,7 +11396,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11370,10 +11410,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45582</v>
+        <v>45917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11386,7 +11426,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11429,7 +11469,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11439,14 +11479,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45287</v>
+        <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11459,7 +11499,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>11.4</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11502,7 +11542,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11516,10 +11556,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46142</v>
+        <v>44747</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11532,7 +11572,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11575,7 +11615,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11589,10 +11629,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11605,7 +11645,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11648,7 +11688,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11662,10 +11702,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45994</v>
+        <v>45993</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11678,7 +11718,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11721,7 +11761,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11735,10 +11775,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45001</v>
+        <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11751,7 +11791,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11794,7 +11834,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11808,10 +11848,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44722</v>
+        <v>45799</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11824,7 +11864,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11867,7 +11907,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11881,10 +11921,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11897,7 +11937,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11940,7 +11980,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11954,10 +11994,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46154</v>
+        <v>44978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11970,7 +12010,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12013,7 +12053,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12027,10 +12067,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46000</v>
+        <v>45826</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12043,7 +12083,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12086,7 +12126,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12100,10 +12140,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46154</v>
+        <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12116,7 +12156,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12159,7 +12199,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12173,10 +12213,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44973</v>
+        <v>45043</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12189,7 +12229,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12232,7 +12272,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12246,10 +12286,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45382</v>
+        <v>45751</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12262,7 +12302,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12305,7 +12345,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12319,10 +12359,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45337</v>
+        <v>46141</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12335,7 +12375,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12378,7 +12418,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12392,10 +12432,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45001</v>
+        <v>44642</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12408,7 +12448,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12451,7 +12491,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12461,14 +12501,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46035</v>
+        <v>45246</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12480,13 +12520,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12529,7 +12564,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12543,10 +12578,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45639</v>
+        <v>45475</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12559,7 +12594,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12602,7 +12637,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12616,10 +12651,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45250</v>
+        <v>46141</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12632,7 +12667,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12675,7 +12710,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12689,10 +12724,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45134</v>
+        <v>46142</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12705,7 +12740,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12748,7 +12783,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12762,10 +12797,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45281</v>
+        <v>44714</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12778,7 +12813,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12821,7 +12856,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12835,10 +12870,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45427</v>
+        <v>46154</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12851,7 +12886,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12894,7 +12929,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12908,10 +12943,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45817</v>
+        <v>45058</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12924,7 +12959,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12967,7 +13002,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12981,10 +13016,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46024</v>
+        <v>46154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12997,7 +13032,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13040,7 +13075,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13050,14 +13085,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46163</v>
+        <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13070,7 +13105,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13113,7 +13148,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13127,10 +13162,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45215</v>
+        <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13143,7 +13178,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13186,7 +13221,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13196,14 +13231,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44642</v>
+        <v>46035</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13215,8 +13250,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13259,7 +13299,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13273,10 +13313,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46044</v>
+        <v>45427</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13289,7 +13329,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13332,7 +13372,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13342,14 +13382,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45408</v>
+        <v>45134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13362,7 +13402,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13405,7 +13445,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13419,10 +13459,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45475</v>
+        <v>46163</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13435,7 +13475,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13478,7 +13518,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13492,10 +13532,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46035</v>
+        <v>44606</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13508,7 +13548,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13551,7 +13591,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13565,10 +13605,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46035</v>
+        <v>46007</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13581,7 +13621,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13624,7 +13664,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13638,10 +13678,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46035</v>
+        <v>45337</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13654,7 +13694,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13697,7 +13737,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13711,10 +13751,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46007</v>
+        <v>44501</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13727,7 +13767,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13770,7 +13810,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13784,10 +13824,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45034</v>
+        <v>44501</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13800,7 +13840,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13843,7 +13883,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13857,10 +13897,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45917</v>
+        <v>44550</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13873,7 +13913,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13916,7 +13956,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13926,14 +13966,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46171</v>
+        <v>45917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13946,7 +13986,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13989,7 +14029,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14003,10 +14043,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44930</v>
+        <v>45307</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14019,7 +14059,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14062,7 +14102,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14072,14 +14112,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46070</v>
+        <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14091,13 +14131,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14140,7 +14175,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14150,14 +14185,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44746</v>
+        <v>46171</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14170,7 +14205,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14213,7 +14248,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14227,10 +14262,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45057</v>
+        <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14243,7 +14278,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14286,7 +14321,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14300,10 +14335,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44747</v>
+        <v>45096</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14316,7 +14351,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14359,7 +14394,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14373,10 +14408,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44978</v>
+        <v>45581</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14389,7 +14424,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14432,7 +14467,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14446,10 +14481,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46094</v>
+        <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14462,7 +14497,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14505,7 +14540,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14519,10 +14554,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45348</v>
+        <v>44980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14535,7 +14570,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14578,7 +14613,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14592,10 +14627,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45034</v>
+        <v>45134</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14608,7 +14643,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14651,7 +14686,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14665,10 +14700,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45582</v>
+        <v>45348</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14681,7 +14716,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14724,7 +14759,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 14886-2026</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14738,10 +14773,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46104</v>
+        <v>45244</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14754,7 +14789,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14797,7 +14832,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14811,10 +14846,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45043</v>
+        <v>45134</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14827,7 +14862,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14870,7 +14905,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14884,10 +14919,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46104</v>
+        <v>45804</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14900,7 +14935,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14943,7 +14978,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14957,10 +14992,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46104</v>
+        <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14973,7 +15008,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15016,7 +15051,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15030,10 +15065,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46104</v>
+        <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15046,7 +15081,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>12.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15089,7 +15124,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15099,14 +15134,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45397</v>
+        <v>45281</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15118,13 +15153,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.8</v>
+        <v>7.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15163,31 +15193,11 @@
         <v>0</v>
       </c>
       <c r="V189" s="2" t="inlineStr"/>
-      <c r="Z189">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA189">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB189">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC189">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD189">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15201,10 +15211,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46111</v>
+        <v>45884</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15216,13 +15226,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15265,7 +15270,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15279,10 +15284,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46119</v>
+        <v>46203</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15295,7 +15300,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15338,7 +15343,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15352,10 +15357,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46119</v>
+        <v>45602</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15368,7 +15373,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15411,7 +15416,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15425,10 +15430,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45047</v>
+        <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15441,7 +15446,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15484,7 +15489,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15498,10 +15503,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45256</v>
+        <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15514,7 +15519,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15557,7 +15562,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15571,10 +15576,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46128</v>
+        <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15587,7 +15592,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15630,7 +15635,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15644,10 +15649,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45594</v>
+        <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15660,7 +15665,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15703,7 +15708,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15717,10 +15722,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45134</v>
+        <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15733,7 +15738,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15776,7 +15781,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15790,10 +15795,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46197</v>
+        <v>46262</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15806,7 +15811,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15849,7 +15854,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15863,10 +15868,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45211</v>
+        <v>45390</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15879,7 +15884,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15922,7 +15927,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15936,10 +15941,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46203</v>
+        <v>44722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15952,7 +15957,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15995,7 +16000,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16009,10 +16014,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45246</v>
+        <v>44824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16025,7 +16030,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16068,7 +16073,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16082,10 +16087,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44645</v>
+        <v>46220</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16098,7 +16103,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16141,7 +16146,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16155,10 +16160,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46209</v>
+        <v>46220</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16171,7 +16176,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16214,7 +16219,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16228,10 +16233,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45337</v>
+        <v>45256</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16244,7 +16249,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16287,7 +16292,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16301,10 +16306,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45244</v>
+        <v>44973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16317,7 +16322,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16360,7 +16365,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16374,10 +16379,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45077</v>
+        <v>46224</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16390,7 +16395,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16433,7 +16438,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16447,10 +16452,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44965</v>
+        <v>46224</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16463,7 +16468,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16506,7 +16511,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16520,10 +16525,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45307</v>
+        <v>44852</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16536,7 +16541,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16579,7 +16584,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16593,10 +16598,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46262</v>
+        <v>45345</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16609,7 +16614,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16652,7 +16657,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16666,10 +16671,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46220</v>
+        <v>45399</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16682,7 +16687,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16725,7 +16730,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16735,14 +16740,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45056</v>
+        <v>45399</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16755,7 +16760,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16798,7 +16803,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16812,10 +16817,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46220</v>
+        <v>46239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16828,7 +16833,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.2</v>
+        <v>11.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16871,7 +16876,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16885,10 +16890,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16901,7 +16906,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16944,7 +16949,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16958,10 +16963,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16974,7 +16979,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17017,7 +17022,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17031,10 +17036,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45558</v>
+        <v>44784</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17047,7 +17052,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17090,7 +17095,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17107,7 +17112,7 @@
         <v>44930</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17120,7 +17125,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17163,7 +17168,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17177,10 +17182,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44501</v>
+        <v>45047</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17193,7 +17198,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17236,7 +17241,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17250,10 +17255,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44501</v>
+        <v>44965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17266,7 +17271,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17309,7 +17314,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 38798-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17323,10 +17328,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45294</v>
+        <v>46286</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17339,7 +17344,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17382,7 +17387,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17392,14 +17397,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44788</v>
+        <v>45274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17412,7 +17417,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17455,7 +17460,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17469,10 +17474,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45581</v>
+        <v>46246</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17485,7 +17490,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17528,7 +17533,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17542,10 +17547,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44966</v>
+        <v>44645</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17558,7 +17563,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17601,7 +17606,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17611,14 +17616,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45014</v>
+        <v>45056</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17631,7 +17636,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17674,7 +17679,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17688,10 +17693,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45244</v>
+        <v>45085</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17704,7 +17709,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17747,7 +17752,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17761,10 +17766,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45571</v>
+        <v>45134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17777,7 +17782,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17820,7 +17825,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17834,10 +17839,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45134</v>
+        <v>45592</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17850,7 +17855,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17893,7 +17898,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17907,10 +17912,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45592</v>
+        <v>45001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17923,7 +17928,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17966,7 +17971,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17980,10 +17985,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46239</v>
+        <v>45062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17996,7 +18001,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18039,7 +18044,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18053,10 +18058,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18069,7 +18074,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18112,7 +18117,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18126,10 +18131,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46239</v>
+        <v>46279</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18142,7 +18147,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18185,7 +18190,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 38798-2026</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18199,10 +18204,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46286</v>
+        <v>44966</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18215,7 +18220,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18258,7 +18263,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18272,10 +18277,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45786</v>
+        <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18288,7 +18293,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18331,7 +18336,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18345,10 +18350,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45721</v>
+        <v>44784</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18361,7 +18366,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18404,7 +18409,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18418,10 +18423,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45565</v>
+        <v>44746</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18434,7 +18439,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18477,7 +18482,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18491,10 +18496,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45735</v>
+        <v>45001</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18507,7 +18512,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18550,7 +18555,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18564,10 +18569,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46246</v>
+        <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18580,7 +18585,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18623,7 +18628,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18633,14 +18638,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45736</v>
+        <v>45134</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18653,7 +18658,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18696,7 +18701,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18706,14 +18711,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45736</v>
+        <v>44659</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18726,7 +18731,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18769,7 +18774,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18779,14 +18784,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45728</v>
+        <v>44630</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18799,7 +18804,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.2</v>
+        <v>10.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18842,7 +18847,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18856,10 +18861,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46279</v>
+        <v>45517</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18872,7 +18877,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18915,7 +18920,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18929,10 +18934,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45798</v>
+        <v>45594</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18945,7 +18950,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18988,7 +18993,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19002,10 +19007,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45798</v>
+        <v>44909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19018,7 +19023,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19061,7 +19066,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19075,10 +19080,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45798</v>
+        <v>45592</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19091,7 +19096,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19134,7 +19139,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19148,10 +19153,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45799</v>
+        <v>45244</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19164,7 +19169,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19207,7 +19212,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19217,14 +19222,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46247</v>
+        <v>45419</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19237,7 +19242,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>11.1</v>
+        <v>1.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19280,7 +19285,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19294,10 +19299,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45589</v>
+        <v>44929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19310,7 +19315,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19353,7 +19358,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19367,10 +19372,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45582</v>
+        <v>44930</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19383,7 +19388,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19426,7 +19431,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19440,10 +19445,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45582</v>
+        <v>45571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19456,7 +19461,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19499,7 +19504,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19513,10 +19518,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45811</v>
+        <v>45077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19529,7 +19534,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19572,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19582,14 +19587,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45328</v>
+        <v>45034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19601,13 +19606,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45603</v>
+        <v>45786</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45728</v>
+        <v>45721</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19810,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45826</v>
+        <v>45565</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19879,14 +19879,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44606</v>
+        <v>45736</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45743</v>
+        <v>45736</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20015,7 +20015,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20029,10 +20029,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45747</v>
+        <v>45735</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20105,7 +20105,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45432</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45742</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45931</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45589</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45971</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45721</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46128</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>46191</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45238</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44788</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45397</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45382</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>45250</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>45313</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>46024</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45294</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45798</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>45798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>44769</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>45896</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45896</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45896</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>46044</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45646</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>46035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45922</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46070</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45014</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45582</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45582</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>45603</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45211</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45938</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45057</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45399</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>46094</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45238</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45589</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45811</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>46104</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>46104</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>46104</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>46111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>46119</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>46119</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45728</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45639</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46128</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45672</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44747</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45993</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45799</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>46000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45826</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45043</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45751</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>46141</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44642</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45246</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45475</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46141</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>46142</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44714</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>46154</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45058</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>46154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46035</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45427</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46163</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44606</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46007</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45337</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44501</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44501</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44550</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45307</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46171</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>45096</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45581</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45134</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45348</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45244</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45134</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45804</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45281</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45884</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>46203</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45602</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>46262</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45390</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>46220</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>46220</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45256</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>46224</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>46224</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44852</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45345</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45399</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45399</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>46239</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>46239</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44784</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44930</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45047</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>46286</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46246</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44645</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45056</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45085</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45592</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>45062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>46247</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>46279</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44966</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44784</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44746</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45001</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45134</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44659</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>44630</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45517</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45594</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45592</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45244</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45419</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44930</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45786</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45721</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45565</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45736</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45736</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45735</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45432</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45742</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45931</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45589</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45971</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45721</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46128</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>46191</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45238</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44467</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44565</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44851</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44488</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44857</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44563</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44693</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44650</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44635</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44753</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44788</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45397</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45382</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>45250</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>45313</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45408</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45446</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>46024</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45294</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45798</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>45798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>44769</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>45896</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45896</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45896</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>46044</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45646</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>46035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45917</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45922</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46070</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45014</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44623</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45030</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45566</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45582</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45582</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45589</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>45603</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45328</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45211</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45938</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>45057</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45399</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>46094</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45238</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45589</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45811</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>46104</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>46104</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>46104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>46104</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>46111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45958</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>46119</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>46119</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45728</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>45057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45639</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>46128</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45672</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44747</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45993</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45799</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>46000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45826</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45043</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45751</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>46141</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44642</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45246</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45475</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>46141</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>46142</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44714</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>46154</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45058</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>46154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>46035</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45427</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46163</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44606</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46007</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45337</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44501</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44501</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44550</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45307</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46171</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>45096</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45581</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45134</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45348</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45244</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45134</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45804</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>46197</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45337</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45281</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45884</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>46203</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45602</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>46209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>46262</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45390</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>46220</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>46220</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45256</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44973</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>46224</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>46224</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44852</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45345</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45399</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45399</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>46239</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>46239</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44784</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44930</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45047</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>44965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>46286</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46246</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44645</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45056</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45085</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45592</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>45062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>46247</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>46279</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44966</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44784</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44746</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45001</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45134</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44659</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>44630</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45517</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45594</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45592</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45244</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45419</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44930</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45786</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45721</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45565</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45736</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45736</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45735</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45432</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45742</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45040</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55617-2023</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45238</v>
+        <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1633,35 +1633,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
         <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45721</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55331-2025</t>
+          <t>A 48163-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45971</v>
+        <v>45589</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2058,143 +2058,147 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 55331-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Mandelriska</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55331-2025 artfynd.xlsx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55331-2025 karta.png", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55331-2025 georefererad karta.tif", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55331-2025 FSC-klagomål.docx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55331-2025 FSC-klagomål mail.docx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55331-2025 tillsynsbegäran.docx", "A 55331-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55331-2025 tillsynsbegäran mail.docx", "A 55331-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 11709-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2215,7 +2219,7 @@
         <v>46128</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2303,7 +2307,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5009-2025</t>
+          <t>A 11709-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2317,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45691</v>
+        <v>45373</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2333,17 +2337,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2357,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2373,46 +2377,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ljungpipare</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17920-2023</t>
+          <t>A 55617-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45040</v>
+        <v>45238</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2482,35 +2482,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
         <v/>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         <v>46191</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48163-2024</t>
+          <t>A 56739-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45589</v>
+        <v>45244</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2761,17 +2761,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14.4</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2797,50 +2797,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56739-2023</t>
+          <t>A 5009-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2850,14 +2846,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45244</v>
+        <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2870,16 +2866,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2894,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2906,39 +2902,43 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ljungpipare</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29346-2022</t>
+          <t>A 34717-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44753</v>
+        <v>44795</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 34717-2022</t>
+          <t>A 29346-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44795</v>
+        <v>44753</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44585</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 10977-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44497</v>
+        <v>44628</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10977-2022</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44628</v>
+        <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44753</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45592</v>
+        <v>44788</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45517</v>
+        <v>45419</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45057</v>
+        <v>45456</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5380,14 +5380,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45545</v>
+        <v>45397</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5399,8 +5399,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5439,11 +5444,31 @@
         <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr"/>
+      <c r="Z56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5457,10 +5482,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44683</v>
+        <v>45382</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5498,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5516,7 +5541,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45751</v>
+        <v>45250</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5571,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44929</v>
+        <v>45721</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5644,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5687,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5701,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>45313</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5717,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5760,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5749,10 +5774,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45399</v>
+        <v>45565</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5790,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5833,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5822,10 +5847,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45399</v>
+        <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5863,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5895,10 +5920,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45786</v>
+        <v>45736</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5936,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5954,7 +5979,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5968,10 +5993,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45884</v>
+        <v>45735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +6009,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6027,7 +6052,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6037,14 +6062,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45345</v>
+        <v>45408</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6114,10 +6139,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45721</v>
+        <v>45446</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6173,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6183,14 +6208,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45565</v>
+        <v>45728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6228,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6271,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6260,10 +6285,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45735</v>
+        <v>46024</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6301,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6344,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6333,10 +6358,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45238</v>
+        <v>44769</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6349,7 +6374,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6392,7 +6417,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6402,14 +6427,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45736</v>
+        <v>45294</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6447,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6490,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6479,10 +6504,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45736</v>
+        <v>45798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6495,7 +6520,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6563,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6548,14 +6573,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45099</v>
+        <v>45798</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6593,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6636,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6621,14 +6646,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45728</v>
+        <v>45798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6666,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6709,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6723,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,7 +6739,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6757,7 +6782,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6771,10 +6796,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44852</v>
+        <v>45337</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6812,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6855,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6869,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45313</v>
+        <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6860,7 +6885,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6903,7 +6928,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6942,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45798</v>
+        <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6958,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7001,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7015,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45798</v>
+        <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7031,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7074,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7088,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45799</v>
+        <v>45896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7104,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7147,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7136,10 +7161,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45897</v>
+        <v>45896</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7177,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7220,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7209,10 +7234,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7225,7 +7250,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7268,7 +7293,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7282,10 +7307,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45896</v>
+        <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7298,7 +7323,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7341,7 +7366,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7355,10 +7380,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45896</v>
+        <v>45582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7371,7 +7396,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7414,7 +7439,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7428,10 +7453,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45896</v>
+        <v>45582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7444,7 +7469,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7487,7 +7512,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7501,10 +7526,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45896</v>
+        <v>45636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7517,7 +7542,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7560,7 +7585,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7574,10 +7599,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45902</v>
+        <v>45589</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7590,7 +7615,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7633,7 +7658,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7647,10 +7672,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45589</v>
+        <v>45646</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7663,7 +7688,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7723,7 +7748,7 @@
         <v>45905</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7779,7 +7804,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7793,10 +7818,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45582</v>
+        <v>44881</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7809,7 +7834,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7852,7 +7877,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7866,10 +7891,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45582</v>
+        <v>45603</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7882,7 +7907,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7925,7 +7950,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7935,14 +7960,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44881</v>
+        <v>45328</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7954,8 +7979,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8015,7 +8045,7 @@
         <v>45811</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8071,7 +8101,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8081,14 +8111,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45328</v>
+        <v>45728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8100,13 +8130,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8149,7 +8174,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8163,10 +8188,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45603</v>
+        <v>45826</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8179,7 +8204,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8222,7 +8247,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8232,14 +8257,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45566</v>
+        <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8252,7 +8277,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8295,7 +8320,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8309,10 +8334,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45728</v>
+        <v>45918</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8325,7 +8350,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8368,7 +8393,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8382,10 +8407,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44909</v>
+        <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8398,7 +8423,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8458,7 +8483,7 @@
         <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8514,7 +8539,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8528,10 +8553,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45917</v>
+        <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8587,7 +8612,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8597,14 +8622,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45917</v>
+        <v>45014</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8617,7 +8642,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8660,7 +8685,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8674,10 +8699,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45918</v>
+        <v>44623</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8690,7 +8715,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8733,7 +8758,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8747,10 +8772,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45446</v>
+        <v>45571</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8763,7 +8788,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8806,7 +8831,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8820,10 +8845,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44784</v>
+        <v>45030</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8836,7 +8861,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8879,7 +8904,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8893,10 +8918,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45922</v>
+        <v>46044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8909,7 +8934,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8952,7 +8977,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8962,14 +8987,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44824</v>
+        <v>45566</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8982,7 +9007,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9025,7 +9050,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9039,10 +9064,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45826</v>
+        <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9055,7 +9080,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9098,7 +9123,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9112,10 +9137,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45930</v>
+        <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9128,7 +9153,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9171,7 +9196,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9181,14 +9206,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44587</v>
+        <v>45471</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9201,7 +9226,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9244,7 +9269,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9254,14 +9279,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45471</v>
+        <v>44587</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9274,7 +9299,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9317,7 +9342,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9331,10 +9356,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44714</v>
+        <v>45215</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9347,7 +9372,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9390,7 +9415,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9404,10 +9429,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44587</v>
+        <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9420,7 +9445,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9463,7 +9488,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9477,10 +9502,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45085</v>
+        <v>45211</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9493,7 +9518,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9536,7 +9561,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9550,10 +9575,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44623</v>
+        <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9566,7 +9591,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9609,7 +9634,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9623,10 +9648,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45938</v>
+        <v>45582</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9639,7 +9664,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9682,7 +9707,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9696,10 +9721,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45943</v>
+        <v>45057</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9712,7 +9737,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9755,7 +9780,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9769,10 +9794,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44606</v>
+        <v>45399</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9785,7 +9810,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9828,7 +9853,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9842,10 +9867,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45337</v>
+        <v>45743</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9858,7 +9883,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9901,7 +9926,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9915,10 +9940,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44980</v>
+        <v>45238</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9931,7 +9956,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9974,7 +9999,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9988,10 +10013,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45244</v>
+        <v>45943</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10004,7 +10029,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10047,7 +10072,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10061,10 +10086,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46024</v>
+        <v>45589</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10077,7 +10102,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>42</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10120,7 +10145,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10134,10 +10159,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45743</v>
+        <v>45558</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10150,7 +10175,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10210,7 +10235,7 @@
         <v>45747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10266,7 +10291,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10276,14 +10301,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45456</v>
+        <v>46035</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10296,7 +10321,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10339,7 +10364,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10353,10 +10378,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45958</v>
+        <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10369,7 +10394,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10412,7 +10437,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10426,10 +10451,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45804</v>
+        <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10442,7 +10467,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10485,7 +10510,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10499,10 +10524,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45419</v>
+        <v>45804</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10515,7 +10540,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10558,7 +10583,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10568,14 +10593,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45964</v>
+        <v>45287</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10588,7 +10613,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.1</v>
+        <v>11.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10631,7 +10656,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10645,10 +10670,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45965</v>
+        <v>45958</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10661,7 +10686,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>13.4</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10704,7 +10729,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10718,10 +10743,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45966</v>
+        <v>45884</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10734,7 +10759,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10777,7 +10802,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10791,10 +10816,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44769</v>
+        <v>45964</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10807,7 +10832,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10850,7 +10875,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10864,10 +10889,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45062</v>
+        <v>45965</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10880,7 +10905,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.4</v>
+        <v>13.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10923,7 +10948,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56261-2025</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10933,14 +10958,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45974</v>
+        <v>45966</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10953,7 +10978,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10996,7 +11021,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11010,10 +11035,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45978</v>
+        <v>45057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11026,7 +11051,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11069,7 +11094,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 56261-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11079,14 +11104,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45215</v>
+        <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11099,7 +11124,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11142,7 +11167,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11156,10 +11181,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46044</v>
+        <v>45639</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11172,7 +11197,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11215,7 +11240,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11225,14 +11250,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45058</v>
+        <v>46070</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11244,8 +11269,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11288,7 +11318,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11302,10 +11332,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45646</v>
+        <v>45978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11318,7 +11348,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11361,7 +11391,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11375,10 +11405,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45993</v>
+        <v>45672</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11391,7 +11421,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11434,7 +11464,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11448,10 +11478,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45994</v>
+        <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11464,7 +11494,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>8.9</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11507,7 +11537,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11521,10 +11551,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45274</v>
+        <v>44747</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11537,7 +11567,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11597,7 +11627,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11653,7 +11683,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11667,10 +11697,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44784</v>
+        <v>45993</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11683,7 +11713,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11726,7 +11756,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11740,10 +11770,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46035</v>
+        <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11756,7 +11786,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>8.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11799,7 +11829,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11813,10 +11843,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44838</v>
+        <v>46000</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11829,7 +11859,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11872,7 +11902,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11886,10 +11916,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46035</v>
+        <v>44978</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11902,7 +11932,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11945,7 +11975,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11959,10 +11989,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46035</v>
+        <v>46094</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11975,7 +12005,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12018,7 +12048,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12032,10 +12062,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46000</v>
+        <v>46104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12048,7 +12078,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12091,7 +12121,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12101,14 +12131,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46070</v>
+        <v>46104</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12120,13 +12150,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12169,7 +12194,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 14886-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12183,10 +12208,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45399</v>
+        <v>46104</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12199,7 +12224,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12242,7 +12267,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12256,10 +12281,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45390</v>
+        <v>46104</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12272,7 +12297,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12315,7 +12340,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12329,10 +12354,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45134</v>
+        <v>45043</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12345,7 +12370,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12388,7 +12413,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12402,10 +12427,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45337</v>
+        <v>45751</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12418,7 +12443,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12461,7 +12486,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12475,10 +12500,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45602</v>
+        <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12490,8 +12515,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12534,7 +12564,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12548,10 +12578,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45636</v>
+        <v>44642</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12564,7 +12594,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12607,7 +12637,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12621,10 +12651,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45096</v>
+        <v>45246</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12637,7 +12667,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12680,7 +12710,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12694,10 +12724,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45134</v>
+        <v>45475</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12710,7 +12740,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12753,7 +12783,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12767,10 +12797,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46094</v>
+        <v>44714</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12783,7 +12813,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12826,7 +12856,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12840,10 +12870,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45571</v>
+        <v>46119</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12856,7 +12886,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12899,7 +12929,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 14886-2026</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12913,10 +12943,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46104</v>
+        <v>46119</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12929,7 +12959,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12972,7 +13002,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12986,10 +13016,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45589</v>
+        <v>45058</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13002,7 +13032,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>42</v>
+        <v>3.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13045,7 +13075,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13059,10 +13089,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45030</v>
+        <v>46128</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13075,7 +13105,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13118,7 +13148,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13128,14 +13158,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46104</v>
+        <v>45099</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13148,7 +13178,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13191,7 +13221,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13205,10 +13235,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46104</v>
+        <v>45917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13221,7 +13251,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13264,7 +13294,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13278,10 +13308,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46104</v>
+        <v>45337</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13294,7 +13324,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13337,7 +13367,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13351,10 +13381,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46111</v>
+        <v>44501</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13366,13 +13396,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13415,7 +13440,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13429,10 +13454,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46119</v>
+        <v>44501</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13445,7 +13470,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13488,7 +13513,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13502,10 +13527,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45672</v>
+        <v>44550</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13518,7 +13543,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13561,7 +13586,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13575,10 +13600,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46119</v>
+        <v>45307</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13591,7 +13616,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13634,7 +13659,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13648,10 +13673,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44630</v>
+        <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13664,7 +13689,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>10.6</v>
+        <v>3.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13707,7 +13732,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13721,10 +13746,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44550</v>
+        <v>45545</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13737,7 +13762,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13780,7 +13805,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13794,10 +13819,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46128</v>
+        <v>45096</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13810,7 +13835,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13853,7 +13878,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13863,14 +13888,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45419</v>
+        <v>45581</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13883,7 +13908,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13926,7 +13951,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13936,14 +13961,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44659</v>
+        <v>44980</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13956,7 +13981,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13999,7 +14024,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14013,10 +14038,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45582</v>
+        <v>45134</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14029,7 +14054,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14072,7 +14097,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14082,14 +14107,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45287</v>
+        <v>45348</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14102,7 +14127,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>11.4</v>
+        <v>5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14145,7 +14170,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14159,10 +14184,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45799</v>
+        <v>45244</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14175,7 +14200,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14218,7 +14243,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14232,10 +14257,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45001</v>
+        <v>45134</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14248,7 +14273,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14291,7 +14316,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14305,10 +14330,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44722</v>
+        <v>45946</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14321,7 +14346,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14364,7 +14389,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14378,10 +14403,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45946</v>
+        <v>46141</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14394,7 +14419,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14437,7 +14462,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14451,10 +14476,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45917</v>
+        <v>46141</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14467,7 +14492,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14510,7 +14535,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14524,10 +14549,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44973</v>
+        <v>46142</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14540,7 +14565,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14583,7 +14608,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14597,10 +14622,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45382</v>
+        <v>45337</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14613,7 +14638,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14656,7 +14681,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14670,10 +14695,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45337</v>
+        <v>45281</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14686,7 +14711,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14729,7 +14754,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14743,10 +14768,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45001</v>
+        <v>46154</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14759,7 +14784,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14802,7 +14827,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14816,10 +14841,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45639</v>
+        <v>45602</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14832,7 +14857,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14875,7 +14900,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14889,10 +14914,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45250</v>
+        <v>46154</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14905,7 +14930,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14948,7 +14973,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14962,10 +14987,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45281</v>
+        <v>45817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14978,7 +15003,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15021,7 +15046,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15031,14 +15056,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46141</v>
+        <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15050,8 +15075,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15094,7 +15124,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15108,10 +15138,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46141</v>
+        <v>45427</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15124,7 +15154,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15167,7 +15197,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15181,10 +15211,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46142</v>
+        <v>45134</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15197,7 +15227,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15240,7 +15270,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15254,10 +15284,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44642</v>
+        <v>46163</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15270,7 +15300,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15313,7 +15343,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15323,14 +15353,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45408</v>
+        <v>46007</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15343,7 +15373,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15386,7 +15416,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15400,10 +15430,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45475</v>
+        <v>44838</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15416,7 +15446,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15459,7 +15489,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15473,10 +15503,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45034</v>
+        <v>45917</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15489,7 +15519,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15532,7 +15562,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15546,10 +15576,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46154</v>
+        <v>44683</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15562,7 +15592,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15605,7 +15635,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15619,10 +15649,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46154</v>
+        <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15635,7 +15665,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15678,7 +15708,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15692,10 +15722,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44930</v>
+        <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15708,7 +15738,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15751,7 +15781,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15765,10 +15795,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46035</v>
+        <v>46171</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15780,13 +15810,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15829,7 +15854,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15843,10 +15868,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45134</v>
+        <v>45390</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15859,7 +15884,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15902,7 +15927,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15916,10 +15941,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45427</v>
+        <v>44722</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15932,7 +15957,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15975,7 +16000,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15989,10 +16014,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45817</v>
+        <v>44824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16005,7 +16030,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16048,7 +16073,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16062,10 +16087,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46163</v>
+        <v>45256</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16078,7 +16103,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16121,7 +16146,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16135,10 +16160,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44746</v>
+        <v>44973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16151,7 +16176,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16194,7 +16219,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16208,10 +16233,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45057</v>
+        <v>44852</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16224,7 +16249,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16267,7 +16292,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16281,10 +16306,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44747</v>
+        <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16297,7 +16322,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16340,7 +16365,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16354,10 +16379,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44978</v>
+        <v>46197</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16370,7 +16395,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16413,7 +16438,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16427,10 +16452,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45348</v>
+        <v>45399</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16443,7 +16468,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16486,7 +16511,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16496,14 +16521,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45034</v>
+        <v>45399</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16516,7 +16541,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16559,7 +16584,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16573,10 +16598,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46007</v>
+        <v>44784</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16589,7 +16614,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16632,7 +16657,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16646,10 +16671,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45917</v>
+        <v>44930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16662,7 +16687,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16705,7 +16730,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16719,10 +16744,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45582</v>
+        <v>45047</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16735,7 +16760,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16778,7 +16803,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16788,14 +16813,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46171</v>
+        <v>44965</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16808,7 +16833,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16851,7 +16876,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16865,10 +16890,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45043</v>
+        <v>45274</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16881,7 +16906,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16924,7 +16949,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16934,14 +16959,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45397</v>
+        <v>46203</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16953,13 +16978,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16998,31 +17018,11 @@
         <v>0</v>
       </c>
       <c r="V214" s="2" t="inlineStr"/>
-      <c r="Z214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17036,10 +17036,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45047</v>
+        <v>44645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17095,7 +17095,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17109,10 +17109,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45256</v>
+        <v>45056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17168,7 +17168,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17182,10 +17182,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45594</v>
+        <v>46209</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17241,7 +17241,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45134</v>
+        <v>45085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45211</v>
+        <v>45134</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17387,7 +17387,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17401,10 +17401,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46197</v>
+        <v>45592</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17460,7 +17460,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45246</v>
+        <v>45001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17533,7 +17533,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17547,10 +17547,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44645</v>
+        <v>45062</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17606,7 +17606,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46203</v>
+        <v>44966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17679,7 +17679,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17693,10 +17693,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45337</v>
+        <v>45034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17752,7 +17752,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17766,10 +17766,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45244</v>
+        <v>44784</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17825,7 +17825,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17839,10 +17839,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46209</v>
+        <v>44746</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17898,7 +17898,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17912,10 +17912,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45077</v>
+        <v>45001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17971,7 +17971,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17985,10 +17985,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44965</v>
+        <v>45337</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18044,7 +18044,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18058,10 +18058,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45307</v>
+        <v>46262</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18117,7 +18117,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45056</v>
+        <v>45134</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46262</v>
+        <v>46220</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18263,7 +18263,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18280,7 +18280,7 @@
         <v>46220</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18336,7 +18336,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18346,14 +18346,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45558</v>
+        <v>44659</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18423,10 +18423,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46220</v>
+        <v>44630</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.2</v>
+        <v>10.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18482,7 +18482,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18499,7 +18499,7 @@
         <v>46224</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18555,7 +18555,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18572,7 +18572,7 @@
         <v>46224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18628,7 +18628,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18642,10 +18642,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44930</v>
+        <v>45517</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18701,7 +18701,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18715,10 +18715,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44501</v>
+        <v>45594</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18774,7 +18774,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18788,10 +18788,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44501</v>
+        <v>44909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18847,7 +18847,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45294</v>
+        <v>45592</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18920,7 +18920,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18930,14 +18930,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44788</v>
+        <v>45244</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18993,7 +18993,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19003,14 +19003,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45581</v>
+        <v>45419</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19066,7 +19066,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19080,10 +19080,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44966</v>
+        <v>46239</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19149,14 +19149,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45014</v>
+        <v>46239</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19212,7 +19212,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45244</v>
+        <v>46239</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19285,7 +19285,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19299,10 +19299,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45571</v>
+        <v>44929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19358,7 +19358,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 38798-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19372,10 +19372,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45134</v>
+        <v>46286</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19445,10 +19445,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45592</v>
+        <v>44930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19504,7 +19504,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46239</v>
+        <v>45571</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19591,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46239</v>
+        <v>45077</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 38798-2026</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46286</v>
+        <v>45034</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19810,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.6</v>
+        <v>11.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>46279</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46247</v>
+        <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20032,7 +20032,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45742</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45040</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45238</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45931</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45721</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45971</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>46128</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>46191</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45040</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45589</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45244</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44795</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44753</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44585</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44497</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44628</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44753</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45592</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45057</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44683</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45399</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45399</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44929</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45786</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45345</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45238</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45884</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>46024</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44881</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45736</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45736</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45566</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>45905</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>45215</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>45446</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44784</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>46044</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44824</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45917</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45798</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45798</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>45798</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45589</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>46035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>46035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>46035</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44714</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45930</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45471</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45582</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45582</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44587</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>46070</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44980</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45938</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45943</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45811</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45328</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45456</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45419</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45958</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45728</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45062</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>46094</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>46104</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>46104</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45974</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45978</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45646</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>46111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44784</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44838</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>46119</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>46119</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45993</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45994</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>46128</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45826</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>46000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45399</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45390</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45799</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>45134</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44606</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45602</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45636</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45096</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45134</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45589</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45030</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45743</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>46141</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>46141</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44550</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>46142</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45419</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45287</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>46154</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44722</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>46154</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>46035</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45382</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45134</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45337</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45427</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45817</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>45001</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>46163</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45639</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45250</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45281</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>46007</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>46171</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44769</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44642</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45408</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45475</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>45034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46197</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>46203</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>44746</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>46209</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45348</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45582</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45043</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>45397</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46262</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>46220</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>46220</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46224</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>46224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45047</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45256</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45594</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>46239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>46239</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>46239</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>46286</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44645</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>46246</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>46279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45244</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46247</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45077</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45307</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45056</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45558</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>44930</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44501</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44501</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>44788</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45581</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44966</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45014</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45571</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45134</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45592</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45742</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45040</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45238</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45931</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45721</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45971</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>46128</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45691</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>46191</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45040</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45166</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45589</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45244</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44795</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44753</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44585</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44497</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44628</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44753</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45592</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45057</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45517</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44683</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45399</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45399</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44929</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45786</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45345</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45238</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45884</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>45099</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>46024</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44881</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45736</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45736</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45566</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>45905</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44909</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>45215</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>45446</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44784</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>46044</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44824</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45917</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45798</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45798</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>45798</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45589</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>45922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>46035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>46035</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>46035</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44714</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45930</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44587</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45471</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45582</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45582</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44587</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>46070</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44980</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45938</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45244</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45943</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45811</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45328</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45603</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45456</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45419</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45958</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45728</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45062</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45966</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>46094</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>46104</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>46104</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>46104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45974</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45978</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45646</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>46111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44784</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44838</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>46119</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>46119</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45993</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45994</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>46128</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45826</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>46000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45399</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45390</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45799</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>45134</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44606</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45602</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45636</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45096</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45134</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45571</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45589</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45030</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45743</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>46141</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45672</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>46141</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44550</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45804</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>46142</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45419</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45287</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>46154</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44722</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>46154</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>46035</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45382</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45134</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>45337</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45427</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45817</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>45001</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>46163</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45639</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45250</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45281</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>46007</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>46171</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44769</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44642</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45408</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45475</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>45034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46197</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>46203</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>44746</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>44978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>46209</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45348</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45582</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45043</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>45397</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46262</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>46220</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>46220</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46224</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>46224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45047</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45256</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45594</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>46239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>46239</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>46239</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>46286</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44645</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>46246</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>46279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45337</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45244</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46247</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45077</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45307</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45056</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45558</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>44930</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44501</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44501</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>44788</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45581</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44966</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45014</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45571</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45134</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45592</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44571</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE258"/>
+  <dimension ref="A1:AE259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14752-2025</t>
+          <t>A 32666-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1035,14 +1035,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45742</v>
+        <v>45838</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,16 +1055,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1091,255 +1091,255 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 32666-2025 artfynd.xlsx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 32666-2025 karta.png", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 32666-2025 georefererad karta.tif", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 32666-2025 FSC-klagomål.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 32666-2025 FSC-klagomål mail.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 32666-2025 tillsynsbegäran.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 32666-2025 tillsynsbegäran mail.docx", "A 32666-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17932-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45040</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17932-2023 artfynd.xlsx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17932-2023 karta.png", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17932-2023 georefererad karta.tif", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17932-2023 FSC-klagomål.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17932-2023 FSC-klagomål mail.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17932-2023 tillsynsbegäran.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17932-2023 tillsynsbegäran mail.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 14752-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45742</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Slåtterfibbla
 Svinrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 14752-2025 artfynd.xlsx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 14752-2025 karta.png", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 14752-2025 georefererad karta.tif", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14752-2025 FSC-klagomål.docx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14752-2025 FSC-klagomål mail.docx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14752-2025 tillsynsbegäran.docx", "A 14752-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14752-2025 tillsynsbegäran mail.docx", "A 14752-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 32666-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Guldlockmossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 32666-2025 artfynd.xlsx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 32666-2025 karta.png", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 32666-2025 georefererad karta.tif", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 32666-2025 FSC-klagomål.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 32666-2025 FSC-klagomål mail.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 32666-2025 tillsynsbegäran.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 32666-2025 tillsynsbegäran mail.docx", "A 32666-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 17932-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17932-2023 artfynd.xlsx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17932-2023 karta.png", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17932-2023 georefererad karta.tif", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17932-2023 FSC-klagomål.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17932-2023 FSC-klagomål mail.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17932-2023 tillsynsbegäran.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17932-2023 tillsynsbegäran mail.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55617-2023</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45238</v>
+        <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1633,42 +1633,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25575-2025</t>
+          <t>A 10515-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1678,14 +1678,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45721</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1697,13 +1697,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1736,49 +1731,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 47783-2025</t>
+          <t>A 48163-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45931</v>
+        <v>45589</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>14.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1848,143 +1843,147 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 47783-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 47783-2025 artfynd.xlsx", "A 47783-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 47783-2025 karta.png", "A 47783-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 47783-2025 georefererad karta.tif", "A 47783-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 47783-2025 FSC-klagomål.docx", "A 47783-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 47783-2025 FSC-klagomål mail.docx", "A 47783-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 47783-2025 tillsynsbegäran.docx", "A 47783-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 47783-2025 tillsynsbegäran mail.docx", "A 47783-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 10515-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45721</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 10515-2025 artfynd.xlsx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 10515-2025 karta.png", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 10515-2025 georefererad karta.tif", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 10515-2025 FSC-klagomål.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 10515-2025 FSC-klagomål mail.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 10515-2025 tillsynsbegäran.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 10515-2025 tillsynsbegäran mail.docx", "A 10515-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2005,7 +2004,7 @@
         <v>45971</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2110,7 +2109,7 @@
         <v>46128</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2215,7 +2214,7 @@
         <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2303,7 +2302,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5009-2025</t>
+          <t>A 27794-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2317,10 +2316,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45691</v>
+        <v>46191</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2333,20 +2332,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2357,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2373,474 +2372,470 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Åkerrättika</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 55617-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45238</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39899-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45166</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 56739-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 5009-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>Ljungpipare</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 27794-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Åkerrättika</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 17920-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 39899-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45166</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 48163-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45589</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56739-2023</t>
+          <t>A 25575-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45244</v>
+        <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2869,17 +2864,22 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2903,42 +2903,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 25575-2025 artfynd.xlsx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 25575-2025 karta.png", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 25575-2025 georefererad karta.tif", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 25575-2025 FSC-klagomål.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 25575-2025 FSC-klagomål mail.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 25575-2025 tillsynsbegäran.docx", "A 25575-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 25575-2025 tillsynsbegäran mail.docx", "A 25575-2025")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44795</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 29346-2022</t>
+          <t>A 54899-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44753</v>
+        <v>44886</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54899-2022</t>
+          <t>A 29346-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44886</v>
+        <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44585</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44753</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 60987-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4428,7 +4428,7 @@
         <v>44497</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10977-2022</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44628</v>
+        <v>44497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60987-2021</t>
+          <t>A 10977-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44497</v>
+        <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>44684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44693</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44579</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44753</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44635</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45592</v>
+        <v>44788</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45057</v>
+        <v>45419</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45517</v>
+        <v>45456</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5380,14 +5380,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45545</v>
+        <v>45397</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5399,8 +5399,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5439,11 +5444,31 @@
         <v>0</v>
       </c>
       <c r="V56" s="2" t="inlineStr"/>
+      <c r="Z56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5457,10 +5482,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44683</v>
+        <v>45382</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5498,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5516,7 +5541,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5555,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45187</v>
+        <v>45250</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5571,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5614,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5628,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45399</v>
+        <v>45313</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5644,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5687,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5701,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45399</v>
+        <v>45408</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5717,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5760,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16452-2025</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5749,10 +5774,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45751</v>
+        <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5790,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5833,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5822,10 +5847,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44929</v>
+        <v>45294</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5863,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5906,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5895,10 +5920,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45786</v>
+        <v>45337</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5936,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5954,7 +5979,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5968,10 +5993,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45345</v>
+        <v>45636</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +6009,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6027,7 +6052,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6041,10 +6066,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45238</v>
+        <v>45646</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6082,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6125,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6114,10 +6139,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45884</v>
+        <v>44881</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6155,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6173,7 +6198,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6183,14 +6208,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45099</v>
+        <v>45582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6228,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6271,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6260,10 +6285,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44852</v>
+        <v>45582</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6301,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6344,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6333,10 +6358,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45313</v>
+        <v>45589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6349,7 +6374,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6392,7 +6417,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6406,10 +6431,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45721</v>
+        <v>45603</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6447,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6490,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6475,14 +6500,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45565</v>
+        <v>45328</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6494,8 +6519,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6538,7 +6568,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6552,10 +6582,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46024</v>
+        <v>45811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6598,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6641,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6655,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45735</v>
+        <v>45728</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6671,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6714,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6728,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45897</v>
+        <v>46044</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,7 +6744,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6757,7 +6787,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6771,10 +6801,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45896</v>
+        <v>44769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6817,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6860,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6874,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45896</v>
+        <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6860,7 +6890,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6903,7 +6933,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6947,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45896</v>
+        <v>45826</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6963,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7006,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7020,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45896</v>
+        <v>46035</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7036,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7079,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7093,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45896</v>
+        <v>46035</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7109,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7152,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7136,10 +7166,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44881</v>
+        <v>46035</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7182,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7225,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7205,14 +7235,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45736</v>
+        <v>45896</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7225,7 +7255,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7268,7 +7298,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7282,10 +7312,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45736</v>
+        <v>45896</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7298,7 +7328,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7341,7 +7371,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7351,14 +7381,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45566</v>
+        <v>45896</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7371,7 +7401,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7414,7 +7444,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7424,14 +7454,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45902</v>
+        <v>45014</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7444,7 +7474,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7487,7 +7517,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7501,10 +7531,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45905</v>
+        <v>45896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7517,7 +7547,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7560,7 +7590,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7574,10 +7604,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44909</v>
+        <v>45896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7590,7 +7620,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7633,7 +7663,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7647,10 +7677,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45215</v>
+        <v>44623</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7663,7 +7693,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7706,7 +7736,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7720,10 +7750,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45446</v>
+        <v>45571</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7736,7 +7766,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7779,7 +7809,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7793,10 +7823,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44784</v>
+        <v>45030</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7809,7 +7839,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7852,7 +7882,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7866,10 +7896,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46044</v>
+        <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7882,7 +7912,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7925,7 +7955,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7939,10 +7969,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44824</v>
+        <v>45902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7955,7 +7985,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7998,7 +8028,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8012,10 +8042,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45728</v>
+        <v>45566</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8028,7 +8058,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8071,7 +8101,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8085,10 +8115,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45917</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8101,7 +8131,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8144,7 +8174,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8158,10 +8188,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45798</v>
+        <v>45905</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8174,7 +8204,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8217,7 +8247,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8231,10 +8261,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45917</v>
+        <v>45211</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8247,7 +8277,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8290,7 +8320,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8304,10 +8334,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45917</v>
+        <v>45582</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8320,7 +8350,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8363,7 +8393,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8377,10 +8407,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45798</v>
+        <v>45743</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8393,7 +8423,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8436,7 +8466,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8450,10 +8480,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45798</v>
+        <v>45057</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8466,7 +8496,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8509,7 +8539,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8523,10 +8553,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45799</v>
+        <v>45399</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8539,7 +8569,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8582,7 +8612,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8596,10 +8626,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45918</v>
+        <v>45238</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8612,7 +8642,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8655,7 +8685,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8672,7 +8702,7 @@
         <v>45589</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8685,7 +8715,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>42</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8728,7 +8758,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8742,10 +8772,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45922</v>
+        <v>45747</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8758,7 +8788,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8801,7 +8831,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8815,10 +8845,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46035</v>
+        <v>45558</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8831,7 +8861,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8874,7 +8904,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8888,10 +8918,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46035</v>
+        <v>45917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8904,7 +8934,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8947,7 +8977,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8961,10 +8991,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46035</v>
+        <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8977,7 +9007,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9020,7 +9050,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9034,10 +9064,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44714</v>
+        <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9050,7 +9080,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9093,7 +9123,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9107,10 +9137,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45085</v>
+        <v>45917</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9123,7 +9153,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9166,7 +9196,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9180,10 +9210,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45930</v>
+        <v>45922</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9196,7 +9226,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9239,7 +9269,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9253,10 +9283,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44623</v>
+        <v>45804</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9269,7 +9299,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9312,7 +9342,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9322,14 +9352,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44587</v>
+        <v>45287</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9342,7 +9372,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9385,7 +9415,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9395,14 +9425,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45471</v>
+        <v>45884</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9415,7 +9445,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9458,7 +9488,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9472,10 +9502,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45582</v>
+        <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9488,7 +9518,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9531,7 +9561,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9545,10 +9575,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45582</v>
+        <v>44587</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9561,7 +9591,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9604,7 +9634,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9614,14 +9644,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44587</v>
+        <v>45471</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9634,7 +9664,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9677,7 +9707,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9691,10 +9721,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45337</v>
+        <v>44587</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9707,7 +9737,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9750,7 +9780,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9760,14 +9790,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46070</v>
+        <v>45057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9779,13 +9809,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9828,7 +9853,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9842,10 +9867,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44980</v>
+        <v>45938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9858,7 +9883,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9901,7 +9926,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9911,14 +9936,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45938</v>
+        <v>46070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9930,8 +9955,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9974,7 +10004,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9988,10 +10018,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45244</v>
+        <v>45639</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10004,7 +10034,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10064,7 +10094,7 @@
         <v>45943</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10120,7 +10150,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 2146-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10134,10 +10164,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45811</v>
+        <v>45672</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10150,7 +10180,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10193,7 +10223,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 46523-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10203,14 +10233,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45328</v>
+        <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10222,13 +10252,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10271,7 +10296,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10285,10 +10310,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45603</v>
+        <v>44747</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10301,7 +10326,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10344,7 +10369,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10354,14 +10379,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45456</v>
+        <v>45958</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10374,7 +10399,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10417,7 +10442,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10431,10 +10456,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45419</v>
+        <v>45964</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10447,7 +10472,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10490,7 +10515,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10504,10 +10529,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45958</v>
+        <v>45965</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10520,7 +10545,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>13.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10563,7 +10588,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10577,10 +10602,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45728</v>
+        <v>46094</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10593,7 +10618,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10636,7 +10661,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10650,10 +10675,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45964</v>
+        <v>44978</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10666,7 +10691,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10709,7 +10734,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 54863-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10723,10 +10748,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10739,7 +10764,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>13.4</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10782,7 +10807,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 56261-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10792,14 +10817,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45062</v>
+        <v>45974</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10812,7 +10837,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10855,7 +10880,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54863-2025</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10869,10 +10894,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45966</v>
+        <v>46104</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10885,7 +10910,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10928,7 +10953,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10942,10 +10967,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10958,7 +10983,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11018,7 +11043,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11074,7 +11099,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11091,7 +11116,7 @@
         <v>46104</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11104,7 +11129,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11147,7 +11172,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11161,10 +11186,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46104</v>
+        <v>45978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11177,7 +11202,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11220,7 +11245,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11234,10 +11259,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11249,8 +11274,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11293,7 +11323,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56261-2025</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11303,14 +11333,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45974</v>
+        <v>46119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11323,7 +11353,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11366,7 +11396,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11380,10 +11410,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45058</v>
+        <v>46119</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11439,7 +11469,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11453,10 +11483,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45978</v>
+        <v>45043</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11469,7 +11499,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11512,7 +11542,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 16452-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11526,10 +11556,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45646</v>
+        <v>45751</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11542,7 +11572,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11585,7 +11615,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11599,10 +11629,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46111</v>
+        <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11614,13 +11644,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11663,7 +11688,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11677,10 +11702,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45274</v>
+        <v>44642</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11693,7 +11718,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11736,7 +11761,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11750,10 +11775,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44784</v>
+        <v>45246</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11766,7 +11791,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11809,7 +11834,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11823,10 +11848,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44838</v>
+        <v>45475</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11839,7 +11864,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11882,7 +11907,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11896,10 +11921,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46119</v>
+        <v>45994</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11912,7 +11937,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11955,7 +11980,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11969,10 +11994,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46119</v>
+        <v>45993</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11985,7 +12010,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12028,7 +12053,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12042,10 +12067,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12058,7 +12083,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12101,7 +12126,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12115,10 +12140,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45994</v>
+        <v>44714</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12131,7 +12156,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12174,7 +12199,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12188,10 +12213,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12204,7 +12229,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12247,7 +12272,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12261,10 +12286,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46128</v>
+        <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12277,7 +12302,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12320,7 +12345,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12334,10 +12359,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45826</v>
+        <v>45058</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12350,7 +12375,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12393,7 +12418,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12403,14 +12428,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46000</v>
+        <v>45099</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12423,7 +12448,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12466,7 +12491,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12480,10 +12505,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45399</v>
+        <v>46024</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12496,7 +12521,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12539,7 +12564,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12553,10 +12578,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45390</v>
+        <v>45799</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12569,7 +12594,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12612,7 +12637,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12626,10 +12651,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45799</v>
+        <v>45337</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12642,7 +12667,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12685,7 +12710,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12699,10 +12724,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45134</v>
+        <v>44501</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12715,7 +12740,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12758,7 +12783,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12772,10 +12797,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45946</v>
+        <v>44501</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12788,7 +12813,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12831,7 +12856,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12845,10 +12870,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45337</v>
+        <v>44550</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12861,7 +12886,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>12.8</v>
+        <v>3.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12904,7 +12929,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12918,10 +12943,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44606</v>
+        <v>45307</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12934,7 +12959,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12977,7 +13002,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12991,10 +13016,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45602</v>
+        <v>45545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13007,7 +13032,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13050,7 +13075,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13064,10 +13089,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45917</v>
+        <v>45096</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13080,7 +13105,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13123,7 +13148,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13137,10 +13162,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45636</v>
+        <v>45581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13153,7 +13178,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13196,7 +13221,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13210,10 +13235,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45096</v>
+        <v>44980</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13226,7 +13251,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13269,7 +13294,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13286,7 +13311,7 @@
         <v>45134</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13299,7 +13324,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13342,7 +13367,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13356,10 +13381,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45571</v>
+        <v>45348</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13372,7 +13397,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13415,7 +13440,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13429,10 +13454,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45589</v>
+        <v>45244</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13445,7 +13470,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>42</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13488,7 +13513,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13502,10 +13527,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45030</v>
+        <v>45134</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13518,7 +13543,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13561,7 +13586,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13575,10 +13600,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45743</v>
+        <v>45946</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13591,7 +13616,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13634,7 +13659,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13648,10 +13673,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45747</v>
+        <v>46141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13664,7 +13689,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13707,7 +13732,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13724,7 +13749,7 @@
         <v>46141</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13737,7 +13762,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13780,7 +13805,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 2146-2025</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13794,10 +13819,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45672</v>
+        <v>46142</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13810,7 +13835,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13853,7 +13878,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13867,10 +13892,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13883,7 +13908,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13926,7 +13951,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13940,10 +13965,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44630</v>
+        <v>46154</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13956,7 +13981,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13999,7 +14024,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14013,10 +14038,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44550</v>
+        <v>45817</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14029,7 +14054,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14072,7 +14097,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14082,14 +14107,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45804</v>
+        <v>46035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14101,8 +14126,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14145,7 +14175,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14159,10 +14189,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46142</v>
+        <v>45427</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14175,7 +14205,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14218,7 +14248,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14228,14 +14258,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45419</v>
+        <v>45134</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14248,7 +14278,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14291,7 +14321,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14301,14 +14331,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44659</v>
+        <v>45337</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14321,7 +14351,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.2</v>
+        <v>12.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14364,7 +14394,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 46523-2024</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14378,10 +14408,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45582</v>
+        <v>46163</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14394,7 +14424,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14437,7 +14467,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14447,14 +14477,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45287</v>
+        <v>45281</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14467,7 +14497,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>11.4</v>
+        <v>7.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14510,7 +14540,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14524,10 +14554,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45001</v>
+        <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14540,7 +14570,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14583,7 +14613,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14597,10 +14627,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46154</v>
+        <v>46007</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14613,7 +14643,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14656,7 +14686,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14670,10 +14700,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44722</v>
+        <v>45917</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14686,7 +14716,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14729,7 +14759,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14739,14 +14769,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14759,7 +14789,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14802,7 +14832,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14816,10 +14846,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44973</v>
+        <v>44838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14832,7 +14862,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14875,7 +14905,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14885,14 +14915,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46035</v>
+        <v>44683</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14904,13 +14934,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14953,7 +14978,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14967,10 +14992,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45382</v>
+        <v>45244</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15026,7 +15051,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15040,10 +15065,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45134</v>
+        <v>45187</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15056,7 +15081,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15099,7 +15124,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15113,10 +15138,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45337</v>
+        <v>45390</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15129,7 +15154,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15172,7 +15197,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15186,10 +15211,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45427</v>
+        <v>44722</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15202,7 +15227,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15245,7 +15270,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15259,10 +15284,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45817</v>
+        <v>44824</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15275,7 +15300,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15318,7 +15343,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15332,10 +15357,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45001</v>
+        <v>45256</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15348,7 +15373,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15391,7 +15416,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15405,10 +15430,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46163</v>
+        <v>44973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15464,7 +15489,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15478,10 +15503,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45639</v>
+        <v>46197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15494,7 +15519,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15537,7 +15562,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15551,10 +15576,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45250</v>
+        <v>44852</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15567,7 +15592,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15610,7 +15635,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15624,10 +15649,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45281</v>
+        <v>46203</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15640,7 +15665,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15683,7 +15708,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15697,10 +15722,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46007</v>
+        <v>45345</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15713,7 +15738,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15756,7 +15781,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15770,10 +15795,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45917</v>
+        <v>45399</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15786,7 +15811,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15829,7 +15854,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15843,10 +15868,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46171</v>
+        <v>45399</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15859,7 +15884,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15902,7 +15927,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15916,10 +15941,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44769</v>
+        <v>46209</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15932,7 +15957,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15975,7 +16000,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15989,10 +16014,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44642</v>
+        <v>44784</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16005,7 +16030,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16048,7 +16073,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16058,14 +16083,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45408</v>
+        <v>44930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16078,7 +16103,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16121,7 +16146,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16135,10 +16160,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45475</v>
+        <v>45047</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16151,7 +16176,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16194,7 +16219,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16208,10 +16233,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45034</v>
+        <v>44965</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16224,7 +16249,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16267,7 +16292,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16281,10 +16306,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46197</v>
+        <v>45274</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16297,7 +16322,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16340,7 +16365,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16354,10 +16379,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44930</v>
+        <v>44645</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16370,7 +16395,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16413,7 +16438,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16427,10 +16452,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46203</v>
+        <v>46262</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16443,7 +16468,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16486,7 +16511,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16500,10 +16525,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44746</v>
+        <v>45056</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16516,7 +16541,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16559,7 +16584,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16573,10 +16598,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45057</v>
+        <v>46220</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16589,7 +16614,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16632,7 +16657,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16646,10 +16671,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44747</v>
+        <v>45085</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16662,7 +16687,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16705,7 +16730,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16719,10 +16744,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44978</v>
+        <v>45134</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16735,7 +16760,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16778,7 +16803,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16792,10 +16817,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46209</v>
+        <v>45592</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16808,7 +16833,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16851,7 +16876,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16865,10 +16890,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45348</v>
+        <v>45001</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16881,7 +16906,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16924,7 +16949,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16938,10 +16963,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45034</v>
+        <v>45062</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16954,7 +16979,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16997,7 +17022,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17011,10 +17036,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45582</v>
+        <v>46220</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17027,7 +17052,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17070,7 +17095,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17084,10 +17109,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45043</v>
+        <v>46224</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17100,7 +17125,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17143,7 +17168,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17153,14 +17178,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45397</v>
+        <v>46224</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17172,13 +17197,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17217,31 +17237,11 @@
         <v>0</v>
       </c>
       <c r="V217" s="2" t="inlineStr"/>
-      <c r="Z217">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA217">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB217">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC217">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD217">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46262</v>
+        <v>44966</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46220</v>
+        <v>45034</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17387,7 +17387,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17401,10 +17401,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46220</v>
+        <v>44784</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17460,7 +17460,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46224</v>
+        <v>44746</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17533,7 +17533,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17547,10 +17547,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46224</v>
+        <v>45001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17606,7 +17606,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45047</v>
+        <v>45337</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17679,7 +17679,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17693,10 +17693,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45256</v>
+        <v>45134</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17752,7 +17752,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17762,14 +17762,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45594</v>
+        <v>44659</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17825,7 +17825,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17839,10 +17839,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45134</v>
+        <v>44630</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>10.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17898,7 +17898,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17912,10 +17912,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45211</v>
+        <v>46239</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.9</v>
+        <v>11.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17971,7 +17971,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17988,7 +17988,7 @@
         <v>46239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18044,7 +18044,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18061,7 +18061,7 @@
         <v>46239</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18117,7 +18117,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46239</v>
+        <v>45517</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 38798-2026</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46286</v>
+        <v>45594</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18263,7 +18263,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45246</v>
+        <v>44909</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18336,7 +18336,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 38798-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18350,10 +18350,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44645</v>
+        <v>46286</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18409,7 +18409,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18423,10 +18423,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46246</v>
+        <v>45592</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18482,7 +18482,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18496,10 +18496,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46279</v>
+        <v>46246</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18555,7 +18555,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18569,10 +18569,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45337</v>
+        <v>45244</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18628,7 +18628,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18638,14 +18638,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45244</v>
+        <v>45419</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18701,7 +18701,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18715,10 +18715,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46247</v>
+        <v>44929</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>11.1</v>
+        <v>0.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18774,7 +18774,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18788,10 +18788,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45077</v>
+        <v>46247</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18847,7 +18847,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44965</v>
+        <v>44930</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18920,7 +18920,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18934,10 +18934,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45307</v>
+        <v>46279</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19007,10 +19007,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45056</v>
+        <v>45571</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19066,7 +19066,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19080,10 +19080,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45558</v>
+        <v>45077</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19153,10 +19153,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44930</v>
+        <v>45034</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19212,7 +19212,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44501</v>
+        <v>45786</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19285,7 +19285,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19299,10 +19299,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44501</v>
+        <v>45721</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19358,7 +19358,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19372,10 +19372,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45294</v>
+        <v>45565</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19445,10 +19445,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44788</v>
+        <v>45736</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19504,7 +19504,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45581</v>
+        <v>45736</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19591,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44966</v>
+        <v>45735</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 41287-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19660,14 +19660,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45014</v>
+        <v>46300</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19733,14 +19733,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45244</v>
+        <v>45728</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19810,10 +19810,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45571</v>
+        <v>45798</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45134</v>
+        <v>45798</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45592</v>
+        <v>45798</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20015,24 +20015,24 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>S 130-2022</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44571</v>
+        <v>45799</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20088,148 +20088,221 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
+          <t>S 130-2022</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Åtgärd i nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E257" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>0</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="n">
+        <v>0</v>
+      </c>
+      <c r="V257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258" ht="15" customHeight="1">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>S 1659-2024</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D257" s="1" t="n">
+      <c r="D258" s="1" t="n">
         <v>45432</v>
       </c>
-      <c r="E257" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I257" t="n">
+      <c r="E258" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
         <v>2.5</v>
       </c>
-      <c r="J257" t="n">
-        <v>0</v>
-      </c>
-      <c r="K257" t="n">
-        <v>0</v>
-      </c>
-      <c r="L257" t="n">
-        <v>0</v>
-      </c>
-      <c r="M257" t="n">
-        <v>0</v>
-      </c>
-      <c r="N257" t="n">
-        <v>0</v>
-      </c>
-      <c r="O257" t="n">
-        <v>0</v>
-      </c>
-      <c r="P257" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
-      <c r="R257" t="n">
-        <v>0</v>
-      </c>
-      <c r="S257" t="n">
-        <v>0</v>
-      </c>
-      <c r="T257" t="n">
-        <v>0</v>
-      </c>
-      <c r="U257" t="n">
-        <v>0</v>
-      </c>
-      <c r="V257" s="2" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0</v>
+      </c>
+      <c r="U258" t="n">
+        <v>0</v>
+      </c>
+      <c r="V258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>S 2050-2025</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D258" s="1" t="n">
+      <c r="D259" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E258" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I258" t="n">
+      <c r="E259" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
         <v>2.2</v>
       </c>
-      <c r="J258" t="n">
-        <v>0</v>
-      </c>
-      <c r="K258" t="n">
-        <v>0</v>
-      </c>
-      <c r="L258" t="n">
-        <v>0</v>
-      </c>
-      <c r="M258" t="n">
-        <v>0</v>
-      </c>
-      <c r="N258" t="n">
-        <v>0</v>
-      </c>
-      <c r="O258" t="n">
-        <v>0</v>
-      </c>
-      <c r="P258" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0</v>
-      </c>
-      <c r="S258" t="n">
-        <v>0</v>
-      </c>
-      <c r="T258" t="n">
-        <v>0</v>
-      </c>
-      <c r="U258" t="n">
-        <v>0</v>
-      </c>
-      <c r="V258" s="2" t="inlineStr"/>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>0</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="n">
+        <v>0</v>
+      </c>
+      <c r="V259" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32666-2025</t>
+          <t>A 17932-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1035,14 +1035,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45838</v>
+        <v>45040</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1088,258 +1088,258 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17932-2023 artfynd.xlsx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17932-2023 karta.png", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17932-2023 georefererad karta.tif", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17932-2023 FSC-klagomål.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17932-2023 FSC-klagomål mail.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17932-2023 tillsynsbegäran.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17932-2023 tillsynsbegäran mail.docx", "A 17932-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 14752-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45742</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 14752-2025 artfynd.xlsx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 14752-2025 karta.png", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 14752-2025 georefererad karta.tif", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14752-2025 FSC-klagomål.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14752-2025 FSC-klagomål mail.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14752-2025 tillsynsbegäran.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14752-2025 tillsynsbegäran mail.docx", "A 14752-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32666-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Guldlockmossa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 32666-2025 artfynd.xlsx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 32666-2025 karta.png", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 32666-2025 georefererad karta.tif", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 32666-2025 FSC-klagomål.docx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 32666-2025 FSC-klagomål mail.docx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 32666-2025 tillsynsbegäran.docx", "A 32666-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 32666-2025 tillsynsbegäran mail.docx", "A 32666-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17932-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17932-2023 artfynd.xlsx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17932-2023 karta.png", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17932-2023 georefererad karta.tif", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17932-2023 FSC-klagomål.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17932-2023 FSC-klagomål mail.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17932-2023 tillsynsbegäran.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17932-2023 tillsynsbegäran mail.docx", "A 17932-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 14752-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45742</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Slåtterfibbla
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 14752-2025 artfynd.xlsx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 14752-2025 karta.png", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 14752-2025 georefererad karta.tif", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14752-2025 FSC-klagomål.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14752-2025 FSC-klagomål mail.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14752-2025 tillsynsbegäran.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14752-2025 tillsynsbegäran mail.docx", "A 14752-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 55617-2023</t>
+          <t>A 17920-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45238</v>
+        <v>45040</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1633,35 +1633,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
         <v/>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
         <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45721</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>45931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18733-2026</t>
+          <t>A 11709-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46128</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2058,35 +2058,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
         <v/>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
         <v>45971</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11709-2024</t>
+          <t>A 48163-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45589</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>14.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2268,42 +2268,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 11709-2024 artfynd.xlsx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 11709-2024 karta.png", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 11709-2024 georefererad karta.tif", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 11709-2024 FSC-klagomål.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 11709-2024 FSC-klagomål mail.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 11709-2024 tillsynsbegäran.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 11709-2024 tillsynsbegäran mail.docx", "A 11709-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27794-2026</t>
+          <t>A 55617-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2317,10 +2321,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46191</v>
+        <v>45238</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2333,10 +2337,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2345,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2357,10 +2361,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2373,575 +2377,571 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 55617-2023 artfynd.xlsx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 55617-2023 karta.png", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 55617-2023 georefererad karta.tif", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 55617-2023 FSC-klagomål.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 55617-2023 FSC-klagomål mail.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 55617-2023 tillsynsbegäran.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 55617-2023 tillsynsbegäran mail.docx", "A 55617-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 27794-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Åkerrättika</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 27794-2026 artfynd.xlsx", "A 27794-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 27794-2026 karta.png", "A 27794-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 27794-2026 georefererad karta.tif", "A 27794-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 27794-2026 FSC-klagomål.docx", "A 27794-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 27794-2026 FSC-klagomål mail.docx", "A 27794-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 27794-2026 tillsynsbegäran.docx", "A 27794-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 27794-2026 tillsynsbegäran mail.docx", "A 27794-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39899-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45166</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 18733-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 18733-2026 artfynd.xlsx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 18733-2026 karta.png", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 18733-2026 georefererad karta.tif", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 18733-2026 FSC-klagomål.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 18733-2026 FSC-klagomål mail.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 18733-2026 tillsynsbegäran.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 18733-2026 tillsynsbegäran mail.docx", "A 18733-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 56739-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 5009-2025</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45691</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VÄNERSBORG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>1.8</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Ljungpipare</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 5009-2025 artfynd.xlsx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 5009-2025 karta.png", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 5009-2025 georefererad karta.tif", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 5009-2025 FSC-klagomål.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 5009-2025 FSC-klagomål mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 5009-2025 tillsynsbegäran.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 5009-2025 tillsynsbegäran mail.docx", "A 5009-2025")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 5009-2025 prioriterade fågelarter.docx", "A 5009-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 17920-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45040</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 17920-2023 artfynd.xlsx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 17920-2023 karta.png", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 17920-2023 georefererad karta.tif", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 17920-2023 FSC-klagomål.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 17920-2023 FSC-klagomål mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 17920-2023 tillsynsbegäran.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 17920-2023 tillsynsbegäran mail.docx", "A 17920-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 39899-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45166</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 39899-2023 artfynd.xlsx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 39899-2023 karta.png", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 39899-2023 georefererad karta.tif", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 39899-2023 FSC-klagomål.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 39899-2023 FSC-klagomål mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 39899-2023 tillsynsbegäran.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 39899-2023 tillsynsbegäran mail.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 39899-2023 prioriterade fågelarter.docx", "A 39899-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 48163-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45589</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 48163-2024 artfynd.xlsx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 48163-2024 karta.png", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 48163-2024 georefererad karta.tif", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 48163-2024 FSC-klagomål.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 48163-2024 FSC-klagomål mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 48163-2024 tillsynsbegäran.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 48163-2024 tillsynsbegäran mail.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/fåglar/A 48163-2024 prioriterade fågelarter.docx", "A 48163-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 56739-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VÄNERSBORG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/artfynd/A 56739-2023 artfynd.xlsx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor/A 56739-2023 karta.png", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/kartor_geotiff/A 56739-2023 georefererad karta.tif", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 56739-2023 FSC-klagomål.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 56739-2023 FSC-klagomål mail.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 56739-2023 tillsynsbegäran.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 56739-2023 tillsynsbegäran mail.docx", "A 56739-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44795</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44753</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44585</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44642</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29371-2022</t>
+          <t>A 9732-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44753</v>
+        <v>44978</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4362,13 +4362,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60987-2021</t>
+          <t>A 29371-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44497</v>
+        <v>44753</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4440,8 +4435,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61042-2021</t>
+          <t>A 11979-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44497</v>
+        <v>44635</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10977-2022</t>
+          <t>A 60987-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44628</v>
+        <v>44497</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19559-2022</t>
+          <t>A 61042-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44693</v>
+        <v>44497</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18157-2022</t>
+          <t>A 29345-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44684</v>
+        <v>44753</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2377-2022</t>
+          <t>A 10977-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44579</v>
+        <v>44628</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 13923-2022</t>
+          <t>A 18157-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44650</v>
+        <v>44684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4878,13 +4878,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4927,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29373-2022</t>
+          <t>A 19559-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4941,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44753</v>
+        <v>44693</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4956,13 +4951,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5005,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11979-2022</t>
+          <t>A 2377-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5019,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44635</v>
+        <v>44579</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5035,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5078,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29345-2022</t>
+          <t>A 13923-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5088,14 +5078,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44753</v>
+        <v>44650</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5107,8 +5097,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5151,7 +5146,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48494-2024</t>
+          <t>A 33476-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5161,14 +5156,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45592</v>
+        <v>44788</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5181,7 +5176,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5224,7 +5219,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33033-2024</t>
+          <t>A 17077-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45517</v>
+        <v>45034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5249,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5297,7 +5292,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20584-2023</t>
+          <t>A 29373-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5311,10 +5306,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45057</v>
+        <v>44753</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5326,8 +5321,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>12.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5370,7 +5370,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38360-2024</t>
+          <t>A 18715-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45545</v>
+        <v>45043</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5460,7 +5460,7 @@
         <v>45751</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17985-2022</t>
+          <t>A 12823-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44683</v>
+        <v>44642</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 369-2023</t>
+          <t>A 57699-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44929</v>
+        <v>45246</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43817-2023</t>
+          <t>A 27815-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>45475</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5735,7 +5735,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15099-2024</t>
+          <t>A 22631-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45399</v>
+        <v>44714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15107-2024</t>
+          <t>A 17861-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5818,14 +5818,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45399</v>
+        <v>45419</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55618-2023</t>
+          <t>A 31051-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45238</v>
+        <v>44769</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7420-2024</t>
+          <t>A 22326-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45345</v>
+        <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2556-2024</t>
+          <t>A 24107-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6037,14 +6037,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45313</v>
+        <v>45456</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28263-2023</t>
+          <t>A 10525-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6110,14 +6110,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45099</v>
+        <v>45721</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47630-2022</t>
+          <t>A 42605-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44852</v>
+        <v>45565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6246,7 +6246,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54006-2022</t>
+          <t>A 20793-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44881</v>
+        <v>45058</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6319,7 +6319,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61409-2022</t>
+          <t>A 13666-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44909</v>
+        <v>45736</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6392,7 +6392,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42698-2024</t>
+          <t>A 13674-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6402,14 +6402,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45566</v>
+        <v>45736</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22402-2024</t>
+          <t>A 14798-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6475,14 +6475,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45446</v>
+        <v>45397</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6494,8 +6494,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6534,11 +6539,31 @@
         <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr"/>
+      <c r="Z71">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AA71">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AB71">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AC71">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
+      <c r="AD71">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40721-2022</t>
+          <t>A 12610-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6552,10 +6577,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44824</v>
+        <v>45382</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6568,7 +6593,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6611,7 +6636,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32838-2022</t>
+          <t>A 13196-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6625,10 +6650,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44784</v>
+        <v>45735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6641,7 +6666,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6684,7 +6709,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24549-2025</t>
+          <t>A 58292-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6698,10 +6723,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45798</v>
+        <v>45250</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6714,7 +6739,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6757,7 +6782,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24567-2025</t>
+          <t>A 28263-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6767,14 +6792,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45798</v>
+        <v>45099</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6787,7 +6812,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6830,7 +6855,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 146-2026</t>
+          <t>A 40553-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6844,10 +6869,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46024</v>
+        <v>45896</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6860,7 +6885,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6903,7 +6928,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24894-2025</t>
+          <t>A 40538-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6917,10 +6942,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45799</v>
+        <v>45896</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6933,7 +6958,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6976,7 +7001,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38614-2025</t>
+          <t>A 40539-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6990,10 +7015,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7006,7 +7031,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7049,7 +7074,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22631-2022</t>
+          <t>A 40544-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7063,10 +7088,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44714</v>
+        <v>45896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7079,7 +7104,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7122,7 +7147,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24940-2023</t>
+          <t>A 40550-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7136,10 +7161,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45085</v>
+        <v>45896</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7152,7 +7177,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7195,7 +7220,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10444-2022</t>
+          <t>A 11883-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7205,14 +7230,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44623</v>
+        <v>45728</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7268,7 +7293,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48034-2024</t>
+          <t>A 2556-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7282,10 +7307,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45589</v>
+        <v>45313</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7298,7 +7323,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7341,7 +7366,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46514-2024</t>
+          <t>A 40844-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7355,10 +7380,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45582</v>
+        <v>45897</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7371,7 +7396,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7414,7 +7439,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46521-2024</t>
+          <t>A 24549-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7428,10 +7453,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45582</v>
+        <v>45798</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7444,7 +7469,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7487,7 +7512,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27031-2025</t>
+          <t>A 24567-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7501,10 +7526,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45811</v>
+        <v>45798</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7517,7 +7542,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7560,7 +7585,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4736-2024</t>
+          <t>A 41795-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7570,14 +7595,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45328</v>
+        <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7589,13 +7614,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7638,7 +7658,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51480-2024</t>
+          <t>A 24560-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7652,10 +7672,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45603</v>
+        <v>45798</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7668,7 +7688,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7711,7 +7731,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50002-2023</t>
+          <t>A 16551-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7721,14 +7741,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45215</v>
+        <v>45408</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7741,7 +7761,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7784,7 +7804,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4195-2026</t>
+          <t>A 24894-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7798,10 +7818,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46044</v>
+        <v>45799</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7814,7 +7834,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7857,7 +7877,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6167-2024</t>
+          <t>A 42566-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7871,10 +7891,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45337</v>
+        <v>45905</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7887,7 +7907,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7930,7 +7950,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11817-2025</t>
+          <t>A 22402-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7944,10 +7964,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45728</v>
+        <v>45446</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7960,7 +7980,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8003,7 +8023,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1930-2026</t>
+          <t>A 46514-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8017,10 +8037,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46035</v>
+        <v>45582</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8076,7 +8096,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40844-2025</t>
+          <t>A 46521-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8090,10 +8110,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45897</v>
+        <v>45582</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8106,7 +8126,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8149,7 +8169,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40544-2025</t>
+          <t>A 48034-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8163,10 +8183,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45896</v>
+        <v>45589</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8179,7 +8199,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8222,7 +8242,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40550-2025</t>
+          <t>A 6179-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8236,10 +8256,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45896</v>
+        <v>45337</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8252,7 +8272,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8295,7 +8315,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40553-2025</t>
+          <t>A 61825-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8309,10 +8329,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45896</v>
+        <v>44501</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8325,7 +8345,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8368,7 +8388,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1925-2026</t>
+          <t>A 61826-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8382,10 +8402,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46035</v>
+        <v>44501</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8398,7 +8418,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8441,7 +8461,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1933-2026</t>
+          <t>A 51480-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8455,10 +8475,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46035</v>
+        <v>45603</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8471,7 +8491,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8514,7 +8534,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40538-2025</t>
+          <t>A 4736-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8524,14 +8544,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45896</v>
+        <v>45328</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8543,8 +8563,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8587,7 +8612,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40539-2025</t>
+          <t>A 120-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8601,10 +8626,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45896</v>
+        <v>45294</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8617,7 +8642,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8660,7 +8685,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 9169-2023</t>
+          <t>A 73226-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8674,10 +8699,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44980</v>
+        <v>44550</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8690,7 +8715,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8733,7 +8758,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56734-2023</t>
+          <t>A 1749-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8747,10 +8772,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45244</v>
+        <v>45307</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8763,7 +8788,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8806,7 +8831,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 41795-2025</t>
+          <t>A 44589-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8820,10 +8845,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45902</v>
+        <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8836,7 +8861,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8879,7 +8904,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42566-2025</t>
+          <t>A 27031-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8893,10 +8918,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45905</v>
+        <v>45811</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8909,7 +8934,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8952,7 +8977,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24107-2024</t>
+          <t>A 44841-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8962,14 +8987,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45456</v>
+        <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8982,7 +9007,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9025,7 +9050,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9289-2026</t>
+          <t>A 44597-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9035,14 +9060,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46070</v>
+        <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9054,13 +9079,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9103,7 +9123,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17861-2024</t>
+          <t>A 44584-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9117,10 +9137,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45419</v>
+        <v>45917</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9133,7 +9153,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9176,7 +9196,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44584-2025</t>
+          <t>A 45537-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9190,10 +9210,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45917</v>
+        <v>45922</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9206,7 +9226,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9249,7 +9269,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44589-2025</t>
+          <t>A 11817-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9263,10 +9283,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45917</v>
+        <v>45728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9279,7 +9299,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9322,7 +9342,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44597-2025</t>
+          <t>A 38360-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9336,10 +9356,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45917</v>
+        <v>45545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9352,7 +9372,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9395,7 +9415,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44841-2025</t>
+          <t>A 27181-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9409,10 +9429,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45918</v>
+        <v>45096</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9425,7 +9445,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9468,7 +9488,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 45537-2025</t>
+          <t>A 46320-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9482,10 +9502,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45922</v>
+        <v>45581</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9498,7 +9518,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9541,7 +9561,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29840-2025</t>
+          <t>A 9169-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9555,10 +9575,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45826</v>
+        <v>44980</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9571,7 +9591,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9614,7 +9634,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21140-2023</t>
+          <t>A 29840-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9628,10 +9648,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45062</v>
+        <v>45826</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9644,7 +9664,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9687,7 +9707,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47342-2025</t>
+          <t>A 6167-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9701,10 +9721,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45930</v>
+        <v>45337</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9717,7 +9737,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9760,7 +9780,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3884-2022</t>
+          <t>A 33912-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9774,10 +9794,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44587</v>
+        <v>45134</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9790,7 +9810,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9833,7 +9853,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27232-2024</t>
+          <t>A 47342-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9843,14 +9863,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45471</v>
+        <v>45930</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9863,7 +9883,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9906,7 +9926,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3880-2022</t>
+          <t>A 7640-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9920,10 +9940,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44587</v>
+        <v>45348</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9936,7 +9956,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9979,7 +9999,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 13491-2026</t>
+          <t>A 3880-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9993,10 +10013,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46094</v>
+        <v>44587</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10052,7 +10072,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14886-2026</t>
+          <t>A 27232-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10062,14 +10082,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46104</v>
+        <v>45471</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10082,7 +10102,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10125,7 +10145,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 49201-2025</t>
+          <t>A 56734-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10139,10 +10159,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45938</v>
+        <v>45244</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10155,7 +10175,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10198,7 +10218,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20793-2023</t>
+          <t>A 3884-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10212,10 +10232,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45058</v>
+        <v>44587</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10228,7 +10248,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10271,7 +10291,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61566-2024</t>
+          <t>A 33942-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10285,10 +10305,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45646</v>
+        <v>45134</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10344,7 +10364,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14853-2026</t>
+          <t>A 49201-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10358,10 +10378,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46104</v>
+        <v>45938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10374,7 +10394,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10417,7 +10437,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14873-2026</t>
+          <t>A 58972-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10431,10 +10451,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46104</v>
+        <v>45636</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10447,7 +10467,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10490,7 +10510,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50145-2025</t>
+          <t>A 61566-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10504,10 +10524,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45943</v>
+        <v>45646</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10520,7 +10540,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10563,7 +10583,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14875-2026</t>
+          <t>A 54006-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10577,10 +10597,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46104</v>
+        <v>44881</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10593,7 +10613,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10636,7 +10656,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7605-2022</t>
+          <t>A 50145-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10650,10 +10670,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44606</v>
+        <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10666,7 +10686,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>7.1</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10709,7 +10729,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63509-2023</t>
+          <t>A 7605-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10723,10 +10743,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45274</v>
+        <v>44606</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10739,7 +10759,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10782,7 +10802,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32843-2022</t>
+          <t>A 14722-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10792,14 +10812,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44784</v>
+        <v>45014</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10812,7 +10832,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10855,7 +10875,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43987-2022</t>
+          <t>A 53296-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10869,10 +10889,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44838</v>
+        <v>45958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10885,7 +10905,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10928,7 +10948,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16192-2026</t>
+          <t>A 10444-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10942,10 +10962,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46111</v>
+        <v>44623</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10957,13 +10977,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11006,7 +11021,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15067-2025</t>
+          <t>A 43799-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11020,10 +11035,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45743</v>
+        <v>45571</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11036,7 +11051,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11079,7 +11094,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15458-2025</t>
+          <t>A 6140-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11093,10 +11108,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45747</v>
+        <v>45337</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11109,7 +11124,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.2</v>
+        <v>12.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11152,7 +11167,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26025-2025</t>
+          <t>A 54244-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11166,10 +11181,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45804</v>
+        <v>45964</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11182,7 +11197,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11225,7 +11240,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17270-2026</t>
+          <t>A 16747-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11239,10 +11254,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46119</v>
+        <v>45030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11255,7 +11270,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11298,7 +11313,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 53296-2025</t>
+          <t>A 15067-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11312,10 +11327,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45958</v>
+        <v>45743</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11328,7 +11343,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11371,7 +11386,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17334-2026</t>
+          <t>A 54467-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11385,10 +11400,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46119</v>
+        <v>45965</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11401,7 +11416,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.3</v>
+        <v>13.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11444,7 +11459,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 54244-2025</t>
+          <t>A 15458-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11458,10 +11473,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45964</v>
+        <v>45747</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11474,7 +11489,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11517,7 +11532,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54467-2025</t>
+          <t>A 64606-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11531,10 +11546,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45965</v>
+        <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11547,7 +11562,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>13.4</v>
+        <v>7.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11590,7 +11605,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18830-2026</t>
+          <t>A 42698-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11600,14 +11615,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46128</v>
+        <v>45566</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11620,7 +11635,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11663,7 +11678,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31051-2022</t>
+          <t>A 50939-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11677,10 +11692,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44769</v>
+        <v>45602</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11693,7 +11708,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11753,7 +11768,7 @@
         <v>45966</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11809,7 +11824,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24892-2025</t>
+          <t>A 26025-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11823,10 +11838,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45799</v>
+        <v>45804</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11839,7 +11854,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11882,7 +11897,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15102-2024</t>
+          <t>A 38614-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11896,10 +11911,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45399</v>
+        <v>45884</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11912,7 +11927,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11955,7 +11970,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13698-2024</t>
+          <t>A 49481-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11969,10 +11984,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45390</v>
+        <v>45211</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11985,7 +12000,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12045,7 +12060,7 @@
         <v>45974</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12101,7 +12116,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56922-2025</t>
+          <t>A 46520-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12115,10 +12130,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45978</v>
+        <v>45582</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12131,7 +12146,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12174,7 +12189,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 50884-2025</t>
+          <t>A 56922-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12188,10 +12203,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45946</v>
+        <v>45978</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12204,7 +12219,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12247,7 +12262,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 44588-2025</t>
+          <t>A 20536-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12261,10 +12276,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45917</v>
+        <v>45057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12277,7 +12292,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12320,7 +12335,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60095-2025</t>
+          <t>A 15102-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12334,10 +12349,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45993</v>
+        <v>45399</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12350,7 +12365,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12393,7 +12408,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60328-2025</t>
+          <t>A 55618-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12407,10 +12422,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45994</v>
+        <v>45238</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12423,7 +12438,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12466,7 +12481,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 60325-2025</t>
+          <t>A 48161-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12480,10 +12495,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45994</v>
+        <v>45589</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12496,7 +12511,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12539,7 +12554,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61120-2025</t>
+          <t>A 40939-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12553,10 +12568,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46000</v>
+        <v>45558</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12569,7 +12584,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12612,7 +12627,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20714-2026</t>
+          <t>A 50884-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12626,10 +12641,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46141</v>
+        <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12642,7 +12657,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12685,7 +12700,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 20738-2026</t>
+          <t>A 20714-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12702,7 +12717,7 @@
         <v>46141</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12715,7 +12730,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12758,7 +12773,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 20864-2026</t>
+          <t>A 20738-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12772,10 +12787,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12788,7 +12803,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12831,7 +12846,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22350-2026</t>
+          <t>A 65120-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12841,14 +12856,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46154</v>
+        <v>45287</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12861,7 +12876,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>11.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12904,7 +12919,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22353-2026</t>
+          <t>A 20864-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12918,10 +12933,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46154</v>
+        <v>46142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12934,7 +12949,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12977,7 +12992,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 33921-2023</t>
+          <t>A 22353-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12991,10 +13006,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45134</v>
+        <v>46154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13007,7 +13022,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13050,7 +13065,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 1937-2026</t>
+          <t>A 60325-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13060,14 +13075,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46035</v>
+        <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13079,13 +13094,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13128,7 +13138,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33915-2023</t>
+          <t>A 22350-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13142,10 +13152,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45134</v>
+        <v>46154</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13158,7 +13168,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13201,7 +13211,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 18997-2024</t>
+          <t>A 60095-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13215,10 +13225,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45427</v>
+        <v>45993</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13231,7 +13241,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13274,7 +13284,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27867-2025</t>
+          <t>A 43987-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13288,10 +13298,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45817</v>
+        <v>44838</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13304,7 +13314,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13347,7 +13357,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 23532-2026</t>
+          <t>A 60328-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13361,10 +13371,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46163</v>
+        <v>45994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13377,7 +13387,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>8.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13420,7 +13430,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 62439-2025</t>
+          <t>A 27867-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13434,10 +13444,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46007</v>
+        <v>45817</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13450,7 +13460,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13493,7 +13503,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 44583-2025</t>
+          <t>A 1937-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13503,14 +13513,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45917</v>
+        <v>46035</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13522,8 +13532,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13566,7 +13581,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 6140-2024</t>
+          <t>A 17985-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13580,10 +13595,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45337</v>
+        <v>44683</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13596,7 +13611,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13639,7 +13654,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 50939-2024</t>
+          <t>A 56829-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13653,10 +13668,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45602</v>
+        <v>45244</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13669,7 +13684,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13712,7 +13727,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24769-2026</t>
+          <t>A 61120-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13722,14 +13737,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46171</v>
+        <v>46000</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13742,7 +13757,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13785,7 +13800,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58972-2024</t>
+          <t>A 43817-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13799,10 +13814,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45636</v>
+        <v>45187</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13815,7 +13830,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13858,7 +13873,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 27181-2023</t>
+          <t>A 20584-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13872,10 +13887,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45096</v>
+        <v>45057</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13888,7 +13903,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13931,7 +13946,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33925-2023</t>
+          <t>A 59745-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13945,10 +13960,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45134</v>
+        <v>45639</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13961,7 +13976,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14004,7 +14019,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 43798-2024</t>
+          <t>A 18997-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14018,10 +14033,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45571</v>
+        <v>45427</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14034,7 +14049,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14077,7 +14092,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 48161-2024</t>
+          <t>A 13698-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14091,10 +14106,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45589</v>
+        <v>45390</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14107,7 +14122,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>42</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14150,7 +14165,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 16747-2023</t>
+          <t>A 33915-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14164,10 +14179,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45030</v>
+        <v>45134</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14180,7 +14195,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14240,7 +14255,7 @@
         <v>45672</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14296,7 +14311,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 11439-2022</t>
+          <t>A 23862-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14310,10 +14325,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44630</v>
+        <v>44722</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14326,7 +14341,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>10.6</v>
+        <v>2.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14369,7 +14384,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 73226-2021</t>
+          <t>A 40721-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14383,10 +14398,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44550</v>
+        <v>44824</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14399,7 +14414,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14442,7 +14457,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28420-2026</t>
+          <t>A 23532-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14456,10 +14471,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46197</v>
+        <v>46163</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14472,7 +14487,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14515,7 +14530,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 17871-2024</t>
+          <t>A 62439-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14525,14 +14540,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45419</v>
+        <v>46007</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14545,7 +14560,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14588,7 +14603,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 15309-2022</t>
+          <t>A 59692-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14598,14 +14613,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44659</v>
+        <v>45256</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14618,7 +14633,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14678,7 +14693,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14734,7 +14749,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 65120-2023</t>
+          <t>A 28385-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14744,14 +14759,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45287</v>
+        <v>44747</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14764,7 +14779,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14807,7 +14822,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 29365-2026</t>
+          <t>A 7795-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14821,10 +14836,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46203</v>
+        <v>44973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14880,7 +14895,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 12910-2023</t>
+          <t>A 44583-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14894,10 +14909,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45001</v>
+        <v>45917</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14910,7 +14925,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14953,7 +14968,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 23862-2022</t>
+          <t>A 146-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14967,10 +14982,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44722</v>
+        <v>46024</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14983,7 +14998,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15026,7 +15041,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 7795-2023</t>
+          <t>A 24769-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15036,14 +15051,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44973</v>
+        <v>46171</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15056,7 +15071,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15099,7 +15114,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 12610-2024</t>
+          <t>A 47630-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15113,10 +15128,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45382</v>
+        <v>44852</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15129,7 +15144,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15172,7 +15187,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 6172-2024</t>
+          <t>A 7420-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15186,10 +15201,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45337</v>
+        <v>45345</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15202,7 +15217,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15245,7 +15260,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30418-2026</t>
+          <t>A 4195-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15259,10 +15274,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46209</v>
+        <v>46044</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15275,7 +15290,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>8.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15318,7 +15333,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 12853-2023</t>
+          <t>A 50002-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15332,10 +15347,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45001</v>
+        <v>45215</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15348,7 +15363,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15391,7 +15406,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 59745-2024</t>
+          <t>A 15099-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15405,10 +15420,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45639</v>
+        <v>45399</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15421,7 +15436,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15464,7 +15479,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 58292-2023</t>
+          <t>A 15107-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15474,14 +15489,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45250</v>
+        <v>45399</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15494,7 +15509,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>19</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15537,7 +15552,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 64606-2023</t>
+          <t>A 1930-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15551,10 +15566,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45281</v>
+        <v>46035</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15567,7 +15582,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15610,7 +15625,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35551-2026</t>
+          <t>A 1925-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15624,10 +15639,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46262</v>
+        <v>46035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15640,7 +15655,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15683,7 +15698,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31386-2026</t>
+          <t>A 1933-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15697,10 +15712,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46220</v>
+        <v>46035</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15713,7 +15728,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15756,7 +15771,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31389-2026</t>
+          <t>A 32838-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15770,10 +15785,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46220</v>
+        <v>44784</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15786,7 +15801,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15829,7 +15844,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31564-2026</t>
+          <t>A 505-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15843,10 +15858,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46224</v>
+        <v>44930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15859,7 +15874,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15902,7 +15917,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31562-2026</t>
+          <t>A 19051-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15916,10 +15931,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46224</v>
+        <v>45047</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15932,7 +15947,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15975,7 +15990,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 12823-2022</t>
+          <t>A 6270-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15989,10 +16004,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44642</v>
+        <v>44965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16005,7 +16020,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16048,7 +16063,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 16551-2024</t>
+          <t>A 63509-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16058,14 +16073,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45408</v>
+        <v>45274</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16078,7 +16093,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16121,7 +16136,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27815-2024</t>
+          <t>A 9289-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16131,14 +16146,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45475</v>
+        <v>46070</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16150,8 +16165,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16194,7 +16214,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 17172-2023</t>
+          <t>A 13334-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16208,10 +16228,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45034</v>
+        <v>44645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16224,7 +16244,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16267,7 +16287,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 505-2023</t>
+          <t>A 28420-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16281,10 +16301,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44930</v>
+        <v>46197</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16297,7 +16317,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16340,7 +16360,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28190-2022</t>
+          <t>A 20280-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16354,10 +16374,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44746</v>
+        <v>45056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16370,7 +16390,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16413,7 +16433,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20536-2023</t>
+          <t>A 24940-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16427,10 +16447,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45057</v>
+        <v>45085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16443,7 +16463,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16486,7 +16506,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28385-2022</t>
+          <t>A 33921-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16500,10 +16520,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44747</v>
+        <v>45134</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16516,7 +16536,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16559,7 +16579,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 9732-2023</t>
+          <t>A 48494-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16573,10 +16593,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44978</v>
+        <v>45592</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16589,7 +16609,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16632,7 +16652,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 7640-2024</t>
+          <t>A 12853-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16646,10 +16666,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45348</v>
+        <v>45001</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16662,7 +16682,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16705,7 +16725,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 17077-2023</t>
+          <t>A 21140-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16719,10 +16739,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45034</v>
+        <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16735,7 +16755,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16778,7 +16798,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 46520-2024</t>
+          <t>A 29365-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16792,10 +16812,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45582</v>
+        <v>46203</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16808,7 +16828,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16851,7 +16871,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 18715-2023</t>
+          <t>A 6752-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16865,10 +16885,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45043</v>
+        <v>44966</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16881,7 +16901,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16924,7 +16944,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 14798-2024</t>
+          <t>A 13491-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16934,14 +16954,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45397</v>
+        <v>46094</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16953,13 +16973,8 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16998,31 +17013,11 @@
         <v>0</v>
       </c>
       <c r="V214" s="2" t="inlineStr"/>
-      <c r="Z214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/knärot/A 14798-2024 karta knärot.png", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AA214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomål/A 14798-2024 FSC-klagomål.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AB214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/klagomålsmail/A 14798-2024 FSC-klagomål mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AC214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsyn/A 14798-2024 tillsynsbegäran.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
-      <c r="AD214">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1487/tillsynsmail/A 14798-2024 tillsynsbegäran mail.docx", "A 14798-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32532-2026</t>
+          <t>A 17172-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17036,10 +17031,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46239</v>
+        <v>45034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17052,7 +17047,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17095,7 +17090,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32525-2026</t>
+          <t>A 32843-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17109,10 +17104,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46239</v>
+        <v>44784</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17125,7 +17120,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>11.5</v>
+        <v>2.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17168,7 +17163,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32527-2026</t>
+          <t>A 28190-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17182,10 +17177,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46239</v>
+        <v>44746</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17198,7 +17193,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17241,7 +17236,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38798-2026</t>
+          <t>A 30418-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17255,10 +17250,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46286</v>
+        <v>46209</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17271,7 +17266,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17314,7 +17309,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33412-2026</t>
+          <t>A 14875-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17328,10 +17323,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46246</v>
+        <v>46104</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17344,7 +17339,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17387,7 +17382,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 19051-2023</t>
+          <t>A 14853-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17401,10 +17396,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45047</v>
+        <v>46104</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17417,7 +17412,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17460,7 +17455,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 59692-2023</t>
+          <t>A 14886-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17474,10 +17469,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45256</v>
+        <v>46104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17490,7 +17485,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17533,7 +17528,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 49131-2024</t>
+          <t>A 14873-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17547,10 +17542,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45594</v>
+        <v>46104</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17563,7 +17558,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17606,7 +17601,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37704-2026</t>
+          <t>A 12910-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17620,10 +17615,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46279</v>
+        <v>45001</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17636,7 +17631,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17679,7 +17674,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33942-2023</t>
+          <t>A 6172-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17693,10 +17688,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45134</v>
+        <v>45337</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17709,7 +17704,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17752,7 +17747,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 33354-2026</t>
+          <t>A 16192-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17766,10 +17761,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46247</v>
+        <v>46111</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17781,8 +17776,13 @@
           <t>VÄNERSBORG</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>11.1</v>
+        <v>6.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17825,7 +17825,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 49481-2023</t>
+          <t>A 33925-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17839,10 +17839,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45211</v>
+        <v>45134</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17898,7 +17898,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 57699-2023</t>
+          <t>A 17270-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17912,10 +17912,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45246</v>
+        <v>46119</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17971,7 +17971,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 13334-2022</t>
+          <t>A 17334-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17985,10 +17985,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44645</v>
+        <v>46119</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18044,7 +18044,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 6179-2024</t>
+          <t>A 15309-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18054,14 +18054,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45337</v>
+        <v>44659</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18117,7 +18117,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 56829-2023</t>
+          <t>A 11439-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45244</v>
+        <v>44630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 23700-2023</t>
+          <t>A 18830-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45077</v>
+        <v>46128</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18263,7 +18263,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 6270-2023</t>
+          <t>A 33033-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44965</v>
+        <v>45517</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18336,7 +18336,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 1749-2024</t>
+          <t>A 49131-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18350,10 +18350,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45307</v>
+        <v>45594</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18409,7 +18409,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 41287-2026</t>
+          <t>A 35551-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18423,10 +18423,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46300</v>
+        <v>46262</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18482,7 +18482,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 20280-2023</t>
+          <t>A 61409-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18496,10 +18496,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45056</v>
+        <v>44909</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18555,7 +18555,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 40939-2024</t>
+          <t>A 44588-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18569,10 +18569,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45558</v>
+        <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18628,7 +18628,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 519-2023</t>
+          <t>A 31386-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18642,10 +18642,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44930</v>
+        <v>46220</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18701,7 +18701,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 61825-2021</t>
+          <t>A 48496-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18715,10 +18715,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44501</v>
+        <v>45592</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18774,7 +18774,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 61826-2021</t>
+          <t>A 24892-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18788,10 +18788,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44501</v>
+        <v>45799</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18847,7 +18847,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 120-2024</t>
+          <t>A 56725-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18861,10 +18861,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45294</v>
+        <v>45244</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18920,7 +18920,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 33476-2022</t>
+          <t>A 31389-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18930,14 +18930,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44788</v>
+        <v>46220</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18993,7 +18993,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 46320-2024</t>
+          <t>A 17871-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19003,14 +19003,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45581</v>
+        <v>45419</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19066,7 +19066,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 6752-2023</t>
+          <t>A 31562-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19080,10 +19080,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44966</v>
+        <v>46224</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 14722-2023</t>
+          <t>A 31564-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19149,14 +19149,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45014</v>
+        <v>46224</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19212,7 +19212,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 56725-2023</t>
+          <t>A 369-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45244</v>
+        <v>44929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19285,7 +19285,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 43799-2024</t>
+          <t>A 519-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19299,10 +19299,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45571</v>
+        <v>44930</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19358,7 +19358,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33912-2023</t>
+          <t>A 43798-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19372,10 +19372,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45134</v>
+        <v>45571</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 48496-2024</t>
+          <t>A 23700-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19445,10 +19445,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45592</v>
+        <v>45077</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19504,7 +19504,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 22326-2025</t>
+          <t>A 32525-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45786</v>
+        <v>46239</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 10525-2025</t>
+          <t>A 32527-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19591,10 +19591,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45721</v>
+        <v>46239</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 42605-2024</t>
+          <t>A 32532-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45565</v>
+        <v>46239</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19723,7 +19723,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 13196-2025</t>
+          <t>A 38798-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19737,10 +19737,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45735</v>
+        <v>46286</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19796,7 +19796,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 13666-2025</t>
+          <t>A 33412-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19806,14 +19806,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45736</v>
+        <v>46246</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19869,7 +19869,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 13674-2025</t>
+          <t>A 33354-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19883,10 +19883,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45736</v>
+        <v>46247</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.4</v>
+        <v>11.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19942,7 +19942,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 11883-2025</t>
+          <t>A 37704-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19952,14 +19952,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45728</v>
+        <v>46279</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20015,7 +20015,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 24560-2025</t>
+          <t>A 41287-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20029,10 +20029,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45798</v>
+        <v>46300</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20105,7 +20105,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45432</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45742</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45040</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45040</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45691</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>45931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45589</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45721</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45971</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45238</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46128</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>46191</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44886</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44497</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44497</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44693</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44693</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44659</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45058</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45099</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44909</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44788</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45397</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45382</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45250</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45313</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>45244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45884</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45419</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>44501</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>44550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>45408</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>45446</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44769</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>45307</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45294</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>44929</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45096</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44980</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>45896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>45896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45896</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45897</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45571</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45902</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45077</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45337</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45034</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45134</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45905</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45636</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45646</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44881</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>45134</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45918</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45917</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>45922</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45786</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45014</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45721</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45571</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45030</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45736</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45736</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45735</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45930</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45566</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45337</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45728</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45798</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45798</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45798</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44587</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45471</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44587</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45211</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45281</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45602</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45057</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45399</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45238</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45938</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45589</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45589</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45603</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45328</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45811</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45728</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45287</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45826</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45057</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>45639</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>45958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44683</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>45244</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45964</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45672</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45965</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45390</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44722</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44824</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45966</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45582</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44606</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44747</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45974</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45256</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45978</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>44973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45743</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45804</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45345</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>46094</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45399</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45399</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45043</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45751</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46104</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>46104</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>46104</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>46104</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44642</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45246</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45475</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44784</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44714</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44930</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46111</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45047</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44965</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45994</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45274</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>46119</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>46119</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45994</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>46000</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>46128</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45056</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45917</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45134</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45592</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45001</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44966</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46024</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45799</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44784</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44746</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46044</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45001</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45337</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45215</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45134</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45946</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>46141</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>46035</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>46035</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>46035</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>46141</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>46142</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>46070</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>46154</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>46154</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45817</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45427</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45134</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46007</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45917</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>46197</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>46203</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>46209</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46220</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>46220</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>46224</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>46224</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>46239</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>46239</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>46286</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46246</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46247</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46279</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>46300</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>46262</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45432</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt VÄNERSBORG.xlsx
+++ b/Översikt VÄNERSBORG.xlsx
@@ -599,7 +599,7 @@
         <v>44137</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44684</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>44753</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45742</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45838</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>45040</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>44753</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>44753</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45244</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45040</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45691</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>45931</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45589</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>45721</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45971</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45238</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>46128</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45166</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>46191</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44886</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>44753</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44551</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44565</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44851</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>44488</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>44753</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44857</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44563</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44497</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44585</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44497</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>44753</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44635</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44693</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44693</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44642</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44650</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44753</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44659</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45058</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>45099</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45517</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44909</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44788</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45397</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45382</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45250</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45313</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>45244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45884</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>45419</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>45337</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>44501</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>44501</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>